--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -2155,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2193,40 +2193,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0FN4GJ9S1</t>
+          <t>B07LDJJ4JP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FBK79790</t>
+          <t>FBA72564</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>715</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B07LDJJ4JP</t>
+          <t>B07RMH1BMS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FBA72564</t>
+          <t>FBA72563</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2243,18 +2243,18 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>159</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B07RMH1BMS</t>
+          <t>B07LDHVWTF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FBA72563</t>
+          <t>FBA72562</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2271,18 +2271,18 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>103</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B07LDHVWTF</t>
+          <t>B07S3X9JYX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FBA72562</t>
+          <t>FBA72570</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2299,18 +2299,18 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B07S3X9JYX</t>
+          <t>B07RMH1F26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FBA72570</t>
+          <t>FBA72907</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2327,18 +2327,18 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B0GQCB4PJC</t>
+          <t>B0GQGZVGLL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FBA80079</t>
+          <t>FBA80082</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2361,12 +2361,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B0GQGK4GJ7</t>
+          <t>B0GQC12GDP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FBA80081</t>
+          <t>FBA80078</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2389,12 +2389,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B0GQGXR9D7</t>
+          <t>B0GQGK4GJ7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FBA80080</t>
+          <t>FBA80081</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2417,12 +2417,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0GQGZVGLL</t>
+          <t>B0GQCB4PJC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FBA80082</t>
+          <t>FBA80079</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2445,17 +2445,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B07RMH1F26</t>
+          <t>B0GQGXR9D7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FBA72907</t>
+          <t>FBA80080</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -2473,17 +2473,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0GQC12GDP</t>
+          <t>B00STAYV6C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FBA80078</t>
+          <t>FBS66968</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2495,18 +2495,18 @@
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B00STAYV6C</t>
+          <t>B0DKJJDZSF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FBS66968</t>
+          <t>FBS79626</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2520,21 +2520,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B085YFCGNF</t>
+          <t>B07RPQWF6B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FBA74027</t>
+          <t>FBP75458</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
@@ -2585,12 +2585,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0DKJJDZSF</t>
+          <t>B07SPCV89W</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FBS79626</t>
+          <t>FBA72904</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>4</v>
@@ -2613,12 +2613,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B07RPQWF6B</t>
+          <t>B085YFCGNF</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FBP75458</t>
+          <t>FBA74027</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
@@ -2641,12 +2641,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B07SPCV89W</t>
+          <t>B00DUCIUDY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FBA72904</t>
+          <t>FBO70542</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2660,21 +2660,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B00DUCIUDY</t>
+          <t>B0DKJG6R31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FBO70542</t>
+          <t>FBS79623</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0DKJG6R31</t>
+          <t>B07N6KCJM4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FBS79623</t>
+          <t>FBA72566</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
@@ -2725,12 +2725,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B07N6KCJM4</t>
+          <t>B00VATDB10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FBA72566</t>
+          <t>FBN69542</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B00VATDB10</t>
+          <t>B0BQZGJHKV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FBN69542</t>
+          <t>FBS77967</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
         <v>2</v>
@@ -2781,12 +2781,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0BQZGJHKV</t>
+          <t>B08K969L6V</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FBS77967</t>
+          <t>FBK74025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -2893,12 +2893,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B08K969L6V</t>
+          <t>B00Z52HG6O</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FBK74025</t>
+          <t>FBO77065</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2912,21 +2912,21 @@
         </is>
       </c>
       <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
         <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B01MZWUN47</t>
+          <t>B00DH9NPBM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FBK72029</t>
+          <t>FBO66628</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2949,12 +2949,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B00DH9NPBM</t>
+          <t>B01MZWUN47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FBO66628</t>
+          <t>FBK72029</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2977,12 +2977,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B00Z52HG6O</t>
+          <t>B088NYP2LX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FBO77065</t>
+          <t>FBA78457</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -3005,12 +3005,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0CZSFTY4V</t>
+          <t>B088NZCC28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FBS79431</t>
+          <t>FBA78458</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -3033,12 +3033,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B088NZCC28</t>
+          <t>B0DKJJBBTS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FBA78458</t>
+          <t>FBA79620</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -3061,12 +3061,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B088NYP2LX</t>
+          <t>B0CZSFTY4V</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FBA78457</t>
+          <t>FBS79431</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -3117,12 +3117,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0DSBQL4PK</t>
+          <t>B0CQNSQ9BJ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBA79747</t>
+          <t>FBA79250</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -3145,12 +3145,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0DKJJBBTS</t>
+          <t>B0DJ2XK4NR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FBA79620</t>
+          <t>FBS79646</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -3173,12 +3173,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0CQNSQ9BJ</t>
+          <t>B0FTKJC5JW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FBA79250</t>
+          <t>FBA79936</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -3201,12 +3201,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0DJ2XK4NR</t>
+          <t>B0DSBQL4PK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FBS79646</t>
+          <t>FBA79747</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3220,1130 +3220,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>B0FTKJC5JW</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>FBA79936</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>B074ZHN54C</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>FBN66667</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>B00KNK7UHI</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>FBS76475</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>B079HF6BL3</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>FBO69618</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>B07T53XXCF</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>FBA79149</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>2</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>B094R8FJ6J</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>FBS79559</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>2</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>B09876MGQ1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>FBO74936</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>B07SRVV8V4</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>FBA71998</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>2</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>B0CJ6ZW8FP</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>FBA79141</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>B0CFH5R7Y7</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>FBA79002</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>B0CFH2C369</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>FBA79001</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>4</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>B0CFH2B2MV</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>FBA79000</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>4</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>B0CFFQK45G</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>FBA78999</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>4</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>B0CCHNK41V</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>FBA79044</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>B0CCHMD6QH</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>FBA79047</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>2</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>B0CCHGLV6Y</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>FBA79051</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>2</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>B0C7WLLHPG</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>FBA79036</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>2</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>B0C77PP76Y</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>FBA79020</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>2</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>B0BSHTX51F</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>FBA79220</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>2</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>B0BLK9QL7X</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>FBA76731</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>3</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>B0BLJYX15C</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>FBA76709</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>B0BLK1Z7PJ</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>FBA76713</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>3</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>B0BHCJHWCL</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>FBO76786</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>2</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>B0BFZHWXBM</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>FBA76896</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>B07T2XZ5K4</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>FBA79802</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>2</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>B0D956WQVM</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>FBS79543</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>2</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>B0DJ2VY8GL</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>FBS79648</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>2</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>B0D9568SNM</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>FBS79560</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>2</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>B0D9361BZL</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>FBS79535</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>2</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>B0CZSDZ5V1</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>FBA79420</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>2</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>B0D9536B5Z</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>FBS79546</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>2</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>B0D936GDTN</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>FBS79536</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>2</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>B0FM3LBN87</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>FBK79595</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>B0F99VFBGY</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>FBK79685</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>B0F2MZJH82</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>FBA79987</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>B0DT37Y5FY</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>FBA79902</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>2</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>B0DSBT6FW8</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>FBA79734</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>2</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>B0DSBR61QS</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>FBA79901</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>2</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>B0DSBPRB2W</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>FBA79739</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>2</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>B0FRVT4SJ1</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>FBA79922</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>2</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -694,6 +695,34 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Sales raw vs snapshot (per brand×wk)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -723,6 +724,34 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Cross-route inventory rule consistency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -798,10 +827,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>154271</v>
+        <v>148727</v>
       </c>
       <c r="D3" t="n">
-        <v>154271</v>
+        <v>148727</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -19,6 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -752,6 +754,62 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Cross-route sales rule consistency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Cross-route ads rule consistency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -21,6 +21,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -810,6 +813,90 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Cross-route sessions consistency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Cross-route Amazon+1P units consistency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Cross-route per-brand totals consistency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,16 +33,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -53,7 +50,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -61,21 +58,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,32 +433,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -683,7 +671,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -711,7 +699,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -739,7 +727,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -763,11 +751,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sales_trend_amzn+1p_gmv</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ams_trend_gmv</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -776,7 +784,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route sales rule consistency</t>
+          <t>B0GYS6CJD9</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>674.58</v>
+      </c>
+      <c r="D2" t="n">
+        <v>674.58</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
         </is>
       </c>
     </row>
@@ -795,7 +817,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -823,7 +845,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -847,11 +869,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sales_trend_units</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ams_trend_units</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -860,7 +902,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route Amazon+1P units consistency</t>
+          <t>B0GYS6CJD9</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
         </is>
       </c>
     </row>
@@ -879,7 +935,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -907,32 +963,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -972,10 +1028,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>148727</v>
+        <v>145093</v>
       </c>
       <c r="D3" t="n">
-        <v>148727</v>
+        <v>145093</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1001,7 +1057,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1029,7 +1085,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1057,32 +1113,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1211,26 +1267,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1405,16 +1461,86 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>DUPLICATE ASIN (2× in master)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B08V41MK2D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DUPLICATE ASIN (2× in master)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B01EUVE61I</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DUPLICATE ASIN (2× in master)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B00JGMUJNQ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>DUPLICATE SKU (2× in master)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
         <is>
           <t>FBK77102</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DUPLICATE SKU (2× in master)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FBA74928</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DUPLICATE SKU (2× in master)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1431,7 +1557,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1455,11 +1581,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1468,7 +1609,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand missing from a layer this week</t>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in sales for W22</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in sales for W22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in sales for W22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in sales for W22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in inventory for W22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in inventory for W22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>22</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in inventory for W22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>22</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in inventory for W22</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1781,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,6 +653,198 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8291</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-8291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>20416</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-20416</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>73141</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-73141</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5558</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-5558</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>blinkit</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2062</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-2062</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>18850</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-18850</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>33419</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-33419</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ynt</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1523</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1523</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3468,678 @@
         <v>-4</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>23</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>7423</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-7423</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>23</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>669</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-669</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>23</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>199</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-199</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>23</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>4950</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-4950</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>23</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>13369</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-13369</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>23</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>523</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-523</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>23</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1574</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-1574</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>23</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>31928</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-31928</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>23</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>34308</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-34308</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>23</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2191</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-2191</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>23</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>4714</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-4714</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>23</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1205</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-1205</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>23</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>4330</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-4330</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>23</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>9</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>23</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>14</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>23</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>blinkit</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>468</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-468</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>23</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>blinkit</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1594</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-1594</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>23</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>9768</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-9768</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>23</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>7002</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-7002</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>23</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>80</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>23</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-2000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>23</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>23056</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-23056</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>23</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>9577</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-9577</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>23</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>286</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-286</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>23</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>500</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>23</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ynt</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>154</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-154</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>23</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ynt</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1355</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>-1355</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>23</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ynt</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>14</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -24,6 +24,7 @@
     <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,198 +654,6 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>UNITS MISMATCH (silent drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>23</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1p</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>8291</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-8291</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>23</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>20416</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-20416</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>23</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>73141</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-73141</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>23</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>5558</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-5558</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>23</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>blinkit</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2062</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-2062</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>23</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>18850</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-18850</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>23</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>33419</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-33419</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>23</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ynt</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1523</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-1523</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
         </is>
       </c>
     </row>
@@ -943,32 +752,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>sales_trend_amzn+1p_gmv</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ams_trend_gmv</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -976,21 +765,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0GYS6CJD9</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>674.58</v>
-      </c>
-      <c r="D2" t="n">
-        <v>674.58</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+          <t>clean — Cross-source sales drift (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -1061,32 +836,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>sales_trend_units</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ams_trend_units</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -1094,21 +849,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0GYS6CJD9</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+          <t>clean — Cross-source units drift (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -1145,6 +886,34 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — (info) Off-master ASINs in raw sales</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1193,13 +962,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>158014</v>
+        <v>163260</v>
       </c>
       <c r="D2" t="n">
-        <v>158014</v>
+        <v>163260</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1217,13 +986,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>145093</v>
+        <v>150483</v>
       </c>
       <c r="D3" t="n">
-        <v>145093</v>
+        <v>150483</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1344,12 +1113,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>1p</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1358,7 +1127,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1386,7 +1155,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1405,7 +1174,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>myntra</t>
+          <t>bi worldwide</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1414,7 +1183,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1442,7 +1211,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1810,11 +1579,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MISSING — no rows for audio array in sales for W22</t>
+          <t>MISSING — no rows for audio array in sales for W23</t>
         </is>
       </c>
     </row>
@@ -1830,11 +1599,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MISSING — no rows for nexlev in sales for W22</t>
+          <t>MISSING — no rows for nexlev in sales for W23</t>
         </is>
       </c>
     </row>
@@ -1850,11 +1619,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MISSING — no rows for tonor in sales for W22</t>
+          <t>MISSING — no rows for tonor in sales for W23</t>
         </is>
       </c>
     </row>
@@ -1870,11 +1639,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MISSING — no rows for white mulberry in sales for W22</t>
+          <t>MISSING — no rows for white mulberry in sales for W23</t>
         </is>
       </c>
     </row>
@@ -1890,11 +1659,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MISSING — no rows for audio array in inventory for W22</t>
+          <t>MISSING — no rows for audio array in inventory for W23</t>
         </is>
       </c>
     </row>
@@ -1910,11 +1679,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MISSING — no rows for nexlev in inventory for W22</t>
+          <t>MISSING — no rows for nexlev in inventory for W23</t>
         </is>
       </c>
     </row>
@@ -1930,11 +1699,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MISSING — no rows for tonor in inventory for W22</t>
+          <t>MISSING — no rows for tonor in inventory for W23</t>
         </is>
       </c>
     </row>
@@ -1950,11 +1719,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MISSING — no rows for white mulberry in inventory for W22</t>
+          <t>MISSING — no rows for white mulberry in inventory for W23</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3468,678 +3237,6 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>23</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1p</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>7423</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-7423</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>23</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1p</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>669</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-669</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>23</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1p</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>199</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-199</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>23</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>4950</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>-4950</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>23</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>13369</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>-13369</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>23</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>523</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-523</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>23</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>1574</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>-1574</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>23</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>31928</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>-31928</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>23</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>34308</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>-34308</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>23</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2191</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>-2191</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>23</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>4714</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>-4714</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>23</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1205</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>-1205</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>23</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>4330</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>-4330</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>23</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>9</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>23</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>14</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>23</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>blinkit</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>468</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>-468</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>23</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>blinkit</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>1594</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>-1594</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>23</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>9768</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>-9768</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>23</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>7002</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>-7002</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>23</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>80</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>23</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>-2000</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>23</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>23056</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
-        <v>-23056</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>23</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>9577</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>-9577</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>23</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>286</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="n">
-        <v>-286</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>23</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>500</v>
-      </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>23</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>ynt</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>154</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>-154</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>23</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>ynt</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>1355</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="n">
-        <v>-1355</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>23</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>ynt</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>14</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>-14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,13 +34,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -51,7 +54,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -59,12 +62,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,36 +442,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -652,6 +664,30 @@
         <v>-25</v>
       </c>
       <c r="F9" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>21311</v>
+      </c>
+      <c r="D10" t="n">
+        <v>21295</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>UNITS MISMATCH (silent drop)</t>
         </is>
@@ -668,21 +704,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>brand_folder</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>weeks_seen</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>total_qty</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — (info) Off-master ASINs in raw inv</t>
-        </is>
+          <t>B0GYSS16FJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FBA80111</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +782,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -728,7 +810,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -756,7 +838,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -784,7 +866,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -812,7 +894,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -840,7 +922,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -868,7 +950,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -892,21 +974,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>brand_folder</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weeks_seen</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — (info) Off-master ASINs in raw sales</t>
-        </is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FBA79347</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>other_channels</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pharmaeasy</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -924,32 +1062,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -962,13 +1100,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>163260</v>
+        <v>165963</v>
       </c>
       <c r="D2" t="n">
-        <v>163260</v>
+        <v>165963</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -986,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>150483</v>
+        <v>153557</v>
       </c>
       <c r="D3" t="n">
-        <v>150483</v>
+        <v>153557</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1018,7 +1156,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1046,7 +1184,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1070,36 +1208,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1127,7 +1265,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1183,37 +1321,9 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>b2b</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1232,22 +1342,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1518,7 +1628,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1542,26 +1652,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1570,160 +1665,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>23</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in sales for W23</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>23</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in sales for W23</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in sales for W23</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>23</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in sales for W23</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>23</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in inventory for W23</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>23</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in inventory for W23</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>23</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in inventory for W23</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>23</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W23</t>
+          <t>clean — Brand missing from a layer (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -1738,36 +1680,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
@@ -3234,6 +3176,78 @@
         <v>14</v>
       </c>
       <c r="F62" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>24</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>13990</v>
+      </c>
+      <c r="E63" t="n">
+        <v>13974</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>24</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" t="n">
+        <v>9</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>24</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>18</v>
+      </c>
+      <c r="E65" t="n">
+        <v>14</v>
+      </c>
+      <c r="F65" t="n">
         <v>-4</v>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,16 +34,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -54,7 +51,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,21 +59,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,32 +434,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -708,32 +696,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -782,7 +770,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -810,7 +798,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -838,7 +826,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -866,7 +854,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -894,7 +882,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -922,7 +910,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -950,7 +938,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -974,77 +962,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>raw_sku</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>brand_folder</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>weeks_seen</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>total_units</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FBA79347</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>other_channels</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pharmaeasy</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
+          <t>clean — (info) Off-master ASINs in raw sales</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1062,32 +994,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1156,7 +1088,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1184,7 +1116,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1212,32 +1144,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1342,22 +1274,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1628,7 +1560,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1652,11 +1584,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1665,7 +1612,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand missing from a layer (diagnostic)</t>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in inventory for W24</t>
         </is>
       </c>
     </row>
@@ -1684,32 +1784,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,30 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,13 +35,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -51,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -59,12 +63,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,36 +443,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -663,19 +676,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>1p</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8520</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E10" t="n">
+        <v>180</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>21311</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>21295</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" t="n">
         <v>-16</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>UNITS MISMATCH (silent drop)</t>
         </is>
@@ -696,32 +733,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -766,20 +803,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>raw_units</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>snap_units</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>clean — Sales raw vs snapshot (per brand×wk)</t>
+      <c r="A2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1696</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1499</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-197</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ROWS LOST (ETL drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3" t="n">
+        <v>83</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ROWS LOST (ETL drop)</t>
         </is>
       </c>
     </row>
@@ -798,7 +901,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -826,7 +929,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -854,7 +957,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -882,7 +985,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -910,7 +1013,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -938,7 +1041,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -962,21 +1065,2018 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>brand_folder</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weeks_seen</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — (info) Off-master ASINs in raw sales</t>
-        </is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FBA79347</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>other_channels</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pharmaeasy</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sales_gmv</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ams_gmv</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ST-01</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>269565</v>
+      </c>
+      <c r="F2" t="n">
+        <v>269565</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26956526.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>WM-GD07-CB</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>239803</v>
+      </c>
+      <c r="F3" t="n">
+        <v>239803</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23980254.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>216958</v>
+      </c>
+      <c r="F4" t="n">
+        <v>216958</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21695849.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>198272</v>
+      </c>
+      <c r="F5" t="n">
+        <v>198272</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19827203.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MR-01</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>129582</v>
+      </c>
+      <c r="F6" t="n">
+        <v>129582</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12958222</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WM-LOD-CF</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>87956</v>
+      </c>
+      <c r="F7" t="n">
+        <v>87956</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8795593.199999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SP-01</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>84246</v>
+      </c>
+      <c r="F8" t="n">
+        <v>84246</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8424584.699999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PB-01</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>81492</v>
+      </c>
+      <c r="F9" t="n">
+        <v>81492</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8149237.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VC-01</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>71224</v>
+      </c>
+      <c r="F10" t="n">
+        <v>71224</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7122374.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>WM-LOD-WH</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>70754</v>
+      </c>
+      <c r="F11" t="n">
+        <v>70754</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7075423.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MR-02</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>69103</v>
+      </c>
+      <c r="F12" t="n">
+        <v>69103</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6910339.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>WM1ML</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>68080</v>
+      </c>
+      <c r="F13" t="n">
+        <v>68080</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6807966.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CFM-01</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>63597</v>
+      </c>
+      <c r="F14" t="n">
+        <v>63597</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6359746.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>24</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>62703</v>
+      </c>
+      <c r="F15" t="n">
+        <v>62703</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6270339</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>24</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SC-01</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>60665</v>
+      </c>
+      <c r="F16" t="n">
+        <v>60665</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6066525.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>WM-MODL-WH</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>50851</v>
+      </c>
+      <c r="F17" t="n">
+        <v>50851</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5085084.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ST-03</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>47540</v>
+      </c>
+      <c r="F18" t="n">
+        <v>47540</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4753983.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>24</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AM-W14</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5253</v>
+      </c>
+      <c r="E19" t="n">
+        <v>52534</v>
+      </c>
+      <c r="F19" t="n">
+        <v>47281</v>
+      </c>
+      <c r="G19" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>24</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>V-03</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>45147</v>
+      </c>
+      <c r="F20" t="n">
+        <v>45147</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4514745.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>24</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>WM-LOD-BK</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>42453</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42453</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4245254.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EA-02</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>35981</v>
+      </c>
+      <c r="F22" t="n">
+        <v>35981</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3598136.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>24</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TVMF1ML</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>33857</v>
+      </c>
+      <c r="F23" t="n">
+        <v>33857</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3385678</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AI-14</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>60584</v>
+      </c>
+      <c r="E24" t="n">
+        <v>93630</v>
+      </c>
+      <c r="F24" t="n">
+        <v>33046</v>
+      </c>
+      <c r="G24" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>WM-GS1M-BK</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>30286</v>
+      </c>
+      <c r="F25" t="n">
+        <v>30286</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3028558</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SPM-01</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>26689</v>
+      </c>
+      <c r="F26" t="n">
+        <v>26689</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2668899.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>WM-SE08-CF</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>25425</v>
+      </c>
+      <c r="F27" t="n">
+        <v>25425</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2542542.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AM-K1</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>23642</v>
+      </c>
+      <c r="F28" t="n">
+        <v>23642</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2364152.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CFM-03</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>23555</v>
+      </c>
+      <c r="F29" t="n">
+        <v>23555</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2355508.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SM-01</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>22536</v>
+      </c>
+      <c r="F30" t="n">
+        <v>22536</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2253644.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AM-W47 WIRED</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12193</v>
+      </c>
+      <c r="E31" t="n">
+        <v>34547</v>
+      </c>
+      <c r="F31" t="n">
+        <v>22354</v>
+      </c>
+      <c r="G31" t="n">
+        <v>183.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AM-W45</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>233515</v>
+      </c>
+      <c r="E32" t="n">
+        <v>255612</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22097</v>
+      </c>
+      <c r="G32" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EA-01</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20508</v>
+      </c>
+      <c r="F33" t="n">
+        <v>20508</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2050847.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>24</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ST-02</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>20337</v>
+      </c>
+      <c r="F34" t="n">
+        <v>20337</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2033728.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>24</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>WM-HA2M-BK</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>18635</v>
+      </c>
+      <c r="F35" t="n">
+        <v>18635</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1863471</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>24</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HSB-04</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>18344</v>
+      </c>
+      <c r="F36" t="n">
+        <v>18344</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1834406.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>24</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GS-02</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16264</v>
+      </c>
+      <c r="F37" t="n">
+        <v>16264</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1626440.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>24</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HDWF1ML</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>15758</v>
+      </c>
+      <c r="F38" t="n">
+        <v>15758</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1575766</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>WM-GS2M-BK</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>14573</v>
+      </c>
+      <c r="F39" t="n">
+        <v>14573</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1457288</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>24</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SB-01</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>26419</v>
+      </c>
+      <c r="E40" t="n">
+        <v>40849</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14431</v>
+      </c>
+      <c r="G40" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>24</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SS-02</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>14384</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14384</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1438390.7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>24</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>WM-LOD-IN</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>14151</v>
+      </c>
+      <c r="F42" t="n">
+        <v>14151</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1415084.7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>24</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AI-13</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>137450</v>
+      </c>
+      <c r="E43" t="n">
+        <v>151412</v>
+      </c>
+      <c r="F43" t="n">
+        <v>13963</v>
+      </c>
+      <c r="G43" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>24</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SW-01</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>13783</v>
+      </c>
+      <c r="F44" t="n">
+        <v>13783</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1378305.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>24</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AM-W32</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10167</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10167</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1016694.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>24</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AM-W19</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10164</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10164</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1016440.7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>24</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AH-50</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>172795</v>
+      </c>
+      <c r="E47" t="n">
+        <v>182958</v>
+      </c>
+      <c r="F47" t="n">
+        <v>10164</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>24</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LE-02</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10164</v>
+      </c>
+      <c r="F48" t="n">
+        <v>10164</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1016440.7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>24</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10084</v>
+      </c>
+      <c r="E49" t="n">
+        <v>20168</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10084</v>
+      </c>
+      <c r="G49" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>24</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FS-01</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10079</v>
+      </c>
+      <c r="F50" t="n">
+        <v>10079</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1007881.4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>24</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AA-21</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>70829</v>
+      </c>
+      <c r="E51" t="n">
+        <v>80584</v>
+      </c>
+      <c r="F51" t="n">
+        <v>9755</v>
+      </c>
+      <c r="G51" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>24</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HSB-03</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>8258</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8258</v>
+      </c>
+      <c r="G52" t="n">
+        <v>825847.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>24</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AM-S1</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>147442</v>
+      </c>
+      <c r="E53" t="n">
+        <v>155492</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8050</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>24</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HU-02</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>7623</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7623</v>
+      </c>
+      <c r="G54" t="n">
+        <v>762288.1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>24</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BR-01</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>7623</v>
+      </c>
+      <c r="F55" t="n">
+        <v>7623</v>
+      </c>
+      <c r="G55" t="n">
+        <v>762288.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>24</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AM-C47</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2414</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9658</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7243</v>
+      </c>
+      <c r="G56" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>24</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VLMS1ML</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>7116</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7116</v>
+      </c>
+      <c r="G57" t="n">
+        <v>711610.2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>24</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>70331</v>
+      </c>
+      <c r="E58" t="n">
+        <v>77434</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7103</v>
+      </c>
+      <c r="G58" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>24</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AI-03</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>20334</v>
+      </c>
+      <c r="E59" t="n">
+        <v>27146</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6812</v>
+      </c>
+      <c r="G59" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HDGS1ML</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>6779</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6779</v>
+      </c>
+      <c r="G60" t="n">
+        <v>677881.4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>24</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BE-4</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>6778</v>
+      </c>
+      <c r="E61" t="n">
+        <v>13556</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6778</v>
+      </c>
+      <c r="G61" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>24</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AM-W47 WIRELESS</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1609</v>
+      </c>
+      <c r="E62" t="n">
+        <v>8047</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6437</v>
+      </c>
+      <c r="G62" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>24</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>VC-02</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>6396</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6396</v>
+      </c>
+      <c r="G63" t="n">
+        <v>639576.3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>24</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TVCT1ML</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>6181</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6181</v>
+      </c>
+      <c r="G64" t="n">
+        <v>618050.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>24</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>WM-HA1M-BK</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>5803</v>
+      </c>
+      <c r="F65" t="n">
+        <v>5803</v>
+      </c>
+      <c r="G65" t="n">
+        <v>580338</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>24</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AM-W22</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>17283</v>
+      </c>
+      <c r="E66" t="n">
+        <v>23044</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5761</v>
+      </c>
+      <c r="G66" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>24</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AH-45 BK</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>59624</v>
+      </c>
+      <c r="E67" t="n">
+        <v>65098</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5475</v>
+      </c>
+      <c r="G67" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>24</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AP-04</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>5253</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5253</v>
+      </c>
+      <c r="G68" t="n">
+        <v>525339</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>24</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DH-01</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>5084</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5084</v>
+      </c>
+      <c r="G69" t="n">
+        <v>508389.8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>24</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>GS-05</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>5082</v>
+      </c>
+      <c r="F70" t="n">
+        <v>5082</v>
+      </c>
+      <c r="G70" t="n">
+        <v>508220.3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>24</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LR-02</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>5069</v>
+      </c>
+      <c r="F71" t="n">
+        <v>5069</v>
+      </c>
+      <c r="G71" t="n">
+        <v>506865.3</v>
       </c>
     </row>
   </sheetData>
@@ -994,32 +3094,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1088,7 +3188,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1116,7 +3216,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1144,32 +3244,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1274,22 +3374,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1560,7 +3660,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1584,26 +3684,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1612,160 +3697,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>24</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>24</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>24</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W24</t>
+          <t>clean — Brand missing from a layer (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -1780,36 +3712,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
@@ -3285,22 +5217,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>1p</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13990</v>
+        <v>7603</v>
       </c>
       <c r="E63" t="n">
-        <v>13974</v>
+        <v>7772</v>
       </c>
       <c r="F63" t="n">
-        <v>-16</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64">
@@ -3314,17 +5246,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>1p</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>686</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>697</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -3333,21 +5265,69 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>13990</v>
+      </c>
+      <c r="E65" t="n">
+        <v>13974</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>24</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>9</v>
+      </c>
+      <c r="F66" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>24</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>white mulberry</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>b2b - ampm</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D67" t="n">
         <v>18</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E67" t="n">
         <v>14</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F67" t="n">
         <v>-4</v>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,43 +676,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8520</v>
+        <v>21311</v>
       </c>
       <c r="D10" t="n">
-        <v>8700</v>
+        <v>21295</v>
       </c>
       <c r="E10" t="n">
-        <v>180</v>
+        <v>-16</v>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>UNITS MISMATCH (silent drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>24</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>21311</v>
-      </c>
-      <c r="D11" t="n">
-        <v>21295</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-16</v>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>UNITS MISMATCH (silent drop)</t>
         </is>
@@ -803,86 +779,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>raw_units</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>snap_units</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1696</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1499</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-197</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ROWS LOST (ETL drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tonor</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>91</v>
-      </c>
-      <c r="D3" t="n">
-        <v>83</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-8</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ROWS LOST (ETL drop)</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Sales raw vs snapshot (per brand×wk)</t>
         </is>
       </c>
     </row>
@@ -1149,1934 +1059,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sales_gmv</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ams_gmv</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pct</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ST-01</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>269565</v>
-      </c>
-      <c r="F2" t="n">
-        <v>269565</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26956526.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>WM-GD07-CB</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>239803</v>
-      </c>
-      <c r="F3" t="n">
-        <v>239803</v>
-      </c>
-      <c r="G3" t="n">
-        <v>23980254.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SC-05</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>216958</v>
-      </c>
-      <c r="F4" t="n">
-        <v>216958</v>
-      </c>
-      <c r="G4" t="n">
-        <v>21695849.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SC-04</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>198272</v>
-      </c>
-      <c r="F5" t="n">
-        <v>198272</v>
-      </c>
-      <c r="G5" t="n">
-        <v>19827203.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MR-01</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>129582</v>
-      </c>
-      <c r="F6" t="n">
-        <v>129582</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12958222</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>WM-LOD-CF</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>87956</v>
-      </c>
-      <c r="F7" t="n">
-        <v>87956</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8795593.199999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SP-01</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>84246</v>
-      </c>
-      <c r="F8" t="n">
-        <v>84246</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8424584.699999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PB-01</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>81492</v>
-      </c>
-      <c r="F9" t="n">
-        <v>81492</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8149237.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>24</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>VC-01</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>71224</v>
-      </c>
-      <c r="F10" t="n">
-        <v>71224</v>
-      </c>
-      <c r="G10" t="n">
-        <v>7122374.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>24</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>WM-LOD-WH</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>70754</v>
-      </c>
-      <c r="F11" t="n">
-        <v>70754</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7075423.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>24</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MR-02</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>69103</v>
-      </c>
-      <c r="F12" t="n">
-        <v>69103</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6910339.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>24</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>WM1ML</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>68080</v>
-      </c>
-      <c r="F13" t="n">
-        <v>68080</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6807966.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>24</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>CFM-01</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>63597</v>
-      </c>
-      <c r="F14" t="n">
-        <v>63597</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6359746.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>24</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SC-03</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>62703</v>
-      </c>
-      <c r="F15" t="n">
-        <v>62703</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6270339</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>24</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SC-01</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>60665</v>
-      </c>
-      <c r="F16" t="n">
-        <v>60665</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6066525.4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>24</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>WM-MODL-WH</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>50851</v>
-      </c>
-      <c r="F17" t="n">
-        <v>50851</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5085084.7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>24</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ST-03</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>47540</v>
-      </c>
-      <c r="F18" t="n">
-        <v>47540</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4753983.1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>24</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AM-W14</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>5253</v>
-      </c>
-      <c r="E19" t="n">
-        <v>52534</v>
-      </c>
-      <c r="F19" t="n">
-        <v>47281</v>
-      </c>
-      <c r="G19" t="n">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>24</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>V-03</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>45147</v>
-      </c>
-      <c r="F20" t="n">
-        <v>45147</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4514745.8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>24</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>WM-LOD-BK</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>42453</v>
-      </c>
-      <c r="F21" t="n">
-        <v>42453</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4245254.2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>24</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>EA-02</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>35981</v>
-      </c>
-      <c r="F22" t="n">
-        <v>35981</v>
-      </c>
-      <c r="G22" t="n">
-        <v>3598136.4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>24</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>TVMF1ML</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>33857</v>
-      </c>
-      <c r="F23" t="n">
-        <v>33857</v>
-      </c>
-      <c r="G23" t="n">
-        <v>3385678</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>24</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AI-14</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>60584</v>
-      </c>
-      <c r="E24" t="n">
-        <v>93630</v>
-      </c>
-      <c r="F24" t="n">
-        <v>33046</v>
-      </c>
-      <c r="G24" t="n">
-        <v>54.5</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>WM-GS1M-BK</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>30286</v>
-      </c>
-      <c r="F25" t="n">
-        <v>30286</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3028558</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>SPM-01</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>26689</v>
-      </c>
-      <c r="F26" t="n">
-        <v>26689</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2668899.2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>WM-SE08-CF</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>25425</v>
-      </c>
-      <c r="F27" t="n">
-        <v>25425</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2542542.4</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AM-K1</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>23642</v>
-      </c>
-      <c r="F28" t="n">
-        <v>23642</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2364152.5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>24</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CFM-03</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>23555</v>
-      </c>
-      <c r="F29" t="n">
-        <v>23555</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2355508.5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>24</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>SM-01</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>22536</v>
-      </c>
-      <c r="F30" t="n">
-        <v>22536</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2253644.1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>24</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AM-W47 WIRED</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>12193</v>
-      </c>
-      <c r="E31" t="n">
-        <v>34547</v>
-      </c>
-      <c r="F31" t="n">
-        <v>22354</v>
-      </c>
-      <c r="G31" t="n">
-        <v>183.3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>24</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AM-W45</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>233515</v>
-      </c>
-      <c r="E32" t="n">
-        <v>255612</v>
-      </c>
-      <c r="F32" t="n">
-        <v>22097</v>
-      </c>
-      <c r="G32" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>24</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>EA-01</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>20508</v>
-      </c>
-      <c r="F33" t="n">
-        <v>20508</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2050847.5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>24</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>ST-02</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>20337</v>
-      </c>
-      <c r="F34" t="n">
-        <v>20337</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2033728.8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>24</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>WM-HA2M-BK</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>18635</v>
-      </c>
-      <c r="F35" t="n">
-        <v>18635</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1863471</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>24</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>HSB-04</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>18344</v>
-      </c>
-      <c r="F36" t="n">
-        <v>18344</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1834406.8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>24</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>GS-02</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>16264</v>
-      </c>
-      <c r="F37" t="n">
-        <v>16264</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1626440.7</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>24</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>HDWF1ML</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>15758</v>
-      </c>
-      <c r="F38" t="n">
-        <v>15758</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1575766</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>24</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>WM-GS2M-BK</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>14573</v>
-      </c>
-      <c r="F39" t="n">
-        <v>14573</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1457288</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>24</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>SB-01</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>26419</v>
-      </c>
-      <c r="E40" t="n">
-        <v>40849</v>
-      </c>
-      <c r="F40" t="n">
-        <v>14431</v>
-      </c>
-      <c r="G40" t="n">
-        <v>54.6</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>24</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SS-02</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>14384</v>
-      </c>
-      <c r="F41" t="n">
-        <v>14384</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1438390.7</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>24</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>WM-LOD-IN</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>14151</v>
-      </c>
-      <c r="F42" t="n">
-        <v>14151</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1415084.7</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>24</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AI-13</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>137450</v>
-      </c>
-      <c r="E43" t="n">
-        <v>151412</v>
-      </c>
-      <c r="F43" t="n">
-        <v>13963</v>
-      </c>
-      <c r="G43" t="n">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>24</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>SW-01</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>13783</v>
-      </c>
-      <c r="F44" t="n">
-        <v>13783</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1378305.1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>24</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AM-W32</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>10167</v>
-      </c>
-      <c r="F45" t="n">
-        <v>10167</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1016694.9</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>24</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AM-W19</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>10164</v>
-      </c>
-      <c r="F46" t="n">
-        <v>10164</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1016440.7</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>24</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AH-50</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>172795</v>
-      </c>
-      <c r="E47" t="n">
-        <v>182958</v>
-      </c>
-      <c r="F47" t="n">
-        <v>10164</v>
-      </c>
-      <c r="G47" t="n">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>24</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>LE-02</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>10164</v>
-      </c>
-      <c r="F48" t="n">
-        <v>10164</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1016440.7</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>24</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10084</v>
-      </c>
-      <c r="E49" t="n">
-        <v>20168</v>
-      </c>
-      <c r="F49" t="n">
-        <v>10084</v>
-      </c>
-      <c r="G49" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>24</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>FS-01</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>10079</v>
-      </c>
-      <c r="F50" t="n">
-        <v>10079</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1007881.4</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>24</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AA-21</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>70829</v>
-      </c>
-      <c r="E51" t="n">
-        <v>80584</v>
-      </c>
-      <c r="F51" t="n">
-        <v>9755</v>
-      </c>
-      <c r="G51" t="n">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>24</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>HSB-03</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>8258</v>
-      </c>
-      <c r="F52" t="n">
-        <v>8258</v>
-      </c>
-      <c r="G52" t="n">
-        <v>825847.5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>24</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AM-S1</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>147442</v>
-      </c>
-      <c r="E53" t="n">
-        <v>155492</v>
-      </c>
-      <c r="F53" t="n">
-        <v>8050</v>
-      </c>
-      <c r="G53" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>24</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>HU-02</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>7623</v>
-      </c>
-      <c r="F54" t="n">
-        <v>7623</v>
-      </c>
-      <c r="G54" t="n">
-        <v>762288.1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>24</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>BR-01</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>7623</v>
-      </c>
-      <c r="F55" t="n">
-        <v>7623</v>
-      </c>
-      <c r="G55" t="n">
-        <v>762288.1</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>24</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AM-C47</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2414</v>
-      </c>
-      <c r="E56" t="n">
-        <v>9658</v>
-      </c>
-      <c r="F56" t="n">
-        <v>7243</v>
-      </c>
-      <c r="G56" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>24</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>VLMS1ML</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>7116</v>
-      </c>
-      <c r="F57" t="n">
-        <v>7116</v>
-      </c>
-      <c r="G57" t="n">
-        <v>711610.2</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>24</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>70331</v>
-      </c>
-      <c r="E58" t="n">
-        <v>77434</v>
-      </c>
-      <c r="F58" t="n">
-        <v>7103</v>
-      </c>
-      <c r="G58" t="n">
-        <v>10.1</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>24</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AI-03</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>20334</v>
-      </c>
-      <c r="E59" t="n">
-        <v>27146</v>
-      </c>
-      <c r="F59" t="n">
-        <v>6812</v>
-      </c>
-      <c r="G59" t="n">
-        <v>33.5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>24</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>HDGS1ML</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>6779</v>
-      </c>
-      <c r="F60" t="n">
-        <v>6779</v>
-      </c>
-      <c r="G60" t="n">
-        <v>677881.4</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>24</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>BE-4</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>6778</v>
-      </c>
-      <c r="E61" t="n">
-        <v>13556</v>
-      </c>
-      <c r="F61" t="n">
-        <v>6778</v>
-      </c>
-      <c r="G61" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>24</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>AM-W47 WIRELESS</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1609</v>
-      </c>
-      <c r="E62" t="n">
-        <v>8047</v>
-      </c>
-      <c r="F62" t="n">
-        <v>6437</v>
-      </c>
-      <c r="G62" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>24</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>VC-02</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="n">
-        <v>6396</v>
-      </c>
-      <c r="F63" t="n">
-        <v>6396</v>
-      </c>
-      <c r="G63" t="n">
-        <v>639576.3</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>24</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>TVCT1ML</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>6181</v>
-      </c>
-      <c r="F64" t="n">
-        <v>6181</v>
-      </c>
-      <c r="G64" t="n">
-        <v>618050.8</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>24</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>WM-HA1M-BK</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="n">
-        <v>5803</v>
-      </c>
-      <c r="F65" t="n">
-        <v>5803</v>
-      </c>
-      <c r="G65" t="n">
-        <v>580338</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>24</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AM-W22</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>17283</v>
-      </c>
-      <c r="E66" t="n">
-        <v>23044</v>
-      </c>
-      <c r="F66" t="n">
-        <v>5761</v>
-      </c>
-      <c r="G66" t="n">
-        <v>33.3</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>24</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AH-45 BK</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>59624</v>
-      </c>
-      <c r="E67" t="n">
-        <v>65098</v>
-      </c>
-      <c r="F67" t="n">
-        <v>5475</v>
-      </c>
-      <c r="G67" t="n">
-        <v>9.199999999999999</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>24</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>AP-04</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>5253</v>
-      </c>
-      <c r="F68" t="n">
-        <v>5253</v>
-      </c>
-      <c r="G68" t="n">
-        <v>525339</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>24</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>DH-01</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="n">
-        <v>5084</v>
-      </c>
-      <c r="F69" t="n">
-        <v>5084</v>
-      </c>
-      <c r="G69" t="n">
-        <v>508389.8</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>24</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>GS-05</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>5082</v>
-      </c>
-      <c r="F70" t="n">
-        <v>5082</v>
-      </c>
-      <c r="G70" t="n">
-        <v>508220.3</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>24</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>LR-02</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>5069</v>
-      </c>
-      <c r="F71" t="n">
-        <v>5069</v>
-      </c>
-      <c r="G71" t="n">
-        <v>506865.3</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — AMS Trend GMV &gt; Sales Trend GMV (per brand×model×wk)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3135,10 +1132,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>165963</v>
+        <v>165783</v>
       </c>
       <c r="D2" t="n">
-        <v>165963</v>
+        <v>165783</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3159,10 +1156,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>153557</v>
+        <v>153377</v>
       </c>
       <c r="D3" t="n">
-        <v>153557</v>
+        <v>153377</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3712,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5217,22 +3214,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>7603</v>
+        <v>13990</v>
       </c>
       <c r="E63" t="n">
-        <v>7772</v>
+        <v>13974</v>
       </c>
       <c r="F63" t="n">
-        <v>169</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="64">
@@ -5246,17 +3243,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>686</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>697</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -5265,69 +3262,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13990</v>
+        <v>18</v>
       </c>
       <c r="E65" t="n">
-        <v>13974</v>
+        <v>14</v>
       </c>
       <c r="F65" t="n">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>24</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>5</v>
-      </c>
-      <c r="E66" t="n">
-        <v>9</v>
-      </c>
-      <c r="F66" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>24</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>18</v>
-      </c>
-      <c r="E67" t="n">
-        <v>14</v>
-      </c>
-      <c r="F67" t="n">
         <v>-4</v>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,16 +35,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,7 +52,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,21 +60,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,36 +431,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -676,19 +664,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>1p</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8700</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8520</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-180</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>21311</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>21295</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" t="n">
         <v>-16</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>UNITS MISMATCH (silent drop)</t>
         </is>
@@ -709,32 +721,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -783,7 +795,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -811,7 +823,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -839,7 +851,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -867,7 +879,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -895,7 +907,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -923,7 +935,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -951,7 +963,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -975,77 +987,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>raw_sku</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>brand_folder</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>weeks_seen</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>total_units</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FBA79347</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>other_channels</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pharmaeasy</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
+          <t>clean — (info) Off-master ASINs in raw sales</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1019,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1091,32 +1047,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1185,7 +1141,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1213,7 +1169,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1241,32 +1197,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1371,22 +1327,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1657,7 +1613,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1681,11 +1637,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1694,7 +1665,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand missing from a layer (diagnostic)</t>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in inventory for W24</t>
         </is>
       </c>
     </row>
@@ -1709,36 +1833,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
@@ -3214,22 +3338,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>1p</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13990</v>
+        <v>7772</v>
       </c>
       <c r="E63" t="n">
-        <v>13974</v>
+        <v>7603</v>
       </c>
       <c r="F63" t="n">
-        <v>-16</v>
+        <v>-169</v>
       </c>
     </row>
     <row r="64">
@@ -3243,17 +3367,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>1p</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>697</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>686</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="65">
@@ -3262,21 +3386,69 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>13990</v>
+      </c>
+      <c r="E65" t="n">
+        <v>13974</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>24</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>9</v>
+      </c>
+      <c r="F66" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>24</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>white mulberry</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>b2b - ampm</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D67" t="n">
         <v>18</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E67" t="n">
         <v>14</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F67" t="n">
         <v>-4</v>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,43 +664,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8700</v>
+        <v>21311</v>
       </c>
       <c r="D10" t="n">
-        <v>8520</v>
+        <v>21295</v>
       </c>
       <c r="E10" t="n">
-        <v>-180</v>
+        <v>-16</v>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>UNITS MISMATCH (silent drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>24</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>21311</v>
-      </c>
-      <c r="D11" t="n">
-        <v>21295</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-16</v>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>UNITS MISMATCH (silent drop)</t>
         </is>
@@ -1833,7 +1809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3338,22 +3314,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>7772</v>
+        <v>13990</v>
       </c>
       <c r="E63" t="n">
-        <v>7603</v>
+        <v>13974</v>
       </c>
       <c r="F63" t="n">
-        <v>-169</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="64">
@@ -3367,17 +3343,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>697</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>686</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>-11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -3386,69 +3362,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13990</v>
+        <v>18</v>
       </c>
       <c r="E65" t="n">
-        <v>13974</v>
+        <v>14</v>
       </c>
       <c r="F65" t="n">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>24</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>5</v>
-      </c>
-      <c r="E66" t="n">
-        <v>9</v>
-      </c>
-      <c r="F66" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>24</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>18</v>
-      </c>
-      <c r="E67" t="n">
-        <v>14</v>
-      </c>
-      <c r="F67" t="n">
         <v>-4</v>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,13 +35,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,12 +63,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,32 +447,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -697,32 +709,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -771,7 +783,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -799,7 +811,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -827,7 +839,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -855,7 +867,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -883,7 +895,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -911,7 +923,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -939,7 +951,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -963,21 +975,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>brand_folder</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weeks_seen</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — (info) Off-master ASINs in raw sales</t>
-        </is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FBA79347</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>other_channels</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pharmaeasy</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +1063,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1023,32 +1091,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1117,7 +1185,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1145,7 +1213,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1173,32 +1241,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1303,22 +1371,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1589,7 +1657,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1613,26 +1681,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1641,160 +1694,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>24</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>24</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>24</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W24</t>
+          <t>clean — Brand missing from a layer (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -1813,32 +1713,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1132,10 +1132,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>165783</v>
+        <v>164331</v>
       </c>
       <c r="D2" t="n">
-        <v>165783</v>
+        <v>164331</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1156,10 +1156,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>153377</v>
+        <v>151925</v>
       </c>
       <c r="D3" t="n">
-        <v>153377</v>
+        <v>151925</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,26 +1303,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bi worldwide</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>units_sold</t>
+          <t>inventory_units</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1500</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1336,23 +1336,51 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bi worldwide</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>nexlev</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>bi worldwide</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>units_sold</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>13</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,16 +35,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,7 +52,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,21 +60,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,32 +435,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -709,32 +697,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -783,7 +771,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -811,7 +799,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -839,7 +827,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -867,7 +855,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -895,7 +883,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -923,7 +911,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -951,7 +939,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -975,77 +963,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>raw_sku</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>brand_folder</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>weeks_seen</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>total_units</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FBA79347</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>other_channels</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pharmaeasy</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
+          <t>clean — (info) Off-master ASINs in raw sales</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +995,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1091,32 +1023,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1185,7 +1117,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1213,7 +1145,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1241,32 +1173,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1399,22 +1331,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1685,7 +1617,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1709,11 +1641,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1722,7 +1669,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand missing from a layer (diagnostic)</t>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in inventory for W24</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1841,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,13 +35,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,12 +63,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,32 +447,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -697,32 +709,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -771,7 +783,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -799,7 +811,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -827,7 +839,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -855,7 +867,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -883,7 +895,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -911,7 +923,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -939,7 +951,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -963,21 +975,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>brand_folder</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weeks_seen</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — (info) Off-master ASINs in raw sales</t>
-        </is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FBA79347</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>other_channels</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pharmaeasy</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +1063,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1023,32 +1091,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1117,7 +1185,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1145,7 +1213,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1173,32 +1241,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1331,22 +1399,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1617,7 +1685,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1641,26 +1709,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1669,160 +1722,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>24</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>24</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>24</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W24</t>
+          <t>clean — Brand missing from a layer (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -1841,32 +1741,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,13 +36,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,7 +56,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,12 +64,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,32 +448,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -697,32 +710,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -771,7 +784,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -799,7 +812,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -827,7 +840,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -855,7 +868,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -883,7 +896,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -911,7 +924,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -939,7 +952,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -963,21 +976,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>brand_folder</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weeks_seen</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — (info) Off-master ASINs in raw sales</t>
-        </is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FBA79347</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>other_channels</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pharmaeasy</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +1064,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1023,32 +1092,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1099,6 +1168,34 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>ok</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Derivative snapshot stale vs parent (re-run needed)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1214,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1145,7 +1242,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1173,32 +1270,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1331,22 +1428,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1617,7 +1714,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1641,26 +1738,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1669,160 +1751,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>24</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>24</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>24</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W24</t>
+          <t>clean — Brand missing from a layer (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -1841,32 +1770,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -27,6 +27,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1204,6 +1205,34 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Brand metric &gt; 50% drop or 2x spike vs prior 4w median</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -28,6 +28,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1233,6 +1234,34 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Snapshot category_l0/l1 coverage &lt; threshold (UI filter broken)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,16 +38,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -58,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -66,21 +63,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,32 +438,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -712,32 +700,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -786,7 +774,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -814,7 +802,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -842,7 +830,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -870,7 +858,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -898,7 +886,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -926,7 +914,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -954,7 +942,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -978,77 +966,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>raw_sku</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>brand_folder</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>weeks_seen</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>total_units</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FBA79347</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>other_channels</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pharmaeasy</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
+          <t>clean — (info) Off-master ASINs in raw sales</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +998,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1094,32 +1026,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1188,7 +1120,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1216,7 +1148,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1244,7 +1176,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1272,7 +1204,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1300,7 +1232,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1328,32 +1260,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1486,22 +1418,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1772,7 +1704,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1796,11 +1728,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1809,7 +1756,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand missing from a layer (diagnostic)</t>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in sales for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in inventory for W24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in inventory for W24</t>
         </is>
       </c>
     </row>
@@ -1828,32 +1928,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,6 +682,30 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8421</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-8421</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3519,54 @@
         <v>-4</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>25</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>7701</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-7701</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>25</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>720</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-720</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,13 +38,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,7 +58,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -63,12 +66,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,32 +450,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -691,21 +703,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8421</v>
+        <v>20451</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>20431</v>
       </c>
       <c r="E11" t="n">
-        <v>-8421</v>
+        <v>-20</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MISSING IN SNAPSHOT (ETL dropping rows)</t>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
@@ -724,32 +736,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -777,10 +789,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -798,7 +810,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -826,7 +838,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -854,7 +866,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -882,7 +894,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -910,7 +922,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -938,7 +950,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -966,7 +978,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -990,21 +1002,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>brand_folder</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weeks_seen</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — (info) Off-master ASINs in raw sales</t>
-        </is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FBA79347</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>other_channels</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pharmaeasy</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +1090,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1050,32 +1118,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1088,13 +1156,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>164331</v>
+        <v>158930</v>
       </c>
       <c r="D2" t="n">
-        <v>164331</v>
+        <v>158930</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1112,13 +1180,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>151925</v>
+        <v>146599</v>
       </c>
       <c r="D3" t="n">
-        <v>151925</v>
+        <v>146599</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1144,7 +1212,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1172,7 +1240,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1200,7 +1268,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1228,7 +1296,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1256,7 +1324,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1280,36 +1348,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1337,7 +1405,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1351,7 +1419,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1365,7 +1433,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1500</v>
+        <v>858</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1374,26 +1442,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bi worldwide</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>units_sold</t>
+          <t>inventory_units</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1421,9 +1489,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1442,22 +1538,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1728,7 +1824,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1752,26 +1848,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1780,160 +1861,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in sales for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>24</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>24</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in inventory for W24</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>24</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W24</t>
+          <t>clean — Brand missing from a layer (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -1948,36 +1876,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
@@ -3525,22 +3453,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7701</v>
+        <v>13745</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>13725</v>
       </c>
       <c r="F66" t="n">
-        <v>-7701</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="67">
@@ -3554,17 +3482,41 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>720</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F67" t="n">
-        <v>-720</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>25</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>18</v>
+      </c>
+      <c r="E68" t="n">
+        <v>14</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-4</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,16 +38,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -58,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -66,21 +63,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,32 +438,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -736,32 +724,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -810,7 +798,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -838,7 +826,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -866,7 +854,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -894,7 +882,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -922,7 +910,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -950,7 +938,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -978,7 +966,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1002,77 +990,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>raw_sku</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>brand_folder</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>weeks_seen</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>total_units</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FBA79347</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>other_channels</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pharmaeasy</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
+          <t>clean — (info) Off-master ASINs in raw sales</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1090,7 +1022,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1118,32 +1050,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1212,7 +1144,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1240,7 +1172,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1268,7 +1200,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1296,7 +1228,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1324,7 +1256,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1352,32 +1284,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1538,22 +1470,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1824,7 +1756,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1848,11 +1780,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1861,7 +1808,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand missing from a layer (diagnostic)</t>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in sales for W25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in sales for W25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in sales for W25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in sales for W25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in inventory for W25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in inventory for W25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in inventory for W25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in inventory for W25</t>
         </is>
       </c>
     </row>
@@ -1880,32 +1980,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,13 +38,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,7 +58,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -63,12 +66,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,32 +450,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -724,32 +736,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -798,7 +810,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -826,7 +838,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -854,7 +866,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -882,7 +894,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -910,7 +922,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -938,7 +950,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -966,7 +978,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -990,21 +1002,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>brand_folder</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weeks_seen</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — (info) Off-master ASINs in raw sales</t>
-        </is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FBA79347</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>other_channels</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pharmaeasy</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +1090,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1050,32 +1118,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1088,13 +1156,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>158930</v>
+        <v>9759</v>
       </c>
       <c r="D2" t="n">
-        <v>158930</v>
+        <v>9759</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1112,13 +1180,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>146599</v>
+        <v>9759</v>
       </c>
       <c r="D3" t="n">
-        <v>146599</v>
+        <v>9759</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1140,11 +1208,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>lag_sec</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1153,7 +1236,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Derivative snapshot stale vs parent (re-run needed)</t>
+          <t>data\processed\inventory_model_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>data\processed\inventory_ams_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>496830.9</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>inventory_model_snapshot → inventory_ams_snapshot (inv_snap needs re-run)</t>
         </is>
       </c>
     </row>
@@ -1168,11 +1264,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>latest</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>prior_4w_median</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>delta_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1181,7 +1302,78 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand metric &gt; 50% drop or 2x spike vs prior 4w median</t>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>inventory_soh</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>9018</v>
+      </c>
+      <c r="D2" t="n">
+        <v>77614</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-88.40000000000001</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>inventory_soh</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>741</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3709</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sessions</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>130228</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
         </is>
       </c>
     </row>
@@ -1196,11 +1388,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>snapshot</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_pct</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>min_required_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1209,7 +1421,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Snapshot category_l0/l1 coverage &lt; threshold (UI filter broken)</t>
+          <t>business_ads_joined.csv</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>category_l0</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>90</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Category coverage below threshold — UI filter will miss rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>business_ads_joined.csv</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>category_l1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Category coverage below threshold — UI filter will miss rows</t>
         </is>
       </c>
     </row>
@@ -1224,11 +1475,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>week_num</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1237,7 +1508,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Never-Zero column regression</t>
+          <t>ams_trend.inventory_snapshot</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>inventory_ampm</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ZERO column — AMPM stock (operator warehouse) — non-zero portfolio-wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ams_trend.inventory_snapshot</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>inventory_amazon</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ZERO column — Amazon FBA stock — non-zero portfolio-wide</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1566,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1280,36 +1590,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1318,26 +1628,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>ams_trend</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>(brand-total)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>sessions</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>391312</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1346,26 +1656,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>ams_trend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>(brand-total)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>ad_spend</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>858</v>
+        <v>769045.5700000001</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1374,26 +1684,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>ams_trend</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>(brand-total)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>attributed_sales</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1000</v>
+        <v>2439501.63</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1402,7 +1712,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>ams_trend</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1412,16 +1722,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bi worldwide</t>
+          <t>(brand-total)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>units_sold</t>
+          <t>amazon_gmv</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>5391141.779661017</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1430,28 +1740,1316 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sessions</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>572747</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sessions</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>11077</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ad_spend</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>318193.03</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>attributed_sales</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1401643.22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>amazon_gmv</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2856656.58</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>sessions</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>51248</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>14723</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>107666</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3475</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>blinkit</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1269</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>28304</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>49526</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ynt</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>462</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>41068</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>104625</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>12776</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>blinkit</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4454</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>29756</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24579</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ynt</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4065</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1574</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6467</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>27</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>240</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>572</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>680</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4777</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>14050</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>42</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>500</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ynt</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>42</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>620</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>449</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>blinkit sales</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>110</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>d2c - audio array</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>49</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>38</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2056</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>b2b</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>398</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>biw</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>26</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>blinkit sales</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>511</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>d2c - nexlev</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>pharmaeasy</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>17</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>27</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>white mulberry</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1p sales</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>249</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>638</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>b2b</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>units_sold</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E52" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1470,22 +3068,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -1756,7 +3354,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1780,26 +3378,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1813,15 +3411,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MISSING — no rows for audio array in sales for W25</t>
+          <t>MISSING — no rows for nexlev in sales for W26</t>
         </is>
       </c>
     </row>
@@ -1833,42 +3431,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MISSING — no rows for nexlev in sales for W25</t>
+          <t>MISSING — no rows for white mulberry in sales for W26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MISSING — no rows for tonor in sales for W25</t>
+          <t>MISSING — no rows for nexlev in inventory for W26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1877,91 +3475,51 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MISSING — no rows for white mulberry in sales for W25</t>
+          <t>MISSING — no rows for white mulberry in inventory for W26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>ams_trend</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MISSING — no rows for audio array in inventory for W25</t>
+          <t>MISSING — no rows for nexlev in ams_trend for W26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>ams_trend</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MISSING — no rows for nexlev in inventory for W25</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>25</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in inventory for W25</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>25</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W25</t>
+          <t>MISSING — no rows for white mulberry in ams_trend for W26</t>
         </is>
       </c>
     </row>
@@ -1980,32 +3538,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,6 +716,54 @@
         <v>-20</v>
       </c>
       <c r="F11" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19699</v>
+      </c>
+      <c r="E12" t="n">
+        <v>19699</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>40427</v>
+      </c>
+      <c r="D13" t="n">
+        <v>39427</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>UNITS MISMATCH (silent drop)</t>
         </is>
@@ -834,12 +882,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>amazon+1p_inventory</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_total_amazon</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -847,7 +920,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route inventory rule consistency</t>
+          <t>amazon+1p_vs_ams_trend</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UB-05 (AM-S2+AA-21)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AMAZON-SIDE RULE DRIFTED between the two routes</t>
         </is>
       </c>
     </row>
@@ -862,12 +954,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sales_trend_amzn+1p_gmv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_gmv</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -875,7 +987,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-source sales drift (diagnostic)</t>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>58241.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-58241.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7286.44</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-7286.44</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>11606.78</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-11606.78</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>16940.63</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-16940.63</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>33881.35</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-33881.35</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5549.15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-5549.15</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>31515.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-31515.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
         </is>
       </c>
     </row>
@@ -1159,10 +1411,10 @@
         <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>9759</v>
+        <v>179341</v>
       </c>
       <c r="D2" t="n">
-        <v>9759</v>
+        <v>179341</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1183,10 +1435,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>9759</v>
+        <v>167741</v>
       </c>
       <c r="D3" t="n">
-        <v>9759</v>
+        <v>167741</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1208,27 +1460,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>child</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>lag_sec</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -1236,20 +1473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>data\processed\inventory_model_snapshot.csv</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>data\processed\inventory_ams_snapshot.csv</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>496830.9</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>inventory_model_snapshot → inventory_ams_snapshot (inv_snap needs re-run)</t>
+          <t>clean — Derivative snapshot stale vs parent (re-run needed)</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1302,22 +1526,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>inventory_soh</t>
+          <t>sales_gmv</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9018</v>
+        <v>632418</v>
       </c>
       <c r="D2" t="n">
-        <v>77614</v>
+        <v>2488801</v>
       </c>
       <c r="E2" t="n">
-        <v>-88.40000000000001</v>
+        <v>-74.59999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1328,22 +1552,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>inventory_soh</t>
+          <t>sales_units</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>741</v>
+        <v>351</v>
       </c>
       <c r="D3" t="n">
-        <v>3709</v>
+        <v>1056</v>
       </c>
       <c r="E3" t="n">
-        <v>-80</v>
+        <v>-66.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1354,24 +1578,154 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sales_gmv</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>165021</v>
+      </c>
+      <c r="D4" t="n">
+        <v>929813</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sales_units</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>79</v>
+      </c>
+      <c r="D5" t="n">
+        <v>295</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-73.2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Audio Array</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>sessions</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D6" t="n">
         <v>130228</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E6" t="n">
         <v>-100</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ad_spend</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>46577</v>
+      </c>
+      <c r="D7" t="n">
+        <v>107333</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>attributed</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>129280</v>
+      </c>
+      <c r="D8" t="n">
+        <v>452669</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-71.40000000000001</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sessions</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17340</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>DROP &gt; 50% vs prior 4-week median</t>
         </is>
@@ -1430,7 +1784,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="D2" t="n">
         <v>90</v>
@@ -1453,7 +1807,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="D3" t="n">
         <v>40</v>
@@ -1475,32 +1829,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>rule</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>week_num</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -1508,46 +1842,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ams_trend.inventory_snapshot</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>inventory_ampm</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>26</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ZERO column — AMPM stock (operator warehouse) — non-zero portfolio-wide</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ams_trend.inventory_snapshot</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>inventory_amazon</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>26</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ZERO column — Amazon FBA stock — non-zero portfolio-wide</t>
+          <t>clean — Never-Zero column regression</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1811,11 +2106,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ad_spend</t>
+          <t>amazon_gmv</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>318193.03</v>
+        <v>2856656.58</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1839,11 +2134,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>attributed_sales</t>
+          <t>sessions</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1401643.22</v>
+        <v>51248</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1852,26 +2147,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>amazon_gmv</t>
+          <t>inventory_units</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2856656.58</v>
+        <v>240</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1880,7 +2175,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1890,16 +2185,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sessions</t>
+          <t>inventory_units</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>51248</v>
+        <v>6000</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1908,7 +2203,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1923,11 +2218,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14723</v>
+        <v>620</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1936,7 +2231,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1946,16 +2241,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ampm</t>
+          <t>flipkart</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>107666</v>
+        <v>38</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1964,26 +2259,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3475</v>
+        <v>2056</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1992,26 +2287,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>blinkit</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1269</v>
+        <v>27</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2020,26 +2315,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>28304</v>
+        <v>638</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2048,1008 +2343,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>b2b</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>49526</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ynt</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>462</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>41068</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>104625</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>12776</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>blinkit</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>4454</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>29756</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>24579</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>ynt</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>4065</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>1574</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>6467</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>27</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>240</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>572</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1p</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>680</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>4777</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>14050</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>42</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>500</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ynt</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>42</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>620</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>b2b</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>449</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>blinkit sales</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>110</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>d2c - audio array</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>49</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>38</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>2056</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>b2b</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>398</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>biw</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>26</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>blinkit sales</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>511</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>d2c - nexlev</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>228</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>pharmaeasy</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>17</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>27</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1p sales</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>249</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>638</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>b2b</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>5</v>
-      </c>
-      <c r="F52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3378,7 +2693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3406,7 +2721,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>ams_trend</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3419,107 +2734,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MISSING — no rows for nexlev in sales for W26</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>26</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in sales for W26</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>26</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in inventory for W26</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>26</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W26</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>26</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
           <t>MISSING — no rows for nexlev in ams_trend for W26</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>26</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in ams_trend for W26</t>
         </is>
       </c>
     </row>
@@ -3534,7 +2749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5177,6 +4392,198 @@
         <v>-4</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>26</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4210</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4210</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>26</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>fossil</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>6916</v>
+      </c>
+      <c r="F70" t="n">
+        <v>6916</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>26</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>13582</v>
+      </c>
+      <c r="F71" t="n">
+        <v>13582</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>26</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>409</v>
+      </c>
+      <c r="F72" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>26</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1498</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>26</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>8</v>
+      </c>
+      <c r="F74" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>26</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>18</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>26</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>26295</v>
+      </c>
+      <c r="E76" t="n">
+        <v>25295</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -882,37 +882,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>pair</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>amazon+1p_inventory</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ams_trend_total_amazon</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -920,26 +895,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>amazon+1p_vs_ams_trend</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>UB-05 (AM-S2+AA-21)</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AMAZON-SIDE RULE DRIFTED between the two routes</t>
+          <t>clean — Cross-route inventory rule consistency</t>
         </is>
       </c>
     </row>
@@ -1435,10 +1391,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>167741</v>
+        <v>171380</v>
       </c>
       <c r="D3" t="n">
-        <v>167741</v>
+        <v>171380</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1488,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1642,90 +1598,12 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>130228</v>
+        <v>126002</v>
       </c>
       <c r="E6" t="n">
         <v>-100</v>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>46577</v>
-      </c>
-      <c r="D7" t="n">
-        <v>107333</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-56.6</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>129280</v>
-      </c>
-      <c r="D8" t="n">
-        <v>452669</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-71.40000000000001</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>sessions</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>17340</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>DROP &gt; 50% vs prior 4-week median</t>
         </is>
@@ -1742,32 +1620,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>snapshot</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>coverage_pct</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>min_required_pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -1775,46 +1633,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>business_ads_joined.csv</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>category_l0</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="D2" t="n">
-        <v>90</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Category coverage below threshold — UI filter will miss rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>business_ads_joined.csv</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>category_l1</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="D3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Category coverage below threshold — UI filter will miss rows</t>
+          <t>clean — Snapshot category_l0/l1 coverage &lt; threshold (UI filter broken)</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1942,7 +1761,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>391312</v>
+        <v>378042</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1956,7 +1775,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1966,11 +1785,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ad_spend</t>
+          <t>sessions</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>769045.5700000001</v>
+        <v>10396</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1984,7 +1803,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1994,11 +1813,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>attributed_sales</t>
+          <t>amazon_gmv</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2439501.63</v>
+        <v>677091.9189830509</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2012,7 +1831,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2022,11 +1841,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>amazon_gmv</t>
+          <t>sessions</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5391141.779661017</v>
+        <v>13856</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2035,26 +1854,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sessions</t>
+          <t>inventory_units</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>572747</v>
+        <v>240</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2063,26 +1882,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sessions</t>
+          <t>inventory_units</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>11077</v>
+        <v>6000</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2091,26 +1910,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>amazon_gmv</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2856656.58</v>
+        <v>620</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2119,26 +1938,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>flipkart</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sessions</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>51248</v>
+        <v>38</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -2147,26 +1966,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>240</v>
+        <v>2056</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -2175,26 +1994,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6000</v>
+        <v>27</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2208,7 +2027,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2222,7 +2041,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2236,12 +2055,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>flipkart</t>
+          <t>b2b</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2250,121 +2069,9 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>2056</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>27</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>638</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>b2b</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1704,7 +1704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>flipkart</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38</v>
+        <v>2056</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2056</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>638</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2041,37 +2041,9 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>638</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>b2b</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -29,6 +29,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -910,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -943,17 +944,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B001J1772I</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58241.5</v>
+        <v>11859.32</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-58241.5</v>
+        <v>-11859.32</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -964,17 +965,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B004D4S7AY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7286.44</v>
+        <v>80049.14999999999</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-7286.44</v>
+        <v>-80049.14999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -985,17 +986,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0058XWUHA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11606.78</v>
+        <v>38974.58</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-11606.78</v>
+        <v>-38974.58</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1006,17 +1007,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B007NM84PQ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16940.63</v>
+        <v>20328.81</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-16940.63</v>
+        <v>-20328.81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1027,17 +1028,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B008AXYWHQ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33881.35</v>
+        <v>275180.51</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-33881.35</v>
+        <v>-275180.51</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1048,17 +1049,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B00944CXEY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5549.15</v>
+        <v>20840.68</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-5549.15</v>
+        <v>-20840.68</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1069,19 +1070,5542 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>B00AFTT8KE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11012.71</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-11012.71</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B00AFTTQ8I</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>77084.75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-77084.75</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B00AG37H8Y</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>417623.73</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-417623.73</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B00AMWDOEK</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>23125.42</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-23125.42</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B00H2ZDX00</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>214978.81</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-214978.81</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B00HVBJ6W4</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>184136.44</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-184136.44</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B00NVAWTLY</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>137586.44</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-137586.44</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B00WM0CF4A</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>94861.02</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-94861.02</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B01487C7CO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>16944.07</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-16944.07</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B017SN1OI8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>69383.89999999999</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-69383.89999999999</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B0183NW5H6</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7878.81</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-7878.81</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B01GZZYSRO</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>33213.56</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-33213.56</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B01GZZZ328</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>12282.2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-12282.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B01MTYS3BW</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>29656.78</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-29656.78</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B06VV5QB6Q</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>40233.05</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-40233.05</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B0769YW2KN</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>33888.14</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-33888.14</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B077SMJP9Z</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6988.14</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-6988.14</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B078Y2PJL4</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7115.25</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-7115.25</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B079DC27J5</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>22023.73</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-22023.73</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B079XB5RXH</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>41515.25</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-41515.25</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B07CSNG8XL</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>32183.05</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-32183.05</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B07GVGMW59</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>27447.42</v>
+      </c>
+      <c r="C29" t="n">
+        <v>20585.56</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-6861.86</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B07M7P7VLX</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>24015.25</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-24015.25</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B07MFZ6S2Q</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>24566.1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-24566.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>B07MM5MH6F</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>33035.59</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-33035.59</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B07RZ1R1HJ</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>33035.59</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-33035.59</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B07T2XYGR5</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>20334.75</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-20334.75</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>B07T3ZLNM3</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>18216.1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-18216.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>B07T53T1KV</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>27538.14</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-27538.14</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>B07T63ZJTR</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>19063.56</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-19063.56</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>B082W4B7SX</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>8301.690000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4150.84</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-4150.85</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>B0846Q1JT5</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>13130.51</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-13130.51</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>B084CG2ZVZ</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>12283.05</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-12283.05</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B08QVCPDVT</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>61415.25</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-61415.25</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>B08V3TK36Z</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>33215.25</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-33215.25</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B08XBYKWW3</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>13640.68</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-13640.68</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>B09BBK2LV4</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>23724.58</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-23724.58</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>B09CSXR4TR</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>13977.97</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-13977.97</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>B09SHQSHBF</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>68199.14999999999</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-68199.14999999999</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>B0B4DPX2J2</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>514062.18</v>
+      </c>
+      <c r="C47" t="n">
+        <v>511757.94</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-2304.24</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B0B4G19R58</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>22439.86</v>
+      </c>
+      <c r="C48" t="n">
+        <v>19316.95</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-3122.91</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>B0B4G5JG4P</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>16014.42</v>
+      </c>
+      <c r="C49" t="n">
+        <v>10676.28</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-5338.14</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>B0B4G7VWXD</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>20157.68</v>
+      </c>
+      <c r="C50" t="n">
+        <v>17278.02</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-2879.66</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>B0B4G8PH2P</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>9105.93</v>
+      </c>
+      <c r="C51" t="n">
+        <v>7284.74</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-1821.19</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>B0B4G94VP3</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3810.16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3383.04</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-427.12</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>B0B4JRQP22</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>19060.2</v>
+      </c>
+      <c r="C53" t="n">
+        <v>16942.4</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-2117.8</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>B0B4KC7VBM</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>18509.3</v>
+      </c>
+      <c r="C54" t="n">
+        <v>16433.88</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-2075.42</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>B0B4WTHLX5</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2117.8</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-2117.8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>49527.97</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-49527.97</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>14150.85</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-14150.85</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>43215.25</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-43215.25</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>B0BFXL8ZP9</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>11012.71</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-11012.71</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>B0BLJVJ2GN</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>16505.93</v>
+      </c>
+      <c r="C60" t="n">
+        <v>15950</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-555.9299999999999</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>B0BPLWW72Y</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>144014.61</v>
+      </c>
+      <c r="C61" t="n">
+        <v>124331.56</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-19683.05</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>423121.18</v>
+      </c>
+      <c r="C62" t="n">
+        <v>410761.49</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-12359.69</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>B0BPM2T7BQ</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>16859.67</v>
+      </c>
+      <c r="C63" t="n">
+        <v>13555.92</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-3303.75</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>B0BQ34TRDX</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>11436.44</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-11436.44</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>B0BQ7H7418</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>9907.620000000001</v>
+      </c>
+      <c r="C65" t="n">
+        <v>6605.08</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-3302.54</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>B0BQZH3LGP</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>10378.81</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-10378.81</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>B0BS4BHNVN</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>20758.47</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-20758.47</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>B0BYHHSLPC</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>22056.76</v>
+      </c>
+      <c r="C68" t="n">
+        <v>18634.73</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-3422.03</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>B0CBCB82MT</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>10822.04</v>
+      </c>
+      <c r="C69" t="n">
+        <v>8152.52</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-2669.52</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>B0CCV74CL7</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>19654.24</v>
+      </c>
+      <c r="C70" t="n">
+        <v>12283.9</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-7370.34</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>B0CDPMX152</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>18297.46</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-18297.46</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>119211.01</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-119211.01</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B0CF5R3V95</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>81546.50999999999</v>
+      </c>
+      <c r="C73" t="n">
+        <v>75022.78</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-6523.73</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>B0CF5SHL15</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>18893.23</v>
+      </c>
+      <c r="C74" t="n">
+        <v>15673.74</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-3219.49</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>B0CF61X2BG</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>11435.59</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-11435.59</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>B0CFBB587Z</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>19487.29</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-19487.29</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>B0CFKHCQ8W</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>8894.07</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-8894.07</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>B0CH4PMR8K</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>20122.96</v>
+      </c>
+      <c r="C78" t="n">
+        <v>13550.8</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-6572.16</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>B0CH4VCD6R</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>14898.32</v>
+      </c>
+      <c r="C79" t="n">
+        <v>13957.64</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-940.6799999999999</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>B0CH9JR3HL</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2117.8</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-2117.8</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B0CHXGWVZJ</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>118603.39</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-118603.39</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B0CJ6ZW8F6</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>10164.41</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-10164.41</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>286555.13</v>
+      </c>
+      <c r="C83" t="n">
+        <v>277573.77</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-8981.360000000001</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B0CM6NTWBP</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>36794.07</v>
+      </c>
+      <c r="C84" t="n">
+        <v>34141.53</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-2652.54</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>B0CM6WH4ZT</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>3556.78</v>
+      </c>
+      <c r="C85" t="n">
+        <v>2371.19</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-1185.59</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>255055.08</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-255055.08</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>25425.42</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-25425.42</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>B0CRCWV9DV</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>13554.24</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-13554.24</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>B0CRD1DRXG</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>18639.83</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-18639.83</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>B0CRD2CVZL</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>10164.41</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-10164.41</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>B0CSCT63BL</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2033.05</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-2033.05</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>150008.49</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-150008.49</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>B0CZ8ZKPJ9</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>9488.139999999999</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-9488.139999999999</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>B0CZ91YKMP</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>8132.2</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-8132.2</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>B0D25LNDSY</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>4062.71</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-4062.71</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>B0D2LD6BYJ</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>7145.77</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-7145.77</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>B0D2LFMY48</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>677.12</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-677.12</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>B0D2LHNS9B</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>846.61</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-846.61</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>B0D2LJSQXZ</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>9658.469999999999</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-9658.469999999999</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>B0D2P5TGWK</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>760.17</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-760.17</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>B0D2P7WLJB</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1522.89</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-1522.89</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>8470.34</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-8470.34</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>B0D3M86SH1</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>12709.32</v>
+      </c>
+      <c r="C103" t="n">
+        <v>8472.879999999999</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-4236.44</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>B0D63FKYZ5</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1727.12</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-1727.12</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>B0D672NXC8</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>75244.07000000001</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-75244.07000000001</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>B0D67727VG</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>12098.32</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-12098.32</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>B0D83Q7L8W</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>7113.56</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-7113.56</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>B0D8445KJN</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1523.73</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-1523.73</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>B0D845B2DG</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>3811.02</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-3811.02</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>B0D84YY632</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>40662.71</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-40662.71</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>B0D85171BL</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>9316.950000000001</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-9316.950000000001</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>B0D8572WTJ</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>54216.95</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-54216.95</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>B0D935TWSR</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>14233.9</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-14233.9</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>B0D9362N4Q</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>11436.44</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-11436.44</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>B0D93652ZY</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>194405.08</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-194405.08</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>B0D9369MTM</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>10164.41</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-10164.41</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>B0D936GPVL</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>34306.78</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-34306.78</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>B0D954M6YQ</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>8005.08</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-8005.08</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>B0D955NZTN</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>16606.78</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-16606.78</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>B0D955YGX7</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>37365.25</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-37365.25</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>B0D9573TBX</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>20759.32</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-20759.32</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>B0D9574DPS</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>18296.61</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-18296.61</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>B0D9KDQCCM</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>7788.99</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-7788.99</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>B0D9KFP4MG</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>6639.83</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-6639.83</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>B0D9KFQG8Q</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1439.83</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-1439.83</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>B0D9KFZYG8</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>5730.53</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-5730.53</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>68027.94</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-68027.94</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>11148.3</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-11148.3</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>11606.78</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-11606.78</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>16940.63</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-16940.63</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>B0DC64BD5R</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>36851.69</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-36851.69</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>B0DC674ZNR</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>14738.98</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-14738.98</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>B0DCGHKRXX</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>3388.14</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-3388.14</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>221815.28</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-221815.28</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>B0DCK3N2JJ</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>27630.51</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-27630.51</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>B0DCK4DR1B</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>3388.14</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-3388.14</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>B0DCK56Q85</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>6353.39</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-6353.39</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>115220.34</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-115220.34</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>B0DFCDZWND</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2371.19</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-2371.19</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>B0DFCG2VGS</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>4548.31</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-4548.31</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>B0DFMKY4TT</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>3050</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-3050</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>B0DJ2V3TH2</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>11435.59</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-11435.59</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>B0DJ2VFZWN</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>13550.85</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-13550.85</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>B0DJ2XCDJ1</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>20758.47</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-20758.47</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>B0DJ2XHK2N</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>172796.61</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-172796.61</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>B0DJ2Y1BG6</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>13555.08</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-13555.08</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>B0DJFH4K8B</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>3286.87</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-3286.87</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>B0DJFH6RTL</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>4319.49</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-4319.49</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>B0DJFJZMC6</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1694.07</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>-1694.07</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>B0DK9LYT4P</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1016.1</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-1016.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>B0DKJHSD8R</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>54213.56</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>-54213.56</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1948.31</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-1948.31</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>B0DKJXRXKM</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1524.58</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-1524.58</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>25413.56</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-25413.56</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>B0DM6BB3VT</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>73678.82000000001</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>-73678.82000000001</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>177885.6</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-177885.6</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>80765.25</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-80765.25</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>23340.68</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-23340.68</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>4744.07</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-4744.07</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
           <t>B0DP32F346</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B160" t="n">
         <v>31515.3</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
         <v>-31515.3</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>B0DP5HM2ZR</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>10972.03</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>-10972.03</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>63436.43</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" t="n">
+        <v>-63436.43</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>B0DQ8W1RBV</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2540.68</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>-2540.68</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>B0DQCWRG3H</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>39938.14</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>-39938.14</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>B0DSBN63D1</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>9192.370000000001</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>-9192.370000000001</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>B0DSBQDZNV</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>27108.47</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>-27108.47</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>B0DSBQYVSM</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>12283.9</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>-12283.9</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>B0DSBR8G7Y</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>12283.9</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>-12283.9</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>B0DSBS17RY</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>12283.05</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>-12283.05</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>B0DSBSD26P</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>24566.1</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>-24566.1</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>B0DSBSGK17</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>40662.71</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>-40662.71</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>B0DT2Q1R2H</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>13555.08</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-13555.08</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>B0DT381WY9</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>9403.389999999999</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>-9403.389999999999</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>B0DT6T6N6B</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>32523.74</v>
+      </c>
+      <c r="C174" t="n">
+        <v>28934.76</v>
+      </c>
+      <c r="D174" t="n">
+        <v>-3588.98</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>B0DT6Y7KJM</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1948.31</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>-1948.31</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>B0DV94R4QD</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>761.86</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>-761.86</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>B0DV9CY3XR</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1795.76</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>-1795.76</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>B0DVC58QPZ</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>7116.95</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>-7116.95</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>190647.46</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>-190647.46</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>B0DVC8NYY2</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>9147.459999999999</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>-9147.459999999999</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>B0DVSZ2VVJ</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>20335.59</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>-20335.59</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>B0F2MZ9BJS</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>253.39</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>-253.39</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>B0F2N37819</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>317.8</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>-317.8</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>B0F2N4N83Y</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>148.31</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>-148.31</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>261623.73</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>-261623.73</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>B0F678L8YT</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>338.14</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>-338.14</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>B0F74DJYG6</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>2100.85</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-2100.85</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>B0FCVBJX29</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>11012.71</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>-11012.71</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>B0FCVLB3FG</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>10165.25</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>-10165.25</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>B0FCVLFLGF</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>7116.1</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>-7116.1</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>B0FCVPBY7Y</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>368491.53</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>-368491.53</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>B0FCVRKB8C</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>12283.05</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>-12283.05</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>B0FFB6YJM1</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>32600.81</v>
+      </c>
+      <c r="C193" t="n">
+        <v>29425.39</v>
+      </c>
+      <c r="D193" t="n">
+        <v>-3175.42</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>B0FFDM5QJX</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>10675.42</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>-10675.42</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>B0FFHXRJNS</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>6777.97</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>-6777.97</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>B0FFJ4N8BK</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>16944.92</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>-16944.92</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>B0FFJPKHZL</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>15672.88</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>-15672.88</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>B0FG88HVQ8</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>122006.6</v>
+      </c>
+      <c r="C198" t="n">
+        <v>118584.57</v>
+      </c>
+      <c r="D198" t="n">
+        <v>-3422.03</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>2471.19</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>-2471.19</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>B0FJ1ZB4G9</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1354.24</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>-1354.24</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>B0FJ2DT13L</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>6523.72</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3261.86</v>
+      </c>
+      <c r="D201" t="n">
+        <v>-3261.86</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>B0FJ8PZ9H7</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>23388.14</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" t="n">
+        <v>-23388.14</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>B0FJG5PFGQ</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>677.12</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>-677.12</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>B0FJS7JZ4V</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>3048.31</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>-3048.31</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>B0FLYHJ6DK</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1355.08</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>-1355.08</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>B0FLYJFC22</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1990.68</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>-1990.68</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>B0FMF1D9NV</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>233.05</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>-233.05</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>3999.15</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>-3999.15</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>25515.25</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>-25515.25</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>B0FN4FHH5Y</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>9320.34</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>-9320.34</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>B0FN4FPJ83</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>15246.61</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" t="n">
+        <v>-15246.61</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>B0FN4GQ9HT</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1235.59</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>-1235.59</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1778.81</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" t="n">
+        <v>-1778.81</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>B0FN4JG97R</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>9879.66</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" t="n">
+        <v>-9879.66</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>B0FN7B3KWS</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>11016.1</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>-11016.1</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>B0FPGDVVCX</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>67615.25</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" t="n">
+        <v>-67615.25</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>B0FPR962YS</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>2795.76</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" t="n">
+        <v>-2795.76</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>B0FQBX8J17</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>15453.38</v>
+      </c>
+      <c r="C218" t="n">
+        <v>14267.79</v>
+      </c>
+      <c r="D218" t="n">
+        <v>-1185.59</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>B0FQBXS6Y2</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>73242.14</v>
+      </c>
+      <c r="C219" t="n">
+        <v>66398.92</v>
+      </c>
+      <c r="D219" t="n">
+        <v>-6843.22</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>B0FQJWWDVK</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1902.52</v>
+      </c>
+      <c r="C220" t="n">
+        <v>1522.01</v>
+      </c>
+      <c r="D220" t="n">
+        <v>-380.51</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>B0FRVBBDM9</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>40029.66</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" t="n">
+        <v>-40029.66</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>B0FS5QZRYB</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>10164.41</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>-10164.41</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>38120.34</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" t="n">
+        <v>-38120.34</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>B0FS7T8151</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>507.63</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" t="n">
+        <v>-507.63</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>B0FSF1N457</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>6599.15</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>-6599.15</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>B0FT8R24QM</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>338.14</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>-338.14</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>B0FTK1RVG8</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>24396.61</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" t="n">
+        <v>-24396.61</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>B0FTK7KQ1P</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>9192.370000000001</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0</v>
+      </c>
+      <c r="D228" t="n">
+        <v>-9192.370000000001</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>B0FTML3VHG</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>45742.37</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>-45742.37</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>B0FTMLYC74</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>40659.32</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" t="n">
+        <v>-40659.32</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>B0FTMM455Z</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>80055.08</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D231" t="n">
+        <v>-80055.08</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>B0FTMMNCK7</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>27108.47</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0</v>
+      </c>
+      <c r="D232" t="n">
+        <v>-27108.47</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>B0FTMRC37L</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>10165.25</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>-10165.25</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>B0FTVV1QJY</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>20334.75</v>
+      </c>
+      <c r="C234" t="n">
+        <v>4066.95</v>
+      </c>
+      <c r="D234" t="n">
+        <v>-16267.8</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>B0FTVVLNS9</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>20167.8</v>
+      </c>
+      <c r="C235" t="n">
+        <v>10083.9</v>
+      </c>
+      <c r="D235" t="n">
+        <v>-10083.9</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>B0FVM17Q4W</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>3388.14</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>-3388.14</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>B0FYNKYJFN</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>338.14</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" t="n">
+        <v>-338.14</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>B0G39ZHDYP</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>24386.41</v>
+      </c>
+      <c r="C238" t="n">
+        <v>21338.1</v>
+      </c>
+      <c r="D238" t="n">
+        <v>-3048.31</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>B0G3B152FR</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>16093.21</v>
+      </c>
+      <c r="C239" t="n">
+        <v>4827.96</v>
+      </c>
+      <c r="D239" t="n">
+        <v>-11265.25</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>B0G4DNF8RZ</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>25161.84</v>
+      </c>
+      <c r="C240" t="n">
+        <v>22366.08</v>
+      </c>
+      <c r="D240" t="n">
+        <v>-2795.76</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>B0G53H49BS</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>108689.77</v>
+      </c>
+      <c r="C241" t="n">
+        <v>106317.74</v>
+      </c>
+      <c r="D241" t="n">
+        <v>-2372.03</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>B0G53KWRVW</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>53384.76</v>
+      </c>
+      <c r="C242" t="n">
+        <v>35589.84</v>
+      </c>
+      <c r="D242" t="n">
+        <v>-17794.92</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>B0G53M9258</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>77106.77</v>
+      </c>
+      <c r="C243" t="n">
+        <v>66091.52</v>
+      </c>
+      <c r="D243" t="n">
+        <v>-11015.25</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>B0GCP1J2HC</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>71516.92999999999</v>
+      </c>
+      <c r="C244" t="n">
+        <v>64314.39</v>
+      </c>
+      <c r="D244" t="n">
+        <v>-7202.54</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>B0GDJPJKSG</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>29652.54</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" t="n">
+        <v>-29652.54</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>B0GDXBGXH2</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>11436.44</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" t="n">
+        <v>-11436.44</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>B0GF7561XM</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>22025.42</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>-22025.42</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>B0GF785MMZ</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>12707.63</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0</v>
+      </c>
+      <c r="D248" t="n">
+        <v>-12707.63</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>B0GF7BLQ27</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>25415.25</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" t="n">
+        <v>-25415.25</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>B0GF7BR5NH</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>22025.42</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" t="n">
+        <v>-22025.42</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>B0GF7GZ4K7</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>8005.93</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0</v>
+      </c>
+      <c r="D251" t="n">
+        <v>-8005.93</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>B0GF7JSSRF</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>36851.69</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0</v>
+      </c>
+      <c r="D252" t="n">
+        <v>-36851.69</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>B0GFD7N73D</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>31347.46</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>-31347.46</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>172866.95</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" t="n">
+        <v>-172866.95</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>B0GKNGWLJ2</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>19825.42</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0</v>
+      </c>
+      <c r="D255" t="n">
+        <v>-19825.42</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>B0GLHC8CB3</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>5759.32</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0</v>
+      </c>
+      <c r="D256" t="n">
+        <v>-5759.32</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>B0GM1CZC7Y</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>48296.61</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" t="n">
+        <v>-48296.61</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>B0GMPGNXX3</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>507.63</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0</v>
+      </c>
+      <c r="D258" t="n">
+        <v>-507.63</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>B0GN2LHJY4</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>38131.36</v>
+      </c>
+      <c r="C259" t="n">
+        <v>30505.09</v>
+      </c>
+      <c r="D259" t="n">
+        <v>-7626.27</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>B0GN86G345</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>9911.02</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0</v>
+      </c>
+      <c r="D260" t="n">
+        <v>-9911.02</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>B0GN8MFDGZ</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>16945.76</v>
+      </c>
+      <c r="C261" t="n">
+        <v>12709.32</v>
+      </c>
+      <c r="D261" t="n">
+        <v>-4236.44</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>B0GN8RQJRG</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>10166.95</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3388.98</v>
+      </c>
+      <c r="D262" t="n">
+        <v>-6777.97</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>71062.72</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" t="n">
+        <v>-71062.72</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>B0GN94YDY2</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>29320.34</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" t="n">
+        <v>-29320.34</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>215311.13</v>
+      </c>
+      <c r="C265" t="n">
+        <v>202261.98</v>
+      </c>
+      <c r="D265" t="n">
+        <v>-13049.15</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>B0GNM35G8X</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>465.25</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0</v>
+      </c>
+      <c r="D266" t="n">
+        <v>-465.25</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>B0GW92TVVC</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>4236.44</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" t="n">
+        <v>-4236.44</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>B0GXP97CZG</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>12945.75</v>
+      </c>
+      <c r="C268" t="n">
+        <v>3287.28</v>
+      </c>
+      <c r="D268" t="n">
+        <v>-9658.469999999999</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>B0GXPBHDRF</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>29656.8</v>
+      </c>
+      <c r="C269" t="n">
+        <v>23725.44</v>
+      </c>
+      <c r="D269" t="n">
+        <v>-5931.36</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>B0GYS6CJD9</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>1686.44</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0</v>
+      </c>
+      <c r="D270" t="n">
+        <v>-1686.44</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>B0H2ZCQFTZ</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>15253.39</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>-15253.39</v>
+      </c>
+      <c r="E271" t="inlineStr">
         <is>
           <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
         </is>
@@ -1154,12 +6678,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sales_trend_units</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_units</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -1167,7 +6711,3276 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-source units drift (diagnostic)</t>
+          <t>B004D4S7AY</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B0058XWUHA</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B007NM84PQ</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B008AXYWHQ</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-29</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B00944CXEY</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B00AFTTQ8I</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B00AG37H8Y</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>34</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-34</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B00AMWDOEK</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B00H2ZDX00</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>25</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-25</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B00HVBJ6W4</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>23</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-23</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B00NVAWTLY</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-16</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B00WM0CF4A</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-16</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B017SN1OI8</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-9</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B01GZZYSRO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B06VV5QB6Q</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B0769YW2KN</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B079DC27J5</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B079XB5RXH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>B07CSNG8XL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B07GVGMW59</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B07M7P7VLX</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>B07MFZ6S2Q</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B07MM5MH6F</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>B07RZ1R1HJ</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B082W4B7SX</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B08QVCPDVT</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B08V3TK36Z</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B09SHQSHBF</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B0B4G7VWXD</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B0BPLWW72Y</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>103</v>
+      </c>
+      <c r="C34" t="n">
+        <v>89</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>104</v>
+      </c>
+      <c r="C35" t="n">
+        <v>101</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>B0BQ7H7418</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>B0BYHHSLPC</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>13</v>
+      </c>
+      <c r="C37" t="n">
+        <v>11</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>B0CBCB82MT</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>9</v>
+      </c>
+      <c r="C38" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>B0CCV74CL7</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>B0CDPMX152</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>33</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-33</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>B0CF5R3V95</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>25</v>
+      </c>
+      <c r="C42" t="n">
+        <v>23</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B0CFKHCQ8W</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>B0CH4PMR8K</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>15</v>
+      </c>
+      <c r="C44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>B0CH4VCD6R</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>32</v>
+      </c>
+      <c r="C45" t="n">
+        <v>30</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>B0CHXGWVZJ</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>8</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>65</v>
+      </c>
+      <c r="C47" t="n">
+        <v>63</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B0CM6WH4ZT</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>37</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-37</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>68</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-68</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>B0D25LNDSY</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>B0D2LD6BYJ</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>8</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-8</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>B0D2LJSQXZ</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>B0D2P5TGWK</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>B0D2P7WLJB</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>B0D63FKYZ5</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>B0D672NXC8</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>13</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-13</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>B0D67727VG</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>14</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>B0D83Q7L8W</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>6</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>B0D8445KJN</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>B0D845B2DG</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>B0D84YY632</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>B0D8572WTJ</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>B0D93652ZY</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>17</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-17</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>B0D936GPVL</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>B0D955NZTN</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>B0D955YGX7</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>B0D9573TBX</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>B0D9574DPS</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>B0D9KDQCCM</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>9</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-9</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B0D9KFP4MG</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>5</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>B0D9KFZYG8</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>29</v>
+      </c>
+      <c r="C75" t="n">
+        <v>25</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>B0DC64BD5R</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>5</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>B0DC674ZNR</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>B0DCGHKRXX</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>127</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-127</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>B0DCK3N2JJ</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>14</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B0DCK4DR1B</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B0DCK56Q85</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>3</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>41</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-41</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B0DFCDZWND</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>B0DFCG2VGS</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>3</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>B0DJ2VFZWN</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>B0DJ2XHK2N</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>17</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-17</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>B0DJFH4K8B</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>B0DJFH6RTL</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>B0DK9LYT4P</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>B0DKJHSD8R</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>4</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>12</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-12</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>B0DM6BB3VT</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>29</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-29</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>37</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-37</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>48</v>
+      </c>
+      <c r="C95" t="n">
+        <v>20</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-28</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>8</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>3</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>5</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>B0DQ8W1RBV</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>B0DQCWRG3H</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>23</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-23</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>B0DSBQDZNV</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>2</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>B0DSBSD26P</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>B0DSBSGK17</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>3</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>B0DT6T6N6B</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>64</v>
+      </c>
+      <c r="C104" t="n">
+        <v>57</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>B0DVC58QPZ</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>B0DVC7VJP1</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>37</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-37</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>B0DVC8NYY2</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>7</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>B0DVSZ2VVJ</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>86</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-86</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>B0F74DJYG6</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>10</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>B0FCVPBY7Y</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>30</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-30</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>B0FFB6YJM1</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>32</v>
+      </c>
+      <c r="C112" t="n">
+        <v>28</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>B0FG88HVQ8</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>72</v>
+      </c>
+      <c r="C113" t="n">
+        <v>70</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>4</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>B0FJ1ZB4G9</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>2</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>B0FJ8PZ9H7</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>2</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>B0FJS7JZ4V</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>3</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>12</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-12</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>52</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-52</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>B0FN4FHH5Y</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>2</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>B0FN4FPJ83</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>13</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-13</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>B0FN4GQ9HT</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>B0FN4JG97R</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>B0FPGDVVCX</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>14</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>B0FQBXS6Y2</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>54</v>
+      </c>
+      <c r="C125" t="n">
+        <v>49</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>B0FRVBBDM9</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>5</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>B0FS6TB7CP</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>21</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-21</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>B0FSF1N457</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>13</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-13</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>B0FT8R24QM</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>B0FTK1RVG8</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>3</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>B0FTML3VHG</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>4</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>B0FTMLYC74</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>4</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>B0FTMM455Z</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>7</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>B0FTMMNCK7</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>B0FTVV1QJY</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>5</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>B0FVM17Q4W</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>B0G39ZHDYP</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>24</v>
+      </c>
+      <c r="C137" t="n">
+        <v>21</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>B0G3B152FR</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>10</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>B0G53KWRVW</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>6</v>
+      </c>
+      <c r="C139" t="n">
+        <v>4</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>B0G53M9258</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>14</v>
+      </c>
+      <c r="C140" t="n">
+        <v>12</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>B0GDJPJKSG</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>B0GF7561XM</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>B0GF7BLQ27</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>B0GF7BR5NH</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>B0GF7JSSRF</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>3</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>B0GFD7N73D</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>18</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-18</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>B0GKNGWLJ2</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>6</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>B0GLHC8CB3</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>4</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>B0GM1CZC7Y</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>10</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>B0GN86G345</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>5</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>B0GN8RQJRG</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>3</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>6</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>B0GN94YDY2</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>33</v>
+      </c>
+      <c r="C155" t="n">
+        <v>31</v>
+      </c>
+      <c r="D155" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>B0GXP97CZG</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>5</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>B0GYS6CJD9</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>10</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
         </is>
       </c>
     </row>
@@ -1444,7 +10257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1482,128 +10295,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sales_gmv</t>
+          <t>sessions</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>632418</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2488801</v>
+        <v>126002</v>
       </c>
       <c r="E2" t="n">
-        <v>-74.59999999999999</v>
+        <v>-100</v>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>sales_units</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>351</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1056</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-66.8</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>sales_gmv</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>165021</v>
-      </c>
-      <c r="D4" t="n">
-        <v>929813</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-82.3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sales_units</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>79</v>
-      </c>
-      <c r="D5" t="n">
-        <v>295</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-73.2</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>sessions</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>126002</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F6" t="inlineStr">
         <is>
           <t>DROP &gt; 50% vs prior 4-week median</t>
         </is>
@@ -1642,6 +10351,34 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — SP-API file has rows but snapshot didn't ingest them</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1704,7 +10441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1915,12 +10652,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1929,121 +10666,9 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>620</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>2056</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>27</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>638</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>b2b</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -10257,7 +10257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10307,12 +10307,64 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>126002</v>
+        <v>129797</v>
       </c>
       <c r="E2" t="n">
         <v>-100</v>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>sessions</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>184194</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sessions</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16742</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>DROP &gt; 50% vs prior 4-week median</t>
         </is>
@@ -10441,7 +10493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10498,7 +10550,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>378042</v>
+        <v>389513</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -10512,7 +10564,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10522,11 +10574,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sessions</t>
+          <t>amazon_gmv</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10396</v>
+        <v>5372790.076271186</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -10540,7 +10592,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10550,11 +10602,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>amazon_gmv</t>
+          <t>sessions</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>677091.9189830509</v>
+        <v>571559</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -10568,7 +10620,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -10582,7 +10634,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13856</v>
+        <v>11076</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -10591,26 +10643,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>ams_trend</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>(brand-total)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>amazon_gmv</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>240</v>
+        <v>2779447.257966102</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -10619,7 +10671,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>ams_trend</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10629,16 +10681,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>(brand-total)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>sessions</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6000</v>
+        <v>50423</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -10647,28 +10699,84 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>240</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>inventory_units</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>white mulberry</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>b2b</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>units_sold</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10997,27 +11105,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -11025,20 +11118,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>26</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in ams_trend for W26</t>
+          <t>clean — Brand missing from a layer (diagnostic)</t>
         </is>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E271"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1511,17 +1511,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B07M7P7VLX</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27447.42</v>
+        <v>24015.25</v>
       </c>
       <c r="C29" t="n">
-        <v>20585.56</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-6861.86</v>
+        <v>-24015.25</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1532,17 +1532,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B07M7P7VLX</t>
+          <t>B07MFZ6S2Q</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24015.25</v>
+        <v>24566.1</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-24015.25</v>
+        <v>-24566.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1553,17 +1553,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B07MFZ6S2Q</t>
+          <t>B07MM5MH6F</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24566.1</v>
+        <v>33035.59</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-24566.1</v>
+        <v>-33035.59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B07MM5MH6F</t>
+          <t>B07RZ1R1HJ</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1595,17 +1595,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B07RZ1R1HJ</t>
+          <t>B07T2XYGR5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>33035.59</v>
+        <v>20334.75</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-33035.59</v>
+        <v>-20334.75</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1616,17 +1616,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B07T2XYGR5</t>
+          <t>B07T3ZLNM3</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>20334.75</v>
+        <v>18216.1</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-20334.75</v>
+        <v>-18216.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1637,17 +1637,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B07T3ZLNM3</t>
+          <t>B07T53T1KV</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>18216.1</v>
+        <v>27538.14</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-18216.1</v>
+        <v>-27538.14</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B07T53T1KV</t>
+          <t>B07T63ZJTR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27538.14</v>
+        <v>19063.56</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>-27538.14</v>
+        <v>-19063.56</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1679,17 +1679,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B07T63ZJTR</t>
+          <t>B0846Q1JT5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19063.56</v>
+        <v>13130.51</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>-19063.56</v>
+        <v>-13130.51</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1700,17 +1700,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B084CG2ZVZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8301.690000000001</v>
+        <v>12283.05</v>
       </c>
       <c r="C38" t="n">
-        <v>4150.84</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-4150.85</v>
+        <v>-12283.05</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1721,17 +1721,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0846Q1JT5</t>
+          <t>B08QVCPDVT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>13130.51</v>
+        <v>61415.25</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>-13130.51</v>
+        <v>-61415.25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1742,17 +1742,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B084CG2ZVZ</t>
+          <t>B08V3TK36Z</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>12283.05</v>
+        <v>33215.25</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>-12283.05</v>
+        <v>-33215.25</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1763,17 +1763,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B08QVCPDVT</t>
+          <t>B08XBYKWW3</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>61415.25</v>
+        <v>13640.68</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>-61415.25</v>
+        <v>-13640.68</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1784,17 +1784,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B08V3TK36Z</t>
+          <t>B09BBK2LV4</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>33215.25</v>
+        <v>23724.58</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>-33215.25</v>
+        <v>-23724.58</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1805,17 +1805,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B08XBYKWW3</t>
+          <t>B09CSXR4TR</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>13640.68</v>
+        <v>13977.97</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>-13640.68</v>
+        <v>-13977.97</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1826,17 +1826,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B09BBK2LV4</t>
+          <t>B09SHQSHBF</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23724.58</v>
+        <v>68199.14999999999</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>-23724.58</v>
+        <v>-68199.14999999999</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1847,17 +1847,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B09CSXR4TR</t>
+          <t>B0BFXL8ZP9</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13977.97</v>
+        <v>11012.71</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>-13977.97</v>
+        <v>-11012.71</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1868,17 +1868,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B09SHQSHBF</t>
+          <t>B0BQ34TRDX</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>68199.14999999999</v>
+        <v>11436.44</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>-68199.14999999999</v>
+        <v>-11436.44</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1889,17 +1889,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0BQZH3LGP</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>514062.18</v>
+        <v>10378.81</v>
       </c>
       <c r="C47" t="n">
-        <v>511757.94</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>-2304.24</v>
+        <v>-10378.81</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1910,17 +1910,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0BS4BHNVN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22439.86</v>
+        <v>20758.47</v>
       </c>
       <c r="C48" t="n">
-        <v>19316.95</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>-3122.91</v>
+        <v>-20758.47</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1931,17 +1931,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0CF61X2BG</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16014.42</v>
+        <v>11435.59</v>
       </c>
       <c r="C49" t="n">
-        <v>10676.28</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>-5338.14</v>
+        <v>-11435.59</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1952,17 +1952,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0CFBB587Z</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>20157.68</v>
+        <v>19487.29</v>
       </c>
       <c r="C50" t="n">
-        <v>17278.02</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>-2879.66</v>
+        <v>-19487.29</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1973,17 +1973,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0CHXGWVZJ</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>9105.93</v>
+        <v>118603.39</v>
       </c>
       <c r="C51" t="n">
-        <v>7284.74</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>-1821.19</v>
+        <v>-118603.39</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1994,17 +1994,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0CJ6ZW8F6</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3810.16</v>
+        <v>10164.41</v>
       </c>
       <c r="C52" t="n">
-        <v>3383.04</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>-427.12</v>
+        <v>-10164.41</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2015,17 +2015,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0CRCWV9DV</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>19060.2</v>
+        <v>13554.24</v>
       </c>
       <c r="C53" t="n">
-        <v>16942.4</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>-2117.8</v>
+        <v>-13554.24</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2036,17 +2036,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0CRD1DRXG</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>18509.3</v>
+        <v>18639.83</v>
       </c>
       <c r="C54" t="n">
-        <v>16433.88</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>-2075.42</v>
+        <v>-18639.83</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2057,17 +2057,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0CRD2CVZL</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2117.8</v>
+        <v>10164.41</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>-2117.8</v>
+        <v>-10164.41</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2078,17 +2078,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CZ8ZKPJ9</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>49527.97</v>
+        <v>9488.139999999999</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>-49527.97</v>
+        <v>-9488.139999999999</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2099,17 +2099,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0CZ91YKMP</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>14150.85</v>
+        <v>8132.2</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>-14150.85</v>
+        <v>-8132.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2120,17 +2120,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0D84YY632</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>43215.25</v>
+        <v>40662.71</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>-43215.25</v>
+        <v>-40662.71</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2141,17 +2141,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0BFXL8ZP9</t>
+          <t>B0D85171BL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>11012.71</v>
+        <v>9316.950000000001</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>-11012.71</v>
+        <v>-9316.950000000001</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2162,17 +2162,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0D8572WTJ</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>16505.93</v>
+        <v>54216.95</v>
       </c>
       <c r="C60" t="n">
-        <v>15950</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>-555.9299999999999</v>
+        <v>-54216.95</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2183,17 +2183,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0D935TWSR</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>144014.61</v>
+        <v>14233.9</v>
       </c>
       <c r="C61" t="n">
-        <v>124331.56</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>-19683.05</v>
+        <v>-14233.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2204,17 +2204,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0D9362N4Q</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>423121.18</v>
+        <v>11436.44</v>
       </c>
       <c r="C62" t="n">
-        <v>410761.49</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>-12359.69</v>
+        <v>-11436.44</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2225,17 +2225,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0D93652ZY</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>16859.67</v>
+        <v>194405.08</v>
       </c>
       <c r="C63" t="n">
-        <v>13555.92</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>-3303.75</v>
+        <v>-194405.08</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2246,17 +2246,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0BQ34TRDX</t>
+          <t>B0D9369MTM</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>11436.44</v>
+        <v>10164.41</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>-11436.44</v>
+        <v>-10164.41</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2267,17 +2267,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0D936GPVL</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>9907.620000000001</v>
+        <v>34306.78</v>
       </c>
       <c r="C65" t="n">
-        <v>6605.08</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>-3302.54</v>
+        <v>-34306.78</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2288,17 +2288,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0BQZH3LGP</t>
+          <t>B0D954M6YQ</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>10378.81</v>
+        <v>8005.08</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>-10378.81</v>
+        <v>-8005.08</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2309,17 +2309,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0BS4BHNVN</t>
+          <t>B0D955NZTN</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>20758.47</v>
+        <v>16606.78</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>-20758.47</v>
+        <v>-16606.78</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2330,17 +2330,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0D955YGX7</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>22056.76</v>
+        <v>37365.25</v>
       </c>
       <c r="C68" t="n">
-        <v>18634.73</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>-3422.03</v>
+        <v>-37365.25</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2351,17 +2351,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0D9573TBX</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>10822.04</v>
+        <v>20759.32</v>
       </c>
       <c r="C69" t="n">
-        <v>8152.52</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>-2669.52</v>
+        <v>-20759.32</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2372,17 +2372,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0D9574DPS</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>19654.24</v>
+        <v>18296.61</v>
       </c>
       <c r="C70" t="n">
-        <v>12283.9</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>-7370.34</v>
+        <v>-18296.61</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2393,17 +2393,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>18297.46</v>
+        <v>68027.94</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>9786.440000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>-18297.46</v>
+        <v>-58241.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2414,17 +2414,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>119211.01</v>
+        <v>11148.3</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>3861.86</v>
       </c>
       <c r="D72" t="n">
-        <v>-119211.01</v>
+        <v>-7286.44</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2435,17 +2435,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>81546.50999999999</v>
+        <v>11606.78</v>
       </c>
       <c r="C73" t="n">
-        <v>75022.78</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>-6523.73</v>
+        <v>-11606.78</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2456,17 +2456,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>18893.23</v>
+        <v>16940.63</v>
       </c>
       <c r="C74" t="n">
-        <v>15673.74</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>-3219.49</v>
+        <v>-16940.63</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2477,17 +2477,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0CF61X2BG</t>
+          <t>B0DC64BD5R</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>11435.59</v>
+        <v>36851.69</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>-11435.59</v>
+        <v>-36851.69</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2498,17 +2498,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0CFBB587Z</t>
+          <t>B0DC674ZNR</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>19487.29</v>
+        <v>14738.98</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>-19487.29</v>
+        <v>-14738.98</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2519,17 +2519,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0DJ2V3TH2</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>8894.07</v>
+        <v>11435.59</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>-8894.07</v>
+        <v>-11435.59</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2540,17 +2540,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0DJ2VFZWN</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>20122.96</v>
+        <v>13550.85</v>
       </c>
       <c r="C78" t="n">
-        <v>13550.8</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>-6572.16</v>
+        <v>-13550.85</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2561,17 +2561,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0DJ2XCDJ1</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>14898.32</v>
+        <v>20758.47</v>
       </c>
       <c r="C79" t="n">
-        <v>13957.64</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>-940.6799999999999</v>
+        <v>-20758.47</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2582,17 +2582,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0CH9JR3HL</t>
+          <t>B0DJ2XHK2N</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2117.8</v>
+        <v>172796.61</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>-2117.8</v>
+        <v>-172796.61</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2603,17 +2603,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0CHXGWVZJ</t>
+          <t>B0DJ2Y1BG6</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>118603.39</v>
+        <v>13555.08</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>-118603.39</v>
+        <v>-13555.08</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2624,17 +2624,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0CJ6ZW8F6</t>
+          <t>B0DKJHSD8R</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>10164.41</v>
+        <v>54213.56</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>-10164.41</v>
+        <v>-54213.56</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2645,17 +2645,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>286555.13</v>
+        <v>80765.25</v>
       </c>
       <c r="C83" t="n">
-        <v>277573.77</v>
+        <v>46883.9</v>
       </c>
       <c r="D83" t="n">
-        <v>-8981.360000000001</v>
+        <v>-33881.35</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2666,17 +2666,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>36794.07</v>
+        <v>23340.68</v>
       </c>
       <c r="C84" t="n">
-        <v>34141.53</v>
+        <v>17791.53</v>
       </c>
       <c r="D84" t="n">
-        <v>-2652.54</v>
+        <v>-5549.15</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2687,17 +2687,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3556.78</v>
+        <v>31515.3</v>
       </c>
       <c r="C85" t="n">
-        <v>2371.19</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>-1185.59</v>
+        <v>-31515.3</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2708,17 +2708,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DP5HM2ZR</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>255055.08</v>
+        <v>10972.03</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>-255055.08</v>
+        <v>-10972.03</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2729,17 +2729,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DSBN63D1</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25425.42</v>
+        <v>9192.370000000001</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>-25425.42</v>
+        <v>-9192.370000000001</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2750,17 +2750,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0CRCWV9DV</t>
+          <t>B0DSBQDZNV</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>13554.24</v>
+        <v>27108.47</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>-13554.24</v>
+        <v>-27108.47</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0CRD1DRXG</t>
+          <t>B0DSBQYVSM</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>18639.83</v>
+        <v>12283.9</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>-18639.83</v>
+        <v>-12283.9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2792,17 +2792,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0CRD2CVZL</t>
+          <t>B0DSBR8G7Y</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>10164.41</v>
+        <v>12283.9</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>-10164.41</v>
+        <v>-12283.9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2813,17 +2813,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B0DSBS17RY</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2033.05</v>
+        <v>12283.05</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>-2033.05</v>
+        <v>-12283.05</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2834,17 +2834,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DSBSD26P</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>150008.49</v>
+        <v>24566.1</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>-150008.49</v>
+        <v>-24566.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2855,17 +2855,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0CZ8ZKPJ9</t>
+          <t>B0DSBSGK17</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>9488.139999999999</v>
+        <v>40662.71</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>-9488.139999999999</v>
+        <v>-40662.71</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2876,17 +2876,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0CZ91YKMP</t>
+          <t>B0DT2Q1R2H</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>8132.2</v>
+        <v>13555.08</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>-8132.2</v>
+        <v>-13555.08</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2897,17 +2897,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DT381WY9</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4062.71</v>
+        <v>9403.389999999999</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>-4062.71</v>
+        <v>-9403.389999999999</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2918,17 +2918,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0FCVBJX29</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>7145.77</v>
+        <v>11012.71</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>-7145.77</v>
+        <v>-11012.71</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2939,17 +2939,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0FCVLB3FG</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>677.12</v>
+        <v>10165.25</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>-677.12</v>
+        <v>-10165.25</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2960,17 +2960,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0FCVLFLGF</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>846.61</v>
+        <v>7116.1</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>-846.61</v>
+        <v>-7116.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2981,17 +2981,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0FCVPBY7Y</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>9658.469999999999</v>
+        <v>368491.53</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>-9658.469999999999</v>
+        <v>-368491.53</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3002,17 +3002,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0D2P5TGWK</t>
+          <t>B0FCVRKB8C</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>760.17</v>
+        <v>12283.05</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>-760.17</v>
+        <v>-12283.05</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3023,17 +3023,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0FFDM5QJX</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1522.89</v>
+        <v>10675.42</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>-1522.89</v>
+        <v>-10675.42</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3044,17 +3044,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0FFHXRJNS</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>8470.34</v>
+        <v>6777.97</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>-8470.34</v>
+        <v>-6777.97</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3065,17 +3065,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0FFJ4N8BK</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>12709.32</v>
+        <v>16944.92</v>
       </c>
       <c r="C103" t="n">
-        <v>8472.879999999999</v>
+        <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>-4236.44</v>
+        <v>-16944.92</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3086,17 +3086,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0FFJPKHZL</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1727.12</v>
+        <v>15672.88</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>-1727.12</v>
+        <v>-15672.88</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3107,17 +3107,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0FRVBBDM9</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>75244.07000000001</v>
+        <v>40029.66</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>-75244.07000000001</v>
+        <v>-40029.66</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3128,17 +3128,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0FS5QZRYB</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>12098.32</v>
+        <v>10164.41</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>-12098.32</v>
+        <v>-10164.41</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3149,17 +3149,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0FTK1RVG8</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>7113.56</v>
+        <v>24396.61</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>-7113.56</v>
+        <v>-24396.61</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3170,17 +3170,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0FTK7KQ1P</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1523.73</v>
+        <v>9192.370000000001</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>-1523.73</v>
+        <v>-9192.370000000001</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3191,17 +3191,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0FTML3VHG</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3811.02</v>
+        <v>45742.37</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>-3811.02</v>
+        <v>-45742.37</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3212,17 +3212,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0D84YY632</t>
+          <t>B0FTMLYC74</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>40662.71</v>
+        <v>40659.32</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>-40662.71</v>
+        <v>-40659.32</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3233,17 +3233,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0D85171BL</t>
+          <t>B0FTMM455Z</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>9316.950000000001</v>
+        <v>80055.08</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>-9316.950000000001</v>
+        <v>-80055.08</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3254,17 +3254,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0D8572WTJ</t>
+          <t>B0FTMMNCK7</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>54216.95</v>
+        <v>27108.47</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>-54216.95</v>
+        <v>-27108.47</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3275,17 +3275,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0D935TWSR</t>
+          <t>B0FTMRC37L</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>14233.9</v>
+        <v>10165.25</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>-14233.9</v>
+        <v>-10165.25</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3296,17 +3296,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0D9362N4Q</t>
+          <t>B0GDJPJKSG</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>11436.44</v>
+        <v>29652.54</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>-11436.44</v>
+        <v>-29652.54</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3317,17 +3317,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0D93652ZY</t>
+          <t>B0GDXBGXH2</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>194405.08</v>
+        <v>11436.44</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>-194405.08</v>
+        <v>-11436.44</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3338,17 +3338,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0D9369MTM</t>
+          <t>B0GF7561XM</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>10164.41</v>
+        <v>22025.42</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>-10164.41</v>
+        <v>-22025.42</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3359,17 +3359,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0D936GPVL</t>
+          <t>B0GF785MMZ</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>34306.78</v>
+        <v>12707.63</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>-34306.78</v>
+        <v>-12707.63</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3380,17 +3380,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0D954M6YQ</t>
+          <t>B0GF7BLQ27</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>8005.08</v>
+        <v>25415.25</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>-8005.08</v>
+        <v>-25415.25</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3401,17 +3401,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0D955NZTN</t>
+          <t>B0GF7BR5NH</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>16606.78</v>
+        <v>22025.42</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>-16606.78</v>
+        <v>-22025.42</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3422,17 +3422,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0D955YGX7</t>
+          <t>B0GF7GZ4K7</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>37365.25</v>
+        <v>8005.93</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>-37365.25</v>
+        <v>-8005.93</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3443,17 +3443,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0D9573TBX</t>
+          <t>B0GF7JSSRF</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>20759.32</v>
+        <v>36851.69</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>-20759.32</v>
+        <v>-36851.69</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -3464,3148 +3464,19 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0D9574DPS</t>
+          <t>B0GFD7N73D</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>18296.61</v>
+        <v>31347.46</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>-18296.61</v>
+        <v>-31347.46</v>
       </c>
       <c r="E122" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>7788.99</v>
-      </c>
-      <c r="C123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" t="n">
-        <v>-7788.99</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>B0D9KFP4MG</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>6639.83</v>
-      </c>
-      <c r="C124" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" t="n">
-        <v>-6639.83</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>B0D9KFQG8Q</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>1439.83</v>
-      </c>
-      <c r="C125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" t="n">
-        <v>-1439.83</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>B0D9KFZYG8</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>5730.53</v>
-      </c>
-      <c r="C126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" t="n">
-        <v>-5730.53</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>68027.94</v>
-      </c>
-      <c r="C127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" t="n">
-        <v>-68027.94</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>B0DB5VVPSB</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>11148.3</v>
-      </c>
-      <c r="C128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" t="n">
-        <v>-11148.3</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>11606.78</v>
-      </c>
-      <c r="C129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" t="n">
-        <v>-11606.78</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>16940.63</v>
-      </c>
-      <c r="C130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" t="n">
-        <v>-16940.63</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>B0DC64BD5R</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>36851.69</v>
-      </c>
-      <c r="C131" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" t="n">
-        <v>-36851.69</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>B0DC674ZNR</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>14738.98</v>
-      </c>
-      <c r="C132" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" t="n">
-        <v>-14738.98</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>B0DCGHKRXX</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>3388.14</v>
-      </c>
-      <c r="C133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" t="n">
-        <v>-3388.14</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>B0DCGHVN81</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>221815.28</v>
-      </c>
-      <c r="C134" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" t="n">
-        <v>-221815.28</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>B0DCK3N2JJ</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>27630.51</v>
-      </c>
-      <c r="C135" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" t="n">
-        <v>-27630.51</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>B0DCK4DR1B</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>3388.14</v>
-      </c>
-      <c r="C136" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" t="n">
-        <v>-3388.14</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>B0DCK56Q85</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>6353.39</v>
-      </c>
-      <c r="C137" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" t="n">
-        <v>-6353.39</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>115220.34</v>
-      </c>
-      <c r="C138" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" t="n">
-        <v>-115220.34</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>B0DFCDZWND</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>2371.19</v>
-      </c>
-      <c r="C139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" t="n">
-        <v>-2371.19</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>B0DFCG2VGS</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>4548.31</v>
-      </c>
-      <c r="C140" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-4548.31</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>B0DFMKY4TT</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>3050</v>
-      </c>
-      <c r="C141" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-3050</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>B0DJ2V3TH2</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>11435.59</v>
-      </c>
-      <c r="C142" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-11435.59</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>B0DJ2VFZWN</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>13550.85</v>
-      </c>
-      <c r="C143" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-13550.85</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>B0DJ2XCDJ1</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>20758.47</v>
-      </c>
-      <c r="C144" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-20758.47</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>B0DJ2XHK2N</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>172796.61</v>
-      </c>
-      <c r="C145" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" t="n">
-        <v>-172796.61</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>B0DJ2Y1BG6</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>13555.08</v>
-      </c>
-      <c r="C146" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-13555.08</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>B0DJFH4K8B</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>3286.87</v>
-      </c>
-      <c r="C147" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-3286.87</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>B0DJFH6RTL</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>4319.49</v>
-      </c>
-      <c r="C148" t="n">
-        <v>0</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-4319.49</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>B0DJFJZMC6</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>1694.07</v>
-      </c>
-      <c r="C149" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-1694.07</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>B0DK9LYT4P</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>1016.1</v>
-      </c>
-      <c r="C150" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-1016.1</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>B0DKJHSD8R</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>54213.56</v>
-      </c>
-      <c r="C151" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-54213.56</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>B0DKJSCLBD</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>1948.31</v>
-      </c>
-      <c r="C152" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-1948.31</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>B0DKJXRXKM</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>1524.58</v>
-      </c>
-      <c r="C153" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" t="n">
-        <v>-1524.58</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>B0DKK15YNJ</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>25413.56</v>
-      </c>
-      <c r="C154" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" t="n">
-        <v>-25413.56</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>B0DM6BB3VT</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>73678.82000000001</v>
-      </c>
-      <c r="C155" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" t="n">
-        <v>-73678.82000000001</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>177885.6</v>
-      </c>
-      <c r="C156" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" t="n">
-        <v>-177885.6</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>B0DP2VVRND</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>80765.25</v>
-      </c>
-      <c r="C157" t="n">
-        <v>0</v>
-      </c>
-      <c r="D157" t="n">
-        <v>-80765.25</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>23340.68</v>
-      </c>
-      <c r="C158" t="n">
-        <v>0</v>
-      </c>
-      <c r="D158" t="n">
-        <v>-23340.68</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>4744.07</v>
-      </c>
-      <c r="C159" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" t="n">
-        <v>-4744.07</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>31515.3</v>
-      </c>
-      <c r="C160" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" t="n">
-        <v>-31515.3</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>B0DP5HM2ZR</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>10972.03</v>
-      </c>
-      <c r="C161" t="n">
-        <v>0</v>
-      </c>
-      <c r="D161" t="n">
-        <v>-10972.03</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>B0DQ4YWSMC</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>63436.43</v>
-      </c>
-      <c r="C162" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" t="n">
-        <v>-63436.43</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>B0DQ8W1RBV</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>2540.68</v>
-      </c>
-      <c r="C163" t="n">
-        <v>0</v>
-      </c>
-      <c r="D163" t="n">
-        <v>-2540.68</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>B0DQCWRG3H</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>39938.14</v>
-      </c>
-      <c r="C164" t="n">
-        <v>0</v>
-      </c>
-      <c r="D164" t="n">
-        <v>-39938.14</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>B0DSBN63D1</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>9192.370000000001</v>
-      </c>
-      <c r="C165" t="n">
-        <v>0</v>
-      </c>
-      <c r="D165" t="n">
-        <v>-9192.370000000001</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>B0DSBQDZNV</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>27108.47</v>
-      </c>
-      <c r="C166" t="n">
-        <v>0</v>
-      </c>
-      <c r="D166" t="n">
-        <v>-27108.47</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>B0DSBQYVSM</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>12283.9</v>
-      </c>
-      <c r="C167" t="n">
-        <v>0</v>
-      </c>
-      <c r="D167" t="n">
-        <v>-12283.9</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>B0DSBR8G7Y</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>12283.9</v>
-      </c>
-      <c r="C168" t="n">
-        <v>0</v>
-      </c>
-      <c r="D168" t="n">
-        <v>-12283.9</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>B0DSBS17RY</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>12283.05</v>
-      </c>
-      <c r="C169" t="n">
-        <v>0</v>
-      </c>
-      <c r="D169" t="n">
-        <v>-12283.05</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>B0DSBSD26P</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>24566.1</v>
-      </c>
-      <c r="C170" t="n">
-        <v>0</v>
-      </c>
-      <c r="D170" t="n">
-        <v>-24566.1</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>B0DSBSGK17</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>40662.71</v>
-      </c>
-      <c r="C171" t="n">
-        <v>0</v>
-      </c>
-      <c r="D171" t="n">
-        <v>-40662.71</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>B0DT2Q1R2H</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>13555.08</v>
-      </c>
-      <c r="C172" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" t="n">
-        <v>-13555.08</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>B0DT381WY9</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>9403.389999999999</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" t="n">
-        <v>-9403.389999999999</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>B0DT6T6N6B</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>32523.74</v>
-      </c>
-      <c r="C174" t="n">
-        <v>28934.76</v>
-      </c>
-      <c r="D174" t="n">
-        <v>-3588.98</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>B0DT6Y7KJM</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>1948.31</v>
-      </c>
-      <c r="C175" t="n">
-        <v>0</v>
-      </c>
-      <c r="D175" t="n">
-        <v>-1948.31</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>B0DV94R4QD</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>761.86</v>
-      </c>
-      <c r="C176" t="n">
-        <v>0</v>
-      </c>
-      <c r="D176" t="n">
-        <v>-761.86</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>B0DV9CY3XR</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>1795.76</v>
-      </c>
-      <c r="C177" t="n">
-        <v>0</v>
-      </c>
-      <c r="D177" t="n">
-        <v>-1795.76</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>B0DVC58QPZ</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>7116.95</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0</v>
-      </c>
-      <c r="D178" t="n">
-        <v>-7116.95</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>190647.46</v>
-      </c>
-      <c r="C179" t="n">
-        <v>0</v>
-      </c>
-      <c r="D179" t="n">
-        <v>-190647.46</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>B0DVC8NYY2</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>9147.459999999999</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0</v>
-      </c>
-      <c r="D180" t="n">
-        <v>-9147.459999999999</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>B0DVSZ2VVJ</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>20335.59</v>
-      </c>
-      <c r="C181" t="n">
-        <v>0</v>
-      </c>
-      <c r="D181" t="n">
-        <v>-20335.59</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>B0F2MZ9BJS</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>253.39</v>
-      </c>
-      <c r="C182" t="n">
-        <v>0</v>
-      </c>
-      <c r="D182" t="n">
-        <v>-253.39</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>B0F2N37819</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>317.8</v>
-      </c>
-      <c r="C183" t="n">
-        <v>0</v>
-      </c>
-      <c r="D183" t="n">
-        <v>-317.8</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>B0F2N4N83Y</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>148.31</v>
-      </c>
-      <c r="C184" t="n">
-        <v>0</v>
-      </c>
-      <c r="D184" t="n">
-        <v>-148.31</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>261623.73</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0</v>
-      </c>
-      <c r="D185" t="n">
-        <v>-261623.73</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>B0F678L8YT</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>338.14</v>
-      </c>
-      <c r="C186" t="n">
-        <v>0</v>
-      </c>
-      <c r="D186" t="n">
-        <v>-338.14</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>B0F74DJYG6</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>2100.85</v>
-      </c>
-      <c r="C187" t="n">
-        <v>0</v>
-      </c>
-      <c r="D187" t="n">
-        <v>-2100.85</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>B0FCVBJX29</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>11012.71</v>
-      </c>
-      <c r="C188" t="n">
-        <v>0</v>
-      </c>
-      <c r="D188" t="n">
-        <v>-11012.71</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>B0FCVLB3FG</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>10165.25</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0</v>
-      </c>
-      <c r="D189" t="n">
-        <v>-10165.25</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>B0FCVLFLGF</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>7116.1</v>
-      </c>
-      <c r="C190" t="n">
-        <v>0</v>
-      </c>
-      <c r="D190" t="n">
-        <v>-7116.1</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>B0FCVPBY7Y</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>368491.53</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0</v>
-      </c>
-      <c r="D191" t="n">
-        <v>-368491.53</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>B0FCVRKB8C</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>12283.05</v>
-      </c>
-      <c r="C192" t="n">
-        <v>0</v>
-      </c>
-      <c r="D192" t="n">
-        <v>-12283.05</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>B0FFB6YJM1</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>32600.81</v>
-      </c>
-      <c r="C193" t="n">
-        <v>29425.39</v>
-      </c>
-      <c r="D193" t="n">
-        <v>-3175.42</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>B0FFDM5QJX</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>10675.42</v>
-      </c>
-      <c r="C194" t="n">
-        <v>0</v>
-      </c>
-      <c r="D194" t="n">
-        <v>-10675.42</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>B0FFHXRJNS</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>6777.97</v>
-      </c>
-      <c r="C195" t="n">
-        <v>0</v>
-      </c>
-      <c r="D195" t="n">
-        <v>-6777.97</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>B0FFJ4N8BK</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>16944.92</v>
-      </c>
-      <c r="C196" t="n">
-        <v>0</v>
-      </c>
-      <c r="D196" t="n">
-        <v>-16944.92</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>B0FFJPKHZL</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>15672.88</v>
-      </c>
-      <c r="C197" t="n">
-        <v>0</v>
-      </c>
-      <c r="D197" t="n">
-        <v>-15672.88</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>B0FG88HVQ8</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>122006.6</v>
-      </c>
-      <c r="C198" t="n">
-        <v>118584.57</v>
-      </c>
-      <c r="D198" t="n">
-        <v>-3422.03</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>B0FHVWHQHR</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>2471.19</v>
-      </c>
-      <c r="C199" t="n">
-        <v>0</v>
-      </c>
-      <c r="D199" t="n">
-        <v>-2471.19</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>B0FJ1ZB4G9</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>1354.24</v>
-      </c>
-      <c r="C200" t="n">
-        <v>0</v>
-      </c>
-      <c r="D200" t="n">
-        <v>-1354.24</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>B0FJ2DT13L</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>6523.72</v>
-      </c>
-      <c r="C201" t="n">
-        <v>3261.86</v>
-      </c>
-      <c r="D201" t="n">
-        <v>-3261.86</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>B0FJ8PZ9H7</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>23388.14</v>
-      </c>
-      <c r="C202" t="n">
-        <v>0</v>
-      </c>
-      <c r="D202" t="n">
-        <v>-23388.14</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>B0FJG5PFGQ</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>677.12</v>
-      </c>
-      <c r="C203" t="n">
-        <v>0</v>
-      </c>
-      <c r="D203" t="n">
-        <v>-677.12</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>B0FJS7JZ4V</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>3048.31</v>
-      </c>
-      <c r="C204" t="n">
-        <v>0</v>
-      </c>
-      <c r="D204" t="n">
-        <v>-3048.31</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>B0FLYHJ6DK</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>1355.08</v>
-      </c>
-      <c r="C205" t="n">
-        <v>0</v>
-      </c>
-      <c r="D205" t="n">
-        <v>-1355.08</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>B0FLYJFC22</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>1990.68</v>
-      </c>
-      <c r="C206" t="n">
-        <v>0</v>
-      </c>
-      <c r="D206" t="n">
-        <v>-1990.68</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>B0FMF1D9NV</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>233.05</v>
-      </c>
-      <c r="C207" t="n">
-        <v>0</v>
-      </c>
-      <c r="D207" t="n">
-        <v>-233.05</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>B0FN4D3C89</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>3999.15</v>
-      </c>
-      <c r="C208" t="n">
-        <v>0</v>
-      </c>
-      <c r="D208" t="n">
-        <v>-3999.15</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>B0FN4DSQ6P</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>25515.25</v>
-      </c>
-      <c r="C209" t="n">
-        <v>0</v>
-      </c>
-      <c r="D209" t="n">
-        <v>-25515.25</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>B0FN4FHH5Y</t>
-        </is>
-      </c>
-      <c r="B210" t="n">
-        <v>9320.34</v>
-      </c>
-      <c r="C210" t="n">
-        <v>0</v>
-      </c>
-      <c r="D210" t="n">
-        <v>-9320.34</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>B0FN4FPJ83</t>
-        </is>
-      </c>
-      <c r="B211" t="n">
-        <v>15246.61</v>
-      </c>
-      <c r="C211" t="n">
-        <v>0</v>
-      </c>
-      <c r="D211" t="n">
-        <v>-15246.61</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>B0FN4GQ9HT</t>
-        </is>
-      </c>
-      <c r="B212" t="n">
-        <v>1235.59</v>
-      </c>
-      <c r="C212" t="n">
-        <v>0</v>
-      </c>
-      <c r="D212" t="n">
-        <v>-1235.59</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>B0FN4HDM6Z</t>
-        </is>
-      </c>
-      <c r="B213" t="n">
-        <v>1778.81</v>
-      </c>
-      <c r="C213" t="n">
-        <v>0</v>
-      </c>
-      <c r="D213" t="n">
-        <v>-1778.81</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>B0FN4JG97R</t>
-        </is>
-      </c>
-      <c r="B214" t="n">
-        <v>9879.66</v>
-      </c>
-      <c r="C214" t="n">
-        <v>0</v>
-      </c>
-      <c r="D214" t="n">
-        <v>-9879.66</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>B0FN7B3KWS</t>
-        </is>
-      </c>
-      <c r="B215" t="n">
-        <v>11016.1</v>
-      </c>
-      <c r="C215" t="n">
-        <v>0</v>
-      </c>
-      <c r="D215" t="n">
-        <v>-11016.1</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>B0FPGDVVCX</t>
-        </is>
-      </c>
-      <c r="B216" t="n">
-        <v>67615.25</v>
-      </c>
-      <c r="C216" t="n">
-        <v>0</v>
-      </c>
-      <c r="D216" t="n">
-        <v>-67615.25</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>B0FPR962YS</t>
-        </is>
-      </c>
-      <c r="B217" t="n">
-        <v>2795.76</v>
-      </c>
-      <c r="C217" t="n">
-        <v>0</v>
-      </c>
-      <c r="D217" t="n">
-        <v>-2795.76</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>B0FQBX8J17</t>
-        </is>
-      </c>
-      <c r="B218" t="n">
-        <v>15453.38</v>
-      </c>
-      <c r="C218" t="n">
-        <v>14267.79</v>
-      </c>
-      <c r="D218" t="n">
-        <v>-1185.59</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>B0FQBXS6Y2</t>
-        </is>
-      </c>
-      <c r="B219" t="n">
-        <v>73242.14</v>
-      </c>
-      <c r="C219" t="n">
-        <v>66398.92</v>
-      </c>
-      <c r="D219" t="n">
-        <v>-6843.22</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>B0FQJWWDVK</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>1902.52</v>
-      </c>
-      <c r="C220" t="n">
-        <v>1522.01</v>
-      </c>
-      <c r="D220" t="n">
-        <v>-380.51</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>B0FRVBBDM9</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>40029.66</v>
-      </c>
-      <c r="C221" t="n">
-        <v>0</v>
-      </c>
-      <c r="D221" t="n">
-        <v>-40029.66</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>B0FS5QZRYB</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>10164.41</v>
-      </c>
-      <c r="C222" t="n">
-        <v>0</v>
-      </c>
-      <c r="D222" t="n">
-        <v>-10164.41</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>B0FS6TB7CP</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>38120.34</v>
-      </c>
-      <c r="C223" t="n">
-        <v>0</v>
-      </c>
-      <c r="D223" t="n">
-        <v>-38120.34</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>B0FS7T8151</t>
-        </is>
-      </c>
-      <c r="B224" t="n">
-        <v>507.63</v>
-      </c>
-      <c r="C224" t="n">
-        <v>0</v>
-      </c>
-      <c r="D224" t="n">
-        <v>-507.63</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>B0FSF1N457</t>
-        </is>
-      </c>
-      <c r="B225" t="n">
-        <v>6599.15</v>
-      </c>
-      <c r="C225" t="n">
-        <v>0</v>
-      </c>
-      <c r="D225" t="n">
-        <v>-6599.15</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>B0FT8R24QM</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>338.14</v>
-      </c>
-      <c r="C226" t="n">
-        <v>0</v>
-      </c>
-      <c r="D226" t="n">
-        <v>-338.14</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>B0FTK1RVG8</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>24396.61</v>
-      </c>
-      <c r="C227" t="n">
-        <v>0</v>
-      </c>
-      <c r="D227" t="n">
-        <v>-24396.61</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>B0FTK7KQ1P</t>
-        </is>
-      </c>
-      <c r="B228" t="n">
-        <v>9192.370000000001</v>
-      </c>
-      <c r="C228" t="n">
-        <v>0</v>
-      </c>
-      <c r="D228" t="n">
-        <v>-9192.370000000001</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>B0FTML3VHG</t>
-        </is>
-      </c>
-      <c r="B229" t="n">
-        <v>45742.37</v>
-      </c>
-      <c r="C229" t="n">
-        <v>0</v>
-      </c>
-      <c r="D229" t="n">
-        <v>-45742.37</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>B0FTMLYC74</t>
-        </is>
-      </c>
-      <c r="B230" t="n">
-        <v>40659.32</v>
-      </c>
-      <c r="C230" t="n">
-        <v>0</v>
-      </c>
-      <c r="D230" t="n">
-        <v>-40659.32</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>B0FTMM455Z</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>80055.08</v>
-      </c>
-      <c r="C231" t="n">
-        <v>0</v>
-      </c>
-      <c r="D231" t="n">
-        <v>-80055.08</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>B0FTMMNCK7</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>27108.47</v>
-      </c>
-      <c r="C232" t="n">
-        <v>0</v>
-      </c>
-      <c r="D232" t="n">
-        <v>-27108.47</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>B0FTMRC37L</t>
-        </is>
-      </c>
-      <c r="B233" t="n">
-        <v>10165.25</v>
-      </c>
-      <c r="C233" t="n">
-        <v>0</v>
-      </c>
-      <c r="D233" t="n">
-        <v>-10165.25</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>B0FTVV1QJY</t>
-        </is>
-      </c>
-      <c r="B234" t="n">
-        <v>20334.75</v>
-      </c>
-      <c r="C234" t="n">
-        <v>4066.95</v>
-      </c>
-      <c r="D234" t="n">
-        <v>-16267.8</v>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>B0FTVVLNS9</t>
-        </is>
-      </c>
-      <c r="B235" t="n">
-        <v>20167.8</v>
-      </c>
-      <c r="C235" t="n">
-        <v>10083.9</v>
-      </c>
-      <c r="D235" t="n">
-        <v>-10083.9</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>B0FVM17Q4W</t>
-        </is>
-      </c>
-      <c r="B236" t="n">
-        <v>3388.14</v>
-      </c>
-      <c r="C236" t="n">
-        <v>0</v>
-      </c>
-      <c r="D236" t="n">
-        <v>-3388.14</v>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>B0FYNKYJFN</t>
-        </is>
-      </c>
-      <c r="B237" t="n">
-        <v>338.14</v>
-      </c>
-      <c r="C237" t="n">
-        <v>0</v>
-      </c>
-      <c r="D237" t="n">
-        <v>-338.14</v>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>B0G39ZHDYP</t>
-        </is>
-      </c>
-      <c r="B238" t="n">
-        <v>24386.41</v>
-      </c>
-      <c r="C238" t="n">
-        <v>21338.1</v>
-      </c>
-      <c r="D238" t="n">
-        <v>-3048.31</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>B0G3B152FR</t>
-        </is>
-      </c>
-      <c r="B239" t="n">
-        <v>16093.21</v>
-      </c>
-      <c r="C239" t="n">
-        <v>4827.96</v>
-      </c>
-      <c r="D239" t="n">
-        <v>-11265.25</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>B0G4DNF8RZ</t>
-        </is>
-      </c>
-      <c r="B240" t="n">
-        <v>25161.84</v>
-      </c>
-      <c r="C240" t="n">
-        <v>22366.08</v>
-      </c>
-      <c r="D240" t="n">
-        <v>-2795.76</v>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>B0G53H49BS</t>
-        </is>
-      </c>
-      <c r="B241" t="n">
-        <v>108689.77</v>
-      </c>
-      <c r="C241" t="n">
-        <v>106317.74</v>
-      </c>
-      <c r="D241" t="n">
-        <v>-2372.03</v>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>B0G53KWRVW</t>
-        </is>
-      </c>
-      <c r="B242" t="n">
-        <v>53384.76</v>
-      </c>
-      <c r="C242" t="n">
-        <v>35589.84</v>
-      </c>
-      <c r="D242" t="n">
-        <v>-17794.92</v>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>B0G53M9258</t>
-        </is>
-      </c>
-      <c r="B243" t="n">
-        <v>77106.77</v>
-      </c>
-      <c r="C243" t="n">
-        <v>66091.52</v>
-      </c>
-      <c r="D243" t="n">
-        <v>-11015.25</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>B0GCP1J2HC</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>71516.92999999999</v>
-      </c>
-      <c r="C244" t="n">
-        <v>64314.39</v>
-      </c>
-      <c r="D244" t="n">
-        <v>-7202.54</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>B0GDJPJKSG</t>
-        </is>
-      </c>
-      <c r="B245" t="n">
-        <v>29652.54</v>
-      </c>
-      <c r="C245" t="n">
-        <v>0</v>
-      </c>
-      <c r="D245" t="n">
-        <v>-29652.54</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>B0GDXBGXH2</t>
-        </is>
-      </c>
-      <c r="B246" t="n">
-        <v>11436.44</v>
-      </c>
-      <c r="C246" t="n">
-        <v>0</v>
-      </c>
-      <c r="D246" t="n">
-        <v>-11436.44</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>B0GF7561XM</t>
-        </is>
-      </c>
-      <c r="B247" t="n">
-        <v>22025.42</v>
-      </c>
-      <c r="C247" t="n">
-        <v>0</v>
-      </c>
-      <c r="D247" t="n">
-        <v>-22025.42</v>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>B0GF785MMZ</t>
-        </is>
-      </c>
-      <c r="B248" t="n">
-        <v>12707.63</v>
-      </c>
-      <c r="C248" t="n">
-        <v>0</v>
-      </c>
-      <c r="D248" t="n">
-        <v>-12707.63</v>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>B0GF7BLQ27</t>
-        </is>
-      </c>
-      <c r="B249" t="n">
-        <v>25415.25</v>
-      </c>
-      <c r="C249" t="n">
-        <v>0</v>
-      </c>
-      <c r="D249" t="n">
-        <v>-25415.25</v>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>B0GF7BR5NH</t>
-        </is>
-      </c>
-      <c r="B250" t="n">
-        <v>22025.42</v>
-      </c>
-      <c r="C250" t="n">
-        <v>0</v>
-      </c>
-      <c r="D250" t="n">
-        <v>-22025.42</v>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>B0GF7GZ4K7</t>
-        </is>
-      </c>
-      <c r="B251" t="n">
-        <v>8005.93</v>
-      </c>
-      <c r="C251" t="n">
-        <v>0</v>
-      </c>
-      <c r="D251" t="n">
-        <v>-8005.93</v>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>B0GF7JSSRF</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>36851.69</v>
-      </c>
-      <c r="C252" t="n">
-        <v>0</v>
-      </c>
-      <c r="D252" t="n">
-        <v>-36851.69</v>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>B0GFD7N73D</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>31347.46</v>
-      </c>
-      <c r="C253" t="n">
-        <v>0</v>
-      </c>
-      <c r="D253" t="n">
-        <v>-31347.46</v>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
-      <c r="B254" t="n">
-        <v>172866.95</v>
-      </c>
-      <c r="C254" t="n">
-        <v>0</v>
-      </c>
-      <c r="D254" t="n">
-        <v>-172866.95</v>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>B0GKNGWLJ2</t>
-        </is>
-      </c>
-      <c r="B255" t="n">
-        <v>19825.42</v>
-      </c>
-      <c r="C255" t="n">
-        <v>0</v>
-      </c>
-      <c r="D255" t="n">
-        <v>-19825.42</v>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>B0GLHC8CB3</t>
-        </is>
-      </c>
-      <c r="B256" t="n">
-        <v>5759.32</v>
-      </c>
-      <c r="C256" t="n">
-        <v>0</v>
-      </c>
-      <c r="D256" t="n">
-        <v>-5759.32</v>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>B0GM1CZC7Y</t>
-        </is>
-      </c>
-      <c r="B257" t="n">
-        <v>48296.61</v>
-      </c>
-      <c r="C257" t="n">
-        <v>0</v>
-      </c>
-      <c r="D257" t="n">
-        <v>-48296.61</v>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>B0GMPGNXX3</t>
-        </is>
-      </c>
-      <c r="B258" t="n">
-        <v>507.63</v>
-      </c>
-      <c r="C258" t="n">
-        <v>0</v>
-      </c>
-      <c r="D258" t="n">
-        <v>-507.63</v>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>B0GN2LHJY4</t>
-        </is>
-      </c>
-      <c r="B259" t="n">
-        <v>38131.36</v>
-      </c>
-      <c r="C259" t="n">
-        <v>30505.09</v>
-      </c>
-      <c r="D259" t="n">
-        <v>-7626.27</v>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>B0GN86G345</t>
-        </is>
-      </c>
-      <c r="B260" t="n">
-        <v>9911.02</v>
-      </c>
-      <c r="C260" t="n">
-        <v>0</v>
-      </c>
-      <c r="D260" t="n">
-        <v>-9911.02</v>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>B0GN8MFDGZ</t>
-        </is>
-      </c>
-      <c r="B261" t="n">
-        <v>16945.76</v>
-      </c>
-      <c r="C261" t="n">
-        <v>12709.32</v>
-      </c>
-      <c r="D261" t="n">
-        <v>-4236.44</v>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>B0GN8RQJRG</t>
-        </is>
-      </c>
-      <c r="B262" t="n">
-        <v>10166.95</v>
-      </c>
-      <c r="C262" t="n">
-        <v>3388.98</v>
-      </c>
-      <c r="D262" t="n">
-        <v>-6777.97</v>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>B0GN8WW6BC</t>
-        </is>
-      </c>
-      <c r="B263" t="n">
-        <v>71062.72</v>
-      </c>
-      <c r="C263" t="n">
-        <v>0</v>
-      </c>
-      <c r="D263" t="n">
-        <v>-71062.72</v>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>B0GN94YDY2</t>
-        </is>
-      </c>
-      <c r="B264" t="n">
-        <v>29320.34</v>
-      </c>
-      <c r="C264" t="n">
-        <v>0</v>
-      </c>
-      <c r="D264" t="n">
-        <v>-29320.34</v>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="B265" t="n">
-        <v>215311.13</v>
-      </c>
-      <c r="C265" t="n">
-        <v>202261.98</v>
-      </c>
-      <c r="D265" t="n">
-        <v>-13049.15</v>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>B0GNM35G8X</t>
-        </is>
-      </c>
-      <c r="B266" t="n">
-        <v>465.25</v>
-      </c>
-      <c r="C266" t="n">
-        <v>0</v>
-      </c>
-      <c r="D266" t="n">
-        <v>-465.25</v>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>B0GW92TVVC</t>
-        </is>
-      </c>
-      <c r="B267" t="n">
-        <v>4236.44</v>
-      </c>
-      <c r="C267" t="n">
-        <v>0</v>
-      </c>
-      <c r="D267" t="n">
-        <v>-4236.44</v>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>B0GXP97CZG</t>
-        </is>
-      </c>
-      <c r="B268" t="n">
-        <v>12945.75</v>
-      </c>
-      <c r="C268" t="n">
-        <v>3287.28</v>
-      </c>
-      <c r="D268" t="n">
-        <v>-9658.469999999999</v>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>B0GXPBHDRF</t>
-        </is>
-      </c>
-      <c r="B269" t="n">
-        <v>29656.8</v>
-      </c>
-      <c r="C269" t="n">
-        <v>23725.44</v>
-      </c>
-      <c r="D269" t="n">
-        <v>-5931.36</v>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>B0GYS6CJD9</t>
-        </is>
-      </c>
-      <c r="B270" t="n">
-        <v>1686.44</v>
-      </c>
-      <c r="C270" t="n">
-        <v>0</v>
-      </c>
-      <c r="D270" t="n">
-        <v>-1686.44</v>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>B0H2ZCQFTZ</t>
-        </is>
-      </c>
-      <c r="B271" t="n">
-        <v>15253.39</v>
-      </c>
-      <c r="C271" t="n">
-        <v>0</v>
-      </c>
-      <c r="D271" t="n">
-        <v>-15253.39</v>
-      </c>
-      <c r="E271" t="inlineStr">
         <is>
           <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
         </is>
@@ -6678,7 +3549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E157"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7110,14 +3981,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B07M7P7VLX</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>-3</v>
@@ -7131,17 +4002,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B07M7P7VLX</t>
+          <t>B07MFZ6S2Q</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -7152,17 +4023,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B07MFZ6S2Q</t>
+          <t>B07MM5MH6F</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -7173,7 +4044,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B07MM5MH6F</t>
+          <t>B07RZ1R1HJ</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -7194,17 +4065,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B07RZ1R1HJ</t>
+          <t>B08QVCPDVT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -7215,14 +4086,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B08V3TK36Z</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>-2</v>
@@ -7236,7 +4107,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B08QVCPDVT</t>
+          <t>B09SHQSHBF</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -7257,17 +4128,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B08V3TK36Z</t>
+          <t>B0CHXGWVZJ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -7278,17 +4149,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B09SHQSHBF</t>
+          <t>B0D84YY632</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -7299,17 +4170,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0D8572WTJ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -7320,17 +4191,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0D93652ZY</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -7341,17 +4212,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0D936GPVL</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -7362,17 +4233,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0D955NZTN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -7383,17 +4254,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0D955YGX7</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-14</v>
+        <v>-3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -7404,17 +4275,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0D9573TBX</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -7425,17 +4296,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0D9574DPS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -7446,17 +4317,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0DC64BD5R</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -7467,17 +4338,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0DC674ZNR</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -7488,17 +4359,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0DJ2VFZWN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -7509,17 +4380,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DJ2XHK2N</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -7530,17 +4401,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DKJHSD8R</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>-33</v>
+        <v>-4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -7551,14 +4422,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0DSBQDZNV</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>-2</v>
@@ -7572,17 +4443,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0DSBSD26P</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -7593,17 +4464,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0DSBSGK17</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -7614,17 +4485,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0FCVPBY7Y</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C45" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>-2</v>
+        <v>-30</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -7635,17 +4506,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0CHXGWVZJ</t>
+          <t>B0FRVBBDM9</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -7656,17 +4527,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0FTK1RVG8</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="C47" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -7677,17 +4548,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0FTML3VHG</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -7698,17 +4569,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0FTMLYC74</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>-37</v>
+        <v>-4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -7719,17 +4590,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0FTMM455Z</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -7740,17 +4611,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0FTMMNCK7</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>-68</v>
+        <v>-2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -7761,17 +4632,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0GDJPJKSG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -7782,17 +4653,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0GF7561XM</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -7803,17 +4674,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0GF7BLQ27</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -7824,17 +4695,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0D2P5TGWK</t>
+          <t>B0GF7BR5NH</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -7845,17 +4716,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0GF7JSSRF</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -7866,2119 +4737,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0GFD7N73D</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="E57" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>B0D63FKYZ5</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>B0D672NXC8</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>13</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-13</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>B0D67727VG</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>14</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>B0D83Q7L8W</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>6</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="n">
-        <v>-6</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>B0D8445KJN</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>2</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>B0D845B2DG</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>3</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>B0D84YY632</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>B0D8572WTJ</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>4</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>B0D93652ZY</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>17</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" t="n">
-        <v>-17</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>B0D936GPVL</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>3</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>B0D955NZTN</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>2</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>B0D955YGX7</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>3</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>B0D9573TBX</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>2</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>B0D9574DPS</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>2</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>9</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="n">
-        <v>-9</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>B0D9KFP4MG</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>5</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>B0D9KFZYG8</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>4</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>29</v>
-      </c>
-      <c r="C75" t="n">
-        <v>25</v>
-      </c>
-      <c r="D75" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>B0DC64BD5R</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>5</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>B0DC674ZNR</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>2</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>B0DCGHKRXX</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>3</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>B0DCGHVN81</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>127</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="n">
-        <v>-127</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>B0DCK3N2JJ</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>14</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>B0DCK4DR1B</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>2</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>B0DCK56Q85</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>3</v>
-      </c>
-      <c r="C82" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>41</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="n">
-        <v>-41</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>B0DFCDZWND</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>2</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>B0DFCG2VGS</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>3</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>B0DJ2VFZWN</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>2</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>B0DJ2XHK2N</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>17</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="n">
-        <v>-17</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>B0DJFH4K8B</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>3</v>
-      </c>
-      <c r="C88" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>B0DJFH6RTL</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>3</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>B0DK9LYT4P</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>2</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>B0DKJHSD8R</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>4</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>B0DKK15YNJ</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>12</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" t="n">
-        <v>-12</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>B0DM6BB3VT</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>29</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" t="n">
-        <v>-29</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>37</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="n">
-        <v>-37</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>B0DP2VVRND</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>48</v>
-      </c>
-      <c r="C95" t="n">
-        <v>20</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-28</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>8</v>
-      </c>
-      <c r="C96" t="n">
-        <v>2</v>
-      </c>
-      <c r="D96" t="n">
-        <v>-6</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>3</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>B0DQ4YWSMC</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>5</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>B0DQ8W1RBV</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>2</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>B0DQCWRG3H</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>23</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="n">
-        <v>-23</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>B0DSBQDZNV</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>2</v>
-      </c>
-      <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>B0DSBSD26P</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>2</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>B0DSBSGK17</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>3</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>B0DT6T6N6B</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>64</v>
-      </c>
-      <c r="C104" t="n">
-        <v>57</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-7</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>B0DVC58QPZ</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>2</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>B0DVC7VJP1</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>37</v>
-      </c>
-      <c r="C106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" t="n">
-        <v>-37</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>B0DVC8NYY2</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>7</v>
-      </c>
-      <c r="C107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" t="n">
-        <v>-7</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>B0DVSZ2VVJ</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>4</v>
-      </c>
-      <c r="C108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>86</v>
-      </c>
-      <c r="C109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" t="n">
-        <v>-86</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>B0F74DJYG6</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>10</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" t="n">
-        <v>-10</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>B0FCVPBY7Y</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>30</v>
-      </c>
-      <c r="C111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" t="n">
-        <v>-30</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>B0FFB6YJM1</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>32</v>
-      </c>
-      <c r="C112" t="n">
-        <v>28</v>
-      </c>
-      <c r="D112" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>B0FG88HVQ8</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>72</v>
-      </c>
-      <c r="C113" t="n">
-        <v>70</v>
-      </c>
-      <c r="D113" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>B0FHVWHQHR</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>4</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>B0FJ1ZB4G9</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>2</v>
-      </c>
-      <c r="C115" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>B0FJ8PZ9H7</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>2</v>
-      </c>
-      <c r="C116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>B0FJS7JZ4V</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>3</v>
-      </c>
-      <c r="C117" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>B0FN4D3C89</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>12</v>
-      </c>
-      <c r="C118" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" t="n">
-        <v>-12</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>B0FN4DSQ6P</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>52</v>
-      </c>
-      <c r="C119" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" t="n">
-        <v>-52</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>B0FN4FHH5Y</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>2</v>
-      </c>
-      <c r="C120" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>B0FN4FPJ83</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>13</v>
-      </c>
-      <c r="C121" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" t="n">
-        <v>-13</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>B0FN4GQ9HT</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>2</v>
-      </c>
-      <c r="C122" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>B0FN4JG97R</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>2</v>
-      </c>
-      <c r="C123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>B0FPGDVVCX</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>14</v>
-      </c>
-      <c r="C124" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>B0FQBXS6Y2</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>54</v>
-      </c>
-      <c r="C125" t="n">
-        <v>49</v>
-      </c>
-      <c r="D125" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>B0FRVBBDM9</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>5</v>
-      </c>
-      <c r="C126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>B0FS6TB7CP</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>21</v>
-      </c>
-      <c r="C127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" t="n">
-        <v>-21</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>B0FSF1N457</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>13</v>
-      </c>
-      <c r="C128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" t="n">
-        <v>-13</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>B0FT8R24QM</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>2</v>
-      </c>
-      <c r="C129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>B0FTK1RVG8</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>3</v>
-      </c>
-      <c r="C130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>B0FTML3VHG</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>4</v>
-      </c>
-      <c r="C131" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>B0FTMLYC74</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>4</v>
-      </c>
-      <c r="C132" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>B0FTMM455Z</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>7</v>
-      </c>
-      <c r="C133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" t="n">
-        <v>-7</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>B0FTMMNCK7</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>2</v>
-      </c>
-      <c r="C134" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>B0FTVV1QJY</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>5</v>
-      </c>
-      <c r="C135" t="n">
-        <v>1</v>
-      </c>
-      <c r="D135" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>B0FVM17Q4W</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>2</v>
-      </c>
-      <c r="C136" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>B0G39ZHDYP</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>24</v>
-      </c>
-      <c r="C137" t="n">
-        <v>21</v>
-      </c>
-      <c r="D137" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>B0G3B152FR</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>10</v>
-      </c>
-      <c r="C138" t="n">
-        <v>3</v>
-      </c>
-      <c r="D138" t="n">
-        <v>-7</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>B0G53KWRVW</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>6</v>
-      </c>
-      <c r="C139" t="n">
-        <v>4</v>
-      </c>
-      <c r="D139" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>B0G53M9258</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>14</v>
-      </c>
-      <c r="C140" t="n">
-        <v>12</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>B0GDJPJKSG</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>2</v>
-      </c>
-      <c r="C141" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>B0GF7561XM</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>2</v>
-      </c>
-      <c r="C142" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>B0GF7BLQ27</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>2</v>
-      </c>
-      <c r="C143" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>B0GF7BR5NH</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>2</v>
-      </c>
-      <c r="C144" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>B0GF7JSSRF</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>3</v>
-      </c>
-      <c r="C145" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>B0GFD7N73D</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>2</v>
-      </c>
-      <c r="C146" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>18</v>
-      </c>
-      <c r="C147" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-18</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>B0GKNGWLJ2</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>6</v>
-      </c>
-      <c r="C148" t="n">
-        <v>0</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-6</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>B0GLHC8CB3</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>4</v>
-      </c>
-      <c r="C149" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>B0GM1CZC7Y</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>10</v>
-      </c>
-      <c r="C150" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-10</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>B0GN86G345</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>5</v>
-      </c>
-      <c r="C151" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>B0GN8RQJRG</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>3</v>
-      </c>
-      <c r="C152" t="n">
-        <v>1</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>B0GN8WW6BC</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>6</v>
-      </c>
-      <c r="C153" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" t="n">
-        <v>-6</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>B0GN94YDY2</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>3</v>
-      </c>
-      <c r="C154" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>33</v>
-      </c>
-      <c r="C155" t="n">
-        <v>31</v>
-      </c>
-      <c r="D155" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>B0GXP97CZG</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>5</v>
-      </c>
-      <c r="C156" t="n">
-        <v>1</v>
-      </c>
-      <c r="D156" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>B0GYS6CJD9</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>10</v>
-      </c>
-      <c r="C157" t="n">
-        <v>0</v>
-      </c>
-      <c r="D157" t="n">
-        <v>-10</v>
-      </c>
-      <c r="E157" t="inlineStr">
         <is>
           <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
         </is>
@@ -10257,37 +5028,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>latest</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>prior_4w_median</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>delta_pct</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -10295,78 +5041,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>sessions</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>129797</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>sessions</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>184194</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>sessions</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16742</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
+          <t>clean — Brand metric &gt; 50% drop or 2x spike vs prior 4w median</t>
         </is>
       </c>
     </row>
@@ -10493,7 +5168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10531,26 +5206,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sessions</t>
+          <t>inventory_units</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>389513</v>
+        <v>240</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -10559,26 +5234,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>amazon_gmv</t>
+          <t>inventory_units</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5372790.076271186</v>
+        <v>6000</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -10587,196 +5262,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>b2b</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sessions</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>571559</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>sessions</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>11076</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>amazon_gmv</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2779447.257966102</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>sessions</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>50423</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>240</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>b2b</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -30,6 +30,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,7 +912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,17 +2394,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DC64BD5R</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>68027.94</v>
+        <v>36851.69</v>
       </c>
       <c r="C71" t="n">
-        <v>9786.440000000001</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>-58241.5</v>
+        <v>-36851.69</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2414,17 +2415,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DC674ZNR</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>11148.3</v>
+        <v>14738.98</v>
       </c>
       <c r="C72" t="n">
-        <v>3861.86</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>-7286.44</v>
+        <v>-14738.98</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2435,17 +2436,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DJ2V3TH2</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>11606.78</v>
+        <v>11435.59</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>-11606.78</v>
+        <v>-11435.59</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2456,17 +2457,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DJ2VFZWN</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>16940.63</v>
+        <v>13550.85</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>-16940.63</v>
+        <v>-13550.85</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2477,17 +2478,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0DC64BD5R</t>
+          <t>B0DJ2XCDJ1</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>36851.69</v>
+        <v>20758.47</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>-36851.69</v>
+        <v>-20758.47</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2498,17 +2499,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0DC674ZNR</t>
+          <t>B0DJ2XHK2N</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>14738.98</v>
+        <v>172796.61</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>-14738.98</v>
+        <v>-172796.61</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2519,17 +2520,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0DJ2V3TH2</t>
+          <t>B0DJ2Y1BG6</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>11435.59</v>
+        <v>13555.08</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>-11435.59</v>
+        <v>-13555.08</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2540,17 +2541,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0DJ2VFZWN</t>
+          <t>B0DKJHSD8R</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>13550.85</v>
+        <v>54213.56</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>-13550.85</v>
+        <v>-54213.56</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2561,17 +2562,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0DJ2XCDJ1</t>
+          <t>B0DP5HM2ZR</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>20758.47</v>
+        <v>10972.03</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>-20758.47</v>
+        <v>-10972.03</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2582,17 +2583,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0DJ2XHK2N</t>
+          <t>B0DSBN63D1</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>172796.61</v>
+        <v>9192.370000000001</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>-172796.61</v>
+        <v>-9192.370000000001</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2603,17 +2604,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0DJ2Y1BG6</t>
+          <t>B0DSBQDZNV</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>13555.08</v>
+        <v>27108.47</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>-13555.08</v>
+        <v>-27108.47</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2624,17 +2625,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0DKJHSD8R</t>
+          <t>B0DSBQYVSM</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>54213.56</v>
+        <v>12283.9</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>-54213.56</v>
+        <v>-12283.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2645,17 +2646,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DSBR8G7Y</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>80765.25</v>
+        <v>12283.9</v>
       </c>
       <c r="C83" t="n">
-        <v>46883.9</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>-33881.35</v>
+        <v>-12283.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2666,17 +2667,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DSBS17RY</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>23340.68</v>
+        <v>12283.05</v>
       </c>
       <c r="C84" t="n">
-        <v>17791.53</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>-5549.15</v>
+        <v>-12283.05</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2687,17 +2688,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DSBSD26P</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>31515.3</v>
+        <v>24566.1</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>-31515.3</v>
+        <v>-24566.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2708,17 +2709,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0DP5HM2ZR</t>
+          <t>B0DSBSGK17</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>10972.03</v>
+        <v>40662.71</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>-10972.03</v>
+        <v>-40662.71</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2729,17 +2730,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0DSBN63D1</t>
+          <t>B0DT2Q1R2H</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>9192.370000000001</v>
+        <v>13555.08</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>-9192.370000000001</v>
+        <v>-13555.08</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2750,17 +2751,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0DSBQDZNV</t>
+          <t>B0DT381WY9</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27108.47</v>
+        <v>9403.389999999999</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>-27108.47</v>
+        <v>-9403.389999999999</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2771,17 +2772,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0DSBQYVSM</t>
+          <t>B0FCVBJX29</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>12283.9</v>
+        <v>11012.71</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>-12283.9</v>
+        <v>-11012.71</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2792,17 +2793,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0DSBR8G7Y</t>
+          <t>B0FCVLB3FG</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>12283.9</v>
+        <v>10165.25</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>-12283.9</v>
+        <v>-10165.25</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2813,17 +2814,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0DSBS17RY</t>
+          <t>B0FCVLFLGF</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>12283.05</v>
+        <v>7116.1</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>-12283.05</v>
+        <v>-7116.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2834,17 +2835,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0DSBSD26P</t>
+          <t>B0FCVPBY7Y</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24566.1</v>
+        <v>368491.53</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>-24566.1</v>
+        <v>-368491.53</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2855,17 +2856,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0DSBSGK17</t>
+          <t>B0FCVRKB8C</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>40662.71</v>
+        <v>12283.05</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>-40662.71</v>
+        <v>-12283.05</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2876,17 +2877,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0DT2Q1R2H</t>
+          <t>B0FFDM5QJX</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13555.08</v>
+        <v>10675.42</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>-13555.08</v>
+        <v>-10675.42</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2897,17 +2898,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0DT381WY9</t>
+          <t>B0FFHXRJNS</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>9403.389999999999</v>
+        <v>6777.97</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>-9403.389999999999</v>
+        <v>-6777.97</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2918,17 +2919,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0FCVBJX29</t>
+          <t>B0FFJ4N8BK</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>11012.71</v>
+        <v>16944.92</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>-11012.71</v>
+        <v>-16944.92</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2939,17 +2940,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0FCVLB3FG</t>
+          <t>B0FFJPKHZL</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>10165.25</v>
+        <v>15672.88</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>-10165.25</v>
+        <v>-15672.88</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2960,17 +2961,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0FCVLFLGF</t>
+          <t>B0FRVBBDM9</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>7116.1</v>
+        <v>40029.66</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>-7116.1</v>
+        <v>-40029.66</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2981,17 +2982,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0FCVPBY7Y</t>
+          <t>B0FS5QZRYB</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>368491.53</v>
+        <v>10164.41</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>-368491.53</v>
+        <v>-10164.41</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3002,17 +3003,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0FCVRKB8C</t>
+          <t>B0FTK1RVG8</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>12283.05</v>
+        <v>24396.61</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>-12283.05</v>
+        <v>-24396.61</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3023,17 +3024,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0FFDM5QJX</t>
+          <t>B0FTK7KQ1P</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>10675.42</v>
+        <v>9192.370000000001</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>-10675.42</v>
+        <v>-9192.370000000001</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3044,17 +3045,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0FFHXRJNS</t>
+          <t>B0FTML3VHG</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>6777.97</v>
+        <v>45742.37</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>-6777.97</v>
+        <v>-45742.37</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3065,17 +3066,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0FFJ4N8BK</t>
+          <t>B0FTMLYC74</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>16944.92</v>
+        <v>40659.32</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>-16944.92</v>
+        <v>-40659.32</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3086,17 +3087,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0FFJPKHZL</t>
+          <t>B0FTMM455Z</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>15672.88</v>
+        <v>80055.08</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>-15672.88</v>
+        <v>-80055.08</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3107,17 +3108,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0FRVBBDM9</t>
+          <t>B0FTMMNCK7</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>40029.66</v>
+        <v>27108.47</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>-40029.66</v>
+        <v>-27108.47</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3128,17 +3129,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0FS5QZRYB</t>
+          <t>B0FTMRC37L</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>10164.41</v>
+        <v>10165.25</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>-10164.41</v>
+        <v>-10165.25</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3149,17 +3150,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0FTK1RVG8</t>
+          <t>B0GDJPJKSG</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>24396.61</v>
+        <v>29652.54</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>-24396.61</v>
+        <v>-29652.54</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3170,17 +3171,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0FTK7KQ1P</t>
+          <t>B0GDXBGXH2</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>9192.370000000001</v>
+        <v>11436.44</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>-9192.370000000001</v>
+        <v>-11436.44</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3191,17 +3192,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0FTML3VHG</t>
+          <t>B0GF7561XM</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>45742.37</v>
+        <v>22025.42</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>-45742.37</v>
+        <v>-22025.42</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3212,17 +3213,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0FTMLYC74</t>
+          <t>B0GF785MMZ</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>40659.32</v>
+        <v>12707.63</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>-40659.32</v>
+        <v>-12707.63</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3233,17 +3234,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0FTMM455Z</t>
+          <t>B0GF7BLQ27</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>80055.08</v>
+        <v>25415.25</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>-80055.08</v>
+        <v>-25415.25</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3254,17 +3255,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0FTMMNCK7</t>
+          <t>B0GF7BR5NH</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>27108.47</v>
+        <v>22025.42</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>-27108.47</v>
+        <v>-22025.42</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3275,17 +3276,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0FTMRC37L</t>
+          <t>B0GF7GZ4K7</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>10165.25</v>
+        <v>8005.93</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>-10165.25</v>
+        <v>-8005.93</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3296,17 +3297,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0GDJPJKSG</t>
+          <t>B0GF7JSSRF</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>29652.54</v>
+        <v>36851.69</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>-29652.54</v>
+        <v>-36851.69</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3317,166 +3318,19 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0GDXBGXH2</t>
+          <t>B0GFD7N73D</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>11436.44</v>
+        <v>31347.46</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>-11436.44</v>
+        <v>-31347.46</v>
       </c>
       <c r="E115" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>B0GF7561XM</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>22025.42</v>
-      </c>
-      <c r="C116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" t="n">
-        <v>-22025.42</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>B0GF785MMZ</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>12707.63</v>
-      </c>
-      <c r="C117" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" t="n">
-        <v>-12707.63</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>B0GF7BLQ27</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>25415.25</v>
-      </c>
-      <c r="C118" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" t="n">
-        <v>-25415.25</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>B0GF7BR5NH</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>22025.42</v>
-      </c>
-      <c r="C119" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" t="n">
-        <v>-22025.42</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>B0GF7GZ4K7</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>8005.93</v>
-      </c>
-      <c r="C120" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" t="n">
-        <v>-8005.93</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>B0GF7JSSRF</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>36851.69</v>
-      </c>
-      <c r="C121" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" t="n">
-        <v>-36851.69</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>B0GFD7N73D</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>31347.46</v>
-      </c>
-      <c r="C122" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" t="n">
-        <v>-31347.46</v>
-      </c>
-      <c r="E122" t="inlineStr">
         <is>
           <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
         </is>
@@ -5106,6 +4960,34 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — AMS Trend GMV vs Sales Trend Amazon-side per brand</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -31,6 +31,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,30 +746,6 @@
       <c r="F12" t="inlineStr">
         <is>
           <t>EXTRA IN SNAPSHOT (stale rows?)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>26</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>40427</v>
-      </c>
-      <c r="D13" t="n">
-        <v>39427</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
@@ -4805,10 +4783,10 @@
         <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>179341</v>
+        <v>180341</v>
       </c>
       <c r="D2" t="n">
-        <v>179341</v>
+        <v>180341</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -4829,10 +4807,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>171380</v>
+        <v>172380</v>
       </c>
       <c r="D3" t="n">
-        <v>171380</v>
+        <v>172380</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4988,6 +4966,150 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Inventory snapshot behind latest raw week (silent ETL failure)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>lag_hours</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>data\processed\returns_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>data\processed\inventory_model_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>snapshot older than anchor by &gt;24h — ETL likely failed silently on the last cron run</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>data\processed\margin_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>data\processed\inventory_model_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>snapshot older than anchor by &gt;24h — ETL likely failed silently on the last cron run</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>data\processed\inbound_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>data\processed\inventory_model_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>snapshot older than anchor by &gt;24h — ETL likely failed silently on the last cron run</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>data\processed\reviews_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>data\processed\inventory_model_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>snapshot older than anchor by &gt;24h — ETL likely failed silently on the last cron run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5098,7 +5220,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5107,7 +5229,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>240</v>
+        <v>572</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -5126,7 +5248,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5135,7 +5257,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6000</v>
+        <v>500</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -5180,7 +5302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5436,7 +5558,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FBA74928</t>
+          <t>FBA80105</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -5450,10 +5572,24 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
+          <t>FBA74928</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DUPLICATE SKU (2× in master)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5522,7 +5658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7333,30 +7469,6 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>26</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>26295</v>
-      </c>
-      <c r="E76" t="n">
-        <v>25295</v>
-      </c>
-      <c r="F76" t="n">
-        <v>-1000</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -762,10 +762,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>15198</v>
+        <v>15309</v>
       </c>
       <c r="E13" t="n">
-        <v>15198</v>
+        <v>15309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -886,21 +886,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>amazon+1p_inventory</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_total_amazon</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>note</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sales_trend_inv</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>inv_dashboard_total</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route inventory rule consistency</t>
-        </is>
+          <t>amazon+1p_vs_ams_trend</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales_trend_vs_inv_dashboard</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -914,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1871,17 +1955,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0CR5NKB4C</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8894.92</v>
+        <v>248112.23</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>243708.84</v>
       </c>
       <c r="D46" t="n">
-        <v>-8894.92</v>
+        <v>-4403.39</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1892,17 +1976,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0CR5RR8Z6</t>
+          <t>B0CR5NKB4C</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>13639.83</v>
+        <v>8894.92</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>-13639.83</v>
+        <v>-8894.92</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1913,17 +1997,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0CRCWV9DV</t>
+          <t>B0CR5RR8Z6</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>54216.95</v>
+        <v>13639.83</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>-54216.95</v>
+        <v>-13639.83</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1934,17 +2018,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0CRD1DRXG</t>
+          <t>B0CRCWV9DV</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>37277.97</v>
+        <v>54216.95</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>-37277.97</v>
+        <v>-54216.95</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1955,17 +2039,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0CRD2CVZL</t>
+          <t>B0CRD1DRXG</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10164.41</v>
+        <v>37277.97</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>-10164.41</v>
+        <v>-37277.97</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1976,7 +2060,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0CRD3QWVJ</t>
+          <t>B0CRD2CVZL</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1997,17 +2081,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0CRD7DH79</t>
+          <t>B0CRD3QWVJ</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>9488.98</v>
+        <v>10164.41</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>-9488.98</v>
+        <v>-10164.41</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2018,17 +2102,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0CZ8ZKPJ9</t>
+          <t>B0CRD7DH79</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28464.41</v>
+        <v>9488.98</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>-28464.41</v>
+        <v>-9488.98</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2039,17 +2123,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0CZ91YKMP</t>
+          <t>B0CZ8ZKPJ9</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>8132.2</v>
+        <v>28464.41</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>-8132.2</v>
+        <v>-28464.41</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2060,17 +2144,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0D85171BL</t>
+          <t>B0CZ91YKMP</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>9316.950000000001</v>
+        <v>8132.2</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>-9316.950000000001</v>
+        <v>-8132.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2081,17 +2165,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0D854LDQM</t>
+          <t>B0D85171BL</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27110.17</v>
+        <v>9316.950000000001</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>-27110.17</v>
+        <v>-9316.950000000001</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2102,17 +2186,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0D8572WTJ</t>
+          <t>B0D854LDQM</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>13554.24</v>
+        <v>27110.17</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>-13554.24</v>
+        <v>-27110.17</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2123,17 +2207,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0D935S1B3</t>
+          <t>B0D8572WTJ</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>14233.9</v>
+        <v>13554.24</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>-14233.9</v>
+        <v>-13554.24</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2144,17 +2228,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0D9362N4Q</t>
+          <t>B0D935S1B3</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>22872.88</v>
+        <v>14233.9</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>-22872.88</v>
+        <v>-14233.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2165,17 +2249,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0D93652ZY</t>
+          <t>B0D9362N4Q</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>251583.05</v>
+        <v>22872.88</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>-251583.05</v>
+        <v>-22872.88</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2186,17 +2270,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0D936GPVL</t>
+          <t>B0D93652ZY</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>57177.97</v>
+        <v>251583.05</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>-57177.97</v>
+        <v>-251583.05</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2207,17 +2291,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0D954M6YQ</t>
+          <t>B0D936GPVL</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8005.08</v>
+        <v>57177.97</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>-8005.08</v>
+        <v>-57177.97</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2228,17 +2312,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0D955L5S7</t>
+          <t>B0D954M6YQ</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>15673.73</v>
+        <v>8005.08</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>-15673.73</v>
+        <v>-8005.08</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2249,17 +2333,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0D955NZTN</t>
+          <t>B0D955L5S7</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>8303.389999999999</v>
+        <v>15673.73</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>-8303.389999999999</v>
+        <v>-15673.73</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2270,17 +2354,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0D955YGX7</t>
+          <t>B0D955NZTN</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24910.17</v>
+        <v>8303.389999999999</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>-24910.17</v>
+        <v>-8303.389999999999</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2291,17 +2375,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0D9564Z9T</t>
+          <t>B0D955YGX7</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>8133.05</v>
+        <v>24910.17</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>-8133.05</v>
+        <v>-24910.17</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2312,17 +2396,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0D9573TBX</t>
+          <t>B0D9564Z9T</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>20759.32</v>
+        <v>8133.05</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>-20759.32</v>
+        <v>-8133.05</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2333,17 +2417,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0D9ZN5NBD</t>
+          <t>B0D9573TBX</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>7793.22</v>
+        <v>20759.32</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>-7793.22</v>
+        <v>-20759.32</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2354,17 +2438,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0DC64BD5R</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>81069.49000000001</v>
+        <v>7077.97</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>6180.51</v>
       </c>
       <c r="D69" t="n">
-        <v>-81069.49000000001</v>
+        <v>-897.46</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2375,17 +2459,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0DC674ZNR</t>
+          <t>B0D9ZN5NBD</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>51586.44</v>
+        <v>7793.22</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>-51586.44</v>
+        <v>-7793.22</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2396,17 +2480,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0DJ2V3TH2</t>
+          <t>B0DC64BD5R</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>11435.59</v>
+        <v>81069.49000000001</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>-11435.59</v>
+        <v>-81069.49000000001</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2417,17 +2501,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0DJ2VFZWN</t>
+          <t>B0DC674ZNR</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>13550.85</v>
+        <v>51586.44</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>-13550.85</v>
+        <v>-51586.44</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2438,17 +2522,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0DJ2WKCPD</t>
+          <t>B0DJ2V3TH2</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>11436.44</v>
+        <v>11435.59</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>-11436.44</v>
+        <v>-11435.59</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2459,17 +2543,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0DJ2WNH1Y</t>
+          <t>B0DJ2VFZWN</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>19487.29</v>
+        <v>13550.85</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>-19487.29</v>
+        <v>-13550.85</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2480,17 +2564,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0DJ2XHK2N</t>
+          <t>B0DJ2WKCPD</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>243945.76</v>
+        <v>11436.44</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>-243945.76</v>
+        <v>-11436.44</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2501,17 +2585,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0DJ2XNSD2</t>
+          <t>B0DJ2WNH1Y</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>16521.19</v>
+        <v>19487.29</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>-16521.19</v>
+        <v>-19487.29</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2522,17 +2606,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0DJ2XQB3P</t>
+          <t>B0DJ2XHK2N</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>7116.1</v>
+        <v>243945.76</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>-7116.1</v>
+        <v>-243945.76</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2543,17 +2627,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0DKJHSD8R</t>
+          <t>B0DJ2XNSD2</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>81320.34</v>
+        <v>16521.19</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>-81320.34</v>
+        <v>-16521.19</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2564,17 +2648,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0DP5J7VF3</t>
+          <t>B0DJ2XQB3P</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>9744.07</v>
+        <v>7116.1</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>-9744.07</v>
+        <v>-7116.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2585,17 +2669,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0DP5JYG31</t>
+          <t>B0DKJHSD8R</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>9743.219999999999</v>
+        <v>81320.34</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>-9743.219999999999</v>
+        <v>-81320.34</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2606,17 +2690,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0DSBPPPJ9</t>
+          <t>B0DP5J7VF3</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>10972.03</v>
+        <v>9744.07</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>-10972.03</v>
+        <v>-9744.07</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2627,17 +2711,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0DSBQCZTK</t>
+          <t>B0DP5JYG31</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>40667.8</v>
+        <v>9743.219999999999</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>-40667.8</v>
+        <v>-9743.219999999999</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2648,17 +2732,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0DSBQDZNV</t>
+          <t>B0DSBPPPJ9</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>13554.24</v>
+        <v>10972.03</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>-13554.24</v>
+        <v>-10972.03</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2669,17 +2753,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0DSBQN2B9</t>
+          <t>B0DSBQCZTK</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>13554.24</v>
+        <v>40667.8</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>-13554.24</v>
+        <v>-40667.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2690,17 +2774,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0DSBQWH32</t>
+          <t>B0DSBQDZNV</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>10971.19</v>
+        <v>13554.24</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>-10971.19</v>
+        <v>-13554.24</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2711,17 +2795,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0DSBQYVSM</t>
+          <t>B0DSBQN2B9</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>12283.9</v>
+        <v>13554.24</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>-12283.9</v>
+        <v>-13554.24</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2732,17 +2816,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0DSBRQNM8</t>
+          <t>B0DSBQWH32</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>21944.07</v>
+        <v>10971.19</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>-21944.07</v>
+        <v>-10971.19</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2753,17 +2837,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0DSBRWZ8N</t>
+          <t>B0DSBQYVSM</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>22023.73</v>
+        <v>12283.9</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>-22023.73</v>
+        <v>-12283.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2774,17 +2858,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0DSBSD26P</t>
+          <t>B0DSBRQNM8</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>36849.15</v>
+        <v>21944.07</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>-36849.15</v>
+        <v>-21944.07</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2795,17 +2879,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0DSBSGK17</t>
+          <t>B0DSBRWZ8N</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>40662.71</v>
+        <v>22023.73</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>-40662.71</v>
+        <v>-22023.73</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2816,17 +2900,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0DT381WY9</t>
+          <t>B0DSBSD26P</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37613.56</v>
+        <v>36849.15</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>-37613.56</v>
+        <v>-36849.15</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2837,17 +2921,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0FCVFDZP7</t>
+          <t>B0DSBSGK17</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>12283.9</v>
+        <v>40662.71</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>-12283.9</v>
+        <v>-40662.71</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2858,17 +2942,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0FCVHPY4B</t>
+          <t>B0DT381WY9</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>14232.2</v>
+        <v>37613.56</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>-14232.2</v>
+        <v>-37613.56</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2879,17 +2963,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0FCVKH4TS</t>
+          <t>B0FCVFDZP7</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>9488.98</v>
+        <v>12283.9</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>-9488.98</v>
+        <v>-12283.9</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2900,17 +2984,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0FCVPBY7Y</t>
+          <t>B0FCVHPY4B</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>221094.92</v>
+        <v>14232.2</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>-221094.92</v>
+        <v>-14232.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2921,17 +3005,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0FCVRKB8C</t>
+          <t>B0FCVKH4TS</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>36849.15</v>
+        <v>9488.98</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>-36849.15</v>
+        <v>-9488.98</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2942,17 +3026,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0FFDJHKR5</t>
+          <t>B0FCVPBY7Y</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>9785.59</v>
+        <v>221094.92</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>-9785.59</v>
+        <v>-221094.92</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2963,17 +3047,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0FFDJNB8T</t>
+          <t>B0FCVRKB8C</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>16940.68</v>
+        <v>36849.15</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>-16940.68</v>
+        <v>-36849.15</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2984,17 +3068,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0FFDSN4S1</t>
+          <t>B0FFDJHKR5</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>10674.58</v>
+        <v>9785.59</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>-10674.58</v>
+        <v>-9785.59</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3005,17 +3089,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0FFJ4N8BK</t>
+          <t>B0FFDJNB8T</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>16944.92</v>
+        <v>16940.68</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>-16944.92</v>
+        <v>-16940.68</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3026,17 +3110,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0FFJQBHGH</t>
+          <t>B0FFDSN4S1</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>16944.92</v>
+        <v>10674.58</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>-16944.92</v>
+        <v>-10674.58</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3047,17 +3131,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0FJ2RND61</t>
+          <t>B0FFJ4N8BK</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>16944.07</v>
+        <v>16944.92</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>-16944.07</v>
+        <v>-16944.92</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3068,17 +3152,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0FRVBBDM9</t>
+          <t>B0FFJQBHGH</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>40029.66</v>
+        <v>16944.92</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>-40029.66</v>
+        <v>-16944.92</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3089,17 +3173,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0FRVG8SR6</t>
+          <t>B0FJ2RND61</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>11861.86</v>
+        <v>16944.07</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>-11861.86</v>
+        <v>-16944.07</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3110,17 +3194,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0FRVZ29NP</t>
+          <t>B0FRVBBDM9</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>30498.31</v>
+        <v>40029.66</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>-30498.31</v>
+        <v>-40029.66</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3131,17 +3215,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0FS5QZRYB</t>
+          <t>B0FRVG8SR6</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>10164.41</v>
+        <v>11861.86</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>-10164.41</v>
+        <v>-11861.86</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3152,17 +3236,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0FTK1RVG8</t>
+          <t>B0FRVZ29NP</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>48793.22</v>
+        <v>30498.31</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>-48793.22</v>
+        <v>-30498.31</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3173,17 +3257,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0FTL6QH21</t>
+          <t>B0FS5QZRYB</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>16944.92</v>
+        <v>10164.41</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>-16944.92</v>
+        <v>-10164.41</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3194,17 +3278,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0FTL71V28</t>
+          <t>B0FTK1RVG8</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>12283.9</v>
+        <v>48793.22</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>-12283.9</v>
+        <v>-48793.22</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3215,17 +3299,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0FTML3VHG</t>
+          <t>B0FTL6QH21</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>34306.78</v>
+        <v>16944.92</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>-34306.78</v>
+        <v>-16944.92</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3236,17 +3320,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0FTMLYC74</t>
+          <t>B0FTL71V28</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>101644.07</v>
+        <v>12283.9</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>-101644.07</v>
+        <v>-12283.9</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3257,17 +3341,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0FTMM455Z</t>
+          <t>B0FTML3VHG</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>160110.17</v>
+        <v>34306.78</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>-160110.17</v>
+        <v>-34306.78</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3278,17 +3362,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0FTMMHDNH</t>
+          <t>B0FTMLYC74</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>20758.47</v>
+        <v>101644.07</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>-20758.47</v>
+        <v>-101644.07</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3299,17 +3383,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0FTMMNCK7</t>
+          <t>B0FTMM455Z</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>13554.24</v>
+        <v>160110.17</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>-13554.24</v>
+        <v>-160110.17</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3320,17 +3404,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0FTMRC37L</t>
+          <t>B0FTMMHDNH</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>20330.51</v>
+        <v>20758.47</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>-20330.51</v>
+        <v>-20758.47</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3341,17 +3425,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0GDJPJKSG</t>
+          <t>B0FTMMNCK7</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>14825.42</v>
+        <v>13554.24</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>-14825.42</v>
+        <v>-13554.24</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3362,17 +3446,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0GF715X4M</t>
+          <t>B0FTMRC37L</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>27110.17</v>
+        <v>20330.51</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>-27110.17</v>
+        <v>-20330.51</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3383,17 +3467,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0GF7561XM</t>
+          <t>B0GD8JSPB1</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>11012.71</v>
+        <v>28810.17</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>21607.63</v>
       </c>
       <c r="D118" t="n">
-        <v>-11012.71</v>
+        <v>-7202.54</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3404,17 +3488,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0GF785MMZ</t>
+          <t>B0GDJPJKSG</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>12707.63</v>
+        <v>14825.42</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>-12707.63</v>
+        <v>-14825.42</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3425,17 +3509,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0GF7BLQ27</t>
+          <t>B0GF715X4M</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>25415.25</v>
+        <v>27110.17</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>-25415.25</v>
+        <v>-27110.17</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3446,7 +3530,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0GF7BR5NH</t>
+          <t>B0GF7561XM</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3467,17 +3551,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0GF7GZ4K7</t>
+          <t>B0GF785MMZ</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>8005.93</v>
+        <v>12707.63</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>-8005.93</v>
+        <v>-12707.63</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -3488,19 +3572,82 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>B0GF7BLQ27</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>25415.25</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-25415.25</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>B0GF7BR5NH</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>11012.71</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-11012.71</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>B0GF7GZ4K7</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>8005.93</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-8005.93</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
           <t>B0GF7JSSRF</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="B126" t="n">
         <v>12283.9</v>
       </c>
-      <c r="C123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" t="n">
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
         <v>-12283.9</v>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
         </is>
@@ -3517,12 +3664,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_file_spend</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_spend</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -3530,7 +3697,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route ads rule consistency</t>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3726,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>file_sessions</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_sessions</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -3558,7 +3759,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route sessions consistency</t>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -4832,12 +5047,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>snap_total_sales</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>am1p_route_sales</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -4845,7 +5080,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route per-brand totals consistency</t>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -4961,17 +5210,17 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>182422</v>
+        <v>180954</v>
       </c>
       <c r="D2" t="n">
-        <v>182422</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -4985,17 +5234,17 @@
         <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>174440</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>174440</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -5038,20 +5287,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>data\processed\weekly_sales_snapshot.csv</t>
+          <t>data\ams_weekly_data\processed_ads\business_ads_joined.csv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>data\ams_weekly_data\ams_weekly_fact\ams_weekly_fact.csv</t>
+          <t>data\ams_weekly_data\ams_weekly_fact\ams_weekly_fact_with_category.csv</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1104.6</v>
+        <v>4934.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>weekly_sales_snapshot → ams_weekly_fact (biz_ads_weekly_etl needs re-run)</t>
+          <t>business_ads_joined → ams_weekly_fact_with_category (step5 needs re-run)</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5316,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>345.3</v>
+        <v>251527.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5159,13 +5408,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1702326</v>
+        <v>1719322</v>
       </c>
       <c r="D3" t="n">
         <v>751045</v>
       </c>
       <c r="E3" t="n">
-        <v>126.7</v>
+        <v>128.9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -5240,12 +5489,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sales_trend_amz_side</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_gmv</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -5253,7 +5522,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — AMS Trend GMV vs Sales Trend Amazon-side per brand</t>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4371063.73</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4359457.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-11605.93</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3003729.73</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3002832.27</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-897.46</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5324,18 +5628,78 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>data\processed\returns_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>data\processed\inventory_model_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>snapshot older than anchor by &gt;24h — ETL likely failed silently on the last cron run</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>data\processed\margin_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>data\processed\inventory_model_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>snapshot older than anchor by &gt;24h — ETL likely failed silently on the last cron run</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>data\processed\inbound_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>data\processed\inventory_model_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>snapshot older than anchor by &gt;24h — ETL likely failed silently on the last cron run</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>data\processed\reviews_snapshot.csv</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>data\processed\inventory_model_snapshot.csv</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>185.1</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C5" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>snapshot older than anchor by &gt;24h — ETL likely failed silently on the last cron run</t>
         </is>
@@ -5352,12 +5716,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>week_num</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -5365,7 +5749,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Never-Zero column regression</t>
+          <t>ams_trend.inventory_snapshot (load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -7779,10 +8179,10 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>3649</v>
+        <v>3631</v>
       </c>
       <c r="F76" t="n">
-        <v>3649</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="77">
@@ -7803,10 +8203,10 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>6622</v>
+        <v>6583</v>
       </c>
       <c r="F77" t="n">
-        <v>6622</v>
+        <v>6583</v>
       </c>
     </row>
     <row r="78">
@@ -7827,10 +8227,10 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>9662</v>
+        <v>9798</v>
       </c>
       <c r="F78" t="n">
-        <v>9662</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="79">
@@ -7875,10 +8275,10 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>1433</v>
+        <v>1426</v>
       </c>
       <c r="F80" t="n">
-        <v>1433</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="81">

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -5210,7 +5210,7 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>180954</v>
+        <v>183173</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>251527.7</v>
+        <v>253831.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>82.3</v>
+        <v>83</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -33,6 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5259,7 +5260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5287,38 +5288,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>data\ams_weekly_data\processed_ads\business_ads_joined.csv</t>
+          <t>data\processed\inventory_model_snapshot.csv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>data\ams_weekly_data\ams_weekly_fact\ams_weekly_fact_with_category.csv</t>
+          <t>data\processed\inventory_ams_snapshot.csv</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4934.1</v>
+        <v>253831.6</v>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>business_ads_joined → ams_weekly_fact_with_category (step5 needs re-run)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>data\processed\inventory_model_snapshot.csv</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>data\processed\inventory_ams_snapshot.csv</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>253831.6</v>
-      </c>
-      <c r="D3" t="inlineStr">
         <is>
           <t>inventory_model_snapshot → inventory_ams_snapshot (inv_snap needs re-run)</t>
         </is>
@@ -5335,7 +5316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5373,50 +5354,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sessions</t>
+          <t>attributed</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>129946</v>
+        <v>1719322</v>
       </c>
       <c r="D2" t="n">
-        <v>316756</v>
+        <v>751045</v>
       </c>
       <c r="E2" t="n">
-        <v>-59</v>
+        <v>128.9</v>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1719322</v>
-      </c>
-      <c r="D3" t="n">
-        <v>751045</v>
-      </c>
-      <c r="E3" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="F3" t="inlineStr">
         <is>
           <t>SPIKE &gt; 2x vs prior 4-week median</t>
         </is>
@@ -5710,6 +5665,1652 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sales_trend_amz_side</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_gmv</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>delta_pct</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3095009.71</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-3095009.71</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2392739.69</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-2392739.69</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>324781.32</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-324781.32</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1906527.52</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1906527.52</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2654996.45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2654996.45</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1396572.19</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1396572.19</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>346045.54</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-346045.54</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1115446.59</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1115446.59</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3119828.81</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-3119828.81</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1608376.27</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1608376.27</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>314639.94</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-314639.94</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1136712.62</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1136712.62</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3039578.87</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-3039578.87</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1577064.99</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1577064.99</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>252253.44</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-252253.44</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1072173.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1072173.2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3033347.93</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-3033347.93</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1410246.25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1410246.25</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>203072.94</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-203072.94</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>942950.09</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-942950.09</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2957495.02</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-2957495.02</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1467359.63</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1467359.63</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>184894.03</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-184894.03</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1185369.31</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1185369.31</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3066258.52</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3066258.52</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1643099.86</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1643099.86</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>110584.75</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-110584.75</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>914785.01</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-914785.01</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3097839.36</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-3097839.36</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2190479.57</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-2190479.57</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>87927.05</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-87927.05</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>667998.22</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-667998.22</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2904810.42</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-2904810.42</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1929190.89</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1929190.89</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>114738.08</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-114738.08</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>555963.54</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-555963.54</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3225192.62</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-3225192.62</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1573750.55</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-1573750.55</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>161457.56</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-161457.56</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>784099.59</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-784099.59</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3058255.43</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-3058255.43</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1694388.76</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-1694388.76</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>114756.74</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-114756.74</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>663401.58</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-663401.58</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2511216.45</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-2511216.45</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1917524.41</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-1917524.41</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>151414.35</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-151414.35</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>494952.2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-494952.2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>470608.43</v>
+      </c>
+      <c r="D50" t="n">
+        <v>386716.9</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-83891.53</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-17.83</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>667942.12</v>
+      </c>
+      <c r="D51" t="n">
+        <v>584995.51</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-82946.61</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-12.42</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>713759.26</v>
+      </c>
+      <c r="D52" t="n">
+        <v>690287.23</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-23472.03</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1077787.08</v>
+      </c>
+      <c r="D53" t="n">
+        <v>976121.8199999999</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-101665.26</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-9.43</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>911351.88</v>
+      </c>
+      <c r="D54" t="n">
+        <v>749514.71</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-161837.17</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-17.76</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>W22</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>888714.46</v>
+      </c>
+      <c r="D55" t="n">
+        <v>823641.58</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-65072.88</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-7.32</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>W23</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1135238.81</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1078365.93</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-56872.88</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,39 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,13 +43,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -60,7 +63,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -68,12 +71,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,32 +455,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2769,32 +2781,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -2839,20 +2851,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>raw_units</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>snap_units</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>clean — Sales raw vs snapshot (per brand×wk)</t>
+      <c r="A2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2042</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1880</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-162</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ROWS LOST (ETL drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>170</v>
+      </c>
+      <c r="D3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ROWS LOST (ETL drop)</t>
         </is>
       </c>
     </row>
@@ -2867,21 +2945,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>amazon+1p_inventory</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_total_amazon</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sales_trend_inv</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>inv_dashboard_total</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route inventory rule consistency</t>
-        </is>
+          <t>amazon+1p_vs_ams_trend</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales_trend_vs_inv_dashboard</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2895,31 +3057,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sales_trend_amzn+1p_gmv</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ams_trend_gmv</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>delta_rs</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -3348,17 +3510,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B01KNMEVDG</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6607.63</v>
+        <v>53868.48</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>54156.62</v>
       </c>
       <c r="D22" t="n">
-        <v>-6607.63</v>
+        <v>288.14</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -3369,17 +3531,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B06VV5QB6Q</t>
+          <t>B01KNMEVDG</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>40233.05</v>
+        <v>6607.63</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-40233.05</v>
+        <v>-6607.63</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -3390,17 +3552,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B078Y2PJL4</t>
+          <t>B06VV5QB6Q</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>97586.44</v>
+        <v>40233.05</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-97586.44</v>
+        <v>-40233.05</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -3411,17 +3573,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B079XB5RXH</t>
+          <t>B078Y2PJL4</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62272.88</v>
+        <v>97586.44</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-62272.88</v>
+        <v>-97586.44</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -3432,17 +3594,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B07CSNG8XL</t>
+          <t>B079XB5RXH</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>64352.54</v>
+        <v>62272.88</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-64352.54</v>
+        <v>-62272.88</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3453,17 +3615,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B07M7P7VLX</t>
+          <t>B07CSNG8XL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>41171.19</v>
+        <v>64352.54</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-41171.19</v>
+        <v>-64352.54</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -3474,17 +3636,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B07MFZ6S2Q</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24566.1</v>
+        <v>49604.24</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>51891.52</v>
       </c>
       <c r="D28" t="n">
-        <v>-24566.1</v>
+        <v>2287.28</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -3495,17 +3657,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B07MM5MH6F</t>
+          <t>B07M7P7VLX</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>33035.59</v>
+        <v>41171.19</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-33035.59</v>
+        <v>-41171.19</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -3516,17 +3678,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B07RZ1R1HJ</t>
+          <t>B07MFZ6S2Q</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>33035.59</v>
+        <v>24566.1</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-33035.59</v>
+        <v>-24566.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -3537,17 +3699,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B07T2XYGR5</t>
+          <t>B07MM5MH6F</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20334.75</v>
+        <v>33035.59</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-20334.75</v>
+        <v>-33035.59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -3558,17 +3720,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B07T3ZPD9X</t>
+          <t>B07RZ1R1HJ</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9192.370000000001</v>
+        <v>33035.59</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-9192.370000000001</v>
+        <v>-33035.59</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3579,17 +3741,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B07T53T1KV</t>
+          <t>B07T2XYGR5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27538.14</v>
+        <v>20334.75</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-27538.14</v>
+        <v>-20334.75</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3600,17 +3762,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B07T62YVHY</t>
+          <t>B07T3ZPD9X</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17791.53</v>
+        <v>9192.370000000001</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-17791.53</v>
+        <v>-9192.370000000001</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -3621,17 +3783,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0846Q1JT5</t>
+          <t>B07T53T1KV</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>13130.51</v>
+        <v>27538.14</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-13130.51</v>
+        <v>-27538.14</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -3642,17 +3804,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B08QTW81S9</t>
+          <t>B07T62YVHY</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>11434.75</v>
+        <v>17791.53</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>-11434.75</v>
+        <v>-17791.53</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -3663,17 +3825,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B08QVCPDVT</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>24566.1</v>
+        <v>9910.16</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>11604.22</v>
       </c>
       <c r="D37" t="n">
-        <v>-24566.1</v>
+        <v>1694.06</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3684,17 +3846,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B08XBYKWW3</t>
+          <t>B0846Q1JT5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>13640.68</v>
+        <v>13130.51</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-13640.68</v>
+        <v>-13130.51</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3705,17 +3867,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B09BBK2LV4</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>23724.58</v>
+        <v>29879.67</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>37504.26</v>
       </c>
       <c r="D39" t="n">
-        <v>-23724.58</v>
+        <v>7624.59</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -3726,17 +3888,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B09NC2NFR9</t>
+          <t>B08QTW81S9</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20328.81</v>
+        <v>11434.75</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>-20328.81</v>
+        <v>-11434.75</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -3747,17 +3909,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B09SHQSHBF</t>
+          <t>B08QVCPDVT</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27279.66</v>
+        <v>24566.1</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>-27279.66</v>
+        <v>-24566.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -3768,17 +3930,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0B75LLWV6</t>
+          <t>B08XBYKWW3</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10166.95</v>
+        <v>13640.68</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>-10166.95</v>
+        <v>-13640.68</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3789,17 +3951,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0BFXL8ZP9</t>
+          <t>B09BBK2LV4</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>11012.71</v>
+        <v>23724.58</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>-11012.71</v>
+        <v>-23724.58</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -3810,17 +3972,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0BQZH3LGP</t>
+          <t>B09NC2NFR9</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8895.76</v>
+        <v>20328.81</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>-8895.76</v>
+        <v>-20328.81</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3831,17 +3993,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0C77PPS9S</t>
+          <t>B09SHQSHBF</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10164.41</v>
+        <v>27279.66</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>-10164.41</v>
+        <v>-27279.66</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3852,17 +4014,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0CHXGWVZJ</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>44476.27</v>
+        <v>418102.9</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>460069.93</v>
       </c>
       <c r="D46" t="n">
-        <v>-44476.27</v>
+        <v>41967.03</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3873,17 +4035,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0CHXTV16D</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>8894.92</v>
+        <v>34057.92</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>37429.11</v>
       </c>
       <c r="D47" t="n">
-        <v>-8894.92</v>
+        <v>3371.19</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3894,17 +4056,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0CJ6ZHK1S</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>13554.24</v>
+        <v>7964.4</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>11946.6</v>
       </c>
       <c r="D48" t="n">
-        <v>-13554.24</v>
+        <v>3982.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3915,17 +4077,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0CJ6ZW8F6</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10164.41</v>
+        <v>46923.75</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>52261.89</v>
       </c>
       <c r="D49" t="n">
-        <v>-10164.41</v>
+        <v>5338.14</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3936,17 +4098,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0CR5NKB4C</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8894.92</v>
+        <v>9705.959999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>14025.47</v>
       </c>
       <c r="D50" t="n">
-        <v>-8894.92</v>
+        <v>4319.51</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3957,17 +4119,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0CRCWV9DV</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>27108.47</v>
+        <v>5294.07</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>7115.26</v>
       </c>
       <c r="D51" t="n">
-        <v>-27108.47</v>
+        <v>1821.19</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3978,17 +4140,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0CRCYMKY8</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10972.03</v>
+        <v>5966.96</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>6833.9</v>
       </c>
       <c r="D52" t="n">
-        <v>-10972.03</v>
+        <v>866.9400000000001</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3999,17 +4161,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0CRD3QWVJ</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10164.41</v>
+        <v>8471.200000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>12706.8</v>
       </c>
       <c r="D53" t="n">
-        <v>-10164.41</v>
+        <v>4235.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -4020,17 +4182,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0CYMWQCKL</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>12283.05</v>
+        <v>42395.73</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>45784.71</v>
       </c>
       <c r="D54" t="n">
-        <v>-12283.05</v>
+        <v>3388.98</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -4041,17 +4203,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0CZ8ZKPJ9</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>37952.54</v>
+        <v>27361.9</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>29479.7</v>
       </c>
       <c r="D55" t="n">
-        <v>-37952.54</v>
+        <v>2117.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -4062,17 +4224,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0CZ9HTWNC</t>
+          <t>B0B75LLWV6</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10970.34</v>
+        <v>10166.95</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>-10970.34</v>
+        <v>-10166.95</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -4083,17 +4245,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0D84YD59Y</t>
+          <t>B0BFXL8ZP9</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10588.14</v>
+        <v>11012.71</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>-10588.14</v>
+        <v>-11012.71</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -4104,17 +4266,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0D84YY632</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>13554.24</v>
+        <v>23322.04</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>26072.04</v>
       </c>
       <c r="D58" t="n">
-        <v>-13554.24</v>
+        <v>2750</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -4125,17 +4287,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0D85171BL</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>9316.950000000001</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1863.56</v>
       </c>
       <c r="D59" t="n">
-        <v>-9316.950000000001</v>
+        <v>1863.56</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -4146,17 +4308,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0D853Y52R</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>13553.39</v>
+        <v>54740.76</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>59009.4</v>
       </c>
       <c r="D60" t="n">
-        <v>-13553.39</v>
+        <v>4268.64</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -4167,17 +4329,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0D854LDQM</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>67775.42</v>
+        <v>524966.73</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>609695.53</v>
       </c>
       <c r="D61" t="n">
-        <v>-67775.42</v>
+        <v>84728.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -4188,17 +4350,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0D8572WTJ</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>27108.47</v>
+        <v>3219.49</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>9997.450000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>-27108.47</v>
+        <v>6777.96</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -4209,17 +4371,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0D935VW9J</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>16014.41</v>
+        <v>11446.59</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>12547.44</v>
       </c>
       <c r="D63" t="n">
-        <v>-16014.41</v>
+        <v>1100.85</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -4230,17 +4392,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0D9362N4Q</t>
+          <t>B0BQZH3LGP</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>34309.32</v>
+        <v>8895.76</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>-34309.32</v>
+        <v>-8895.76</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -4251,17 +4413,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0D9363BB2</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>15672.88</v>
+        <v>6183.91</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>8301.709999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>-15672.88</v>
+        <v>2117.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -4272,17 +4434,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0D93652ZY</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>194405.08</v>
+        <v>22991.52</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>26549.14</v>
       </c>
       <c r="D66" t="n">
-        <v>-194405.08</v>
+        <v>3557.62</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -4293,17 +4455,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0D9369MTM</t>
+          <t>B0C77PPS9S</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>20328.81</v>
+        <v>10164.41</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>-20328.81</v>
+        <v>-10164.41</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -4314,17 +4476,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0D936GPVL</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>80049.14999999999</v>
+        <v>10755.9</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>12110.98</v>
       </c>
       <c r="D68" t="n">
-        <v>-80049.14999999999</v>
+        <v>1355.08</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -4335,17 +4497,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0D936YHDH</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>11861.02</v>
+        <v>100531.4</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>114053.42</v>
       </c>
       <c r="D69" t="n">
-        <v>-11861.02</v>
+        <v>13522.02</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -4356,17 +4518,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0D955L5S7</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>15672.88</v>
+        <v>30337.27</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>27202.52</v>
       </c>
       <c r="D70" t="n">
-        <v>-15672.88</v>
+        <v>-3134.75</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -4377,17 +4539,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0D955NZTN</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>16606.78</v>
+        <v>125435.88</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>152059.59</v>
       </c>
       <c r="D71" t="n">
-        <v>-16606.78</v>
+        <v>26623.71</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -4398,17 +4560,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0D955YGX7</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>12455.08</v>
+        <v>5316.11</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>6671.19</v>
       </c>
       <c r="D72" t="n">
-        <v>-12455.08</v>
+        <v>1355.08</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -4419,17 +4581,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0D9564Z9T</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>24399.15</v>
+        <v>634.75</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>1311.87</v>
       </c>
       <c r="D73" t="n">
-        <v>-24399.15</v>
+        <v>677.12</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -4440,17 +4602,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0D9573TBX</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>41518.64</v>
+        <v>41913.6</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>50384.8</v>
       </c>
       <c r="D74" t="n">
-        <v>-41518.64</v>
+        <v>8471.200000000001</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -4461,17 +4623,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0D9574DPS</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>27444.92</v>
+        <v>20974.57</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>23300.85</v>
       </c>
       <c r="D75" t="n">
-        <v>-27444.92</v>
+        <v>2326.28</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -4482,17 +4644,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0DC64BD5R</t>
+          <t>B0CHXGWVZJ</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>7369.49</v>
+        <v>44476.27</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>-7369.49</v>
+        <v>-44476.27</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -4503,17 +4665,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0DC674ZNR</t>
+          <t>B0CHXTV16D</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>44217.8</v>
+        <v>8894.92</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>-44217.8</v>
+        <v>-8894.92</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -4524,17 +4686,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0DJ2V3TH2</t>
+          <t>B0CJ6ZHK1S</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>11435.59</v>
+        <v>13554.24</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>-11435.59</v>
+        <v>-13554.24</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -4545,17 +4707,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0DJ2VFZWN</t>
+          <t>B0CJ6ZW8F6</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>20326.27</v>
+        <v>10164.41</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>-20326.27</v>
+        <v>-10164.41</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4566,17 +4728,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0DJ2WKCPD</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>34309.32</v>
+        <v>6305.93</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>9183.889999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>-34309.32</v>
+        <v>2877.96</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4587,17 +4749,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0DJ2WP1M5</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>13894.92</v>
+        <v>53939.84</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>56566.11</v>
       </c>
       <c r="D81" t="n">
-        <v>-13894.92</v>
+        <v>2626.27</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -4608,17 +4770,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0DJ2XHK2N</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>264274.58</v>
+        <v>27932.14</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>31931.29</v>
       </c>
       <c r="D82" t="n">
-        <v>-264274.58</v>
+        <v>3999.15</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4629,17 +4791,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0DJ2Y1BG6</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>13554.24</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>3982.2</v>
       </c>
       <c r="D83" t="n">
-        <v>-13554.24</v>
+        <v>3982.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4650,17 +4812,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0DKJHSD8R</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>162640.68</v>
+        <v>1439.83</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>4319.51</v>
       </c>
       <c r="D84" t="n">
-        <v>-162640.68</v>
+        <v>2879.68</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4671,17 +4833,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0DSBN62LR</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>27108.47</v>
+        <v>5421.19</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>7284.75</v>
       </c>
       <c r="D85" t="n">
-        <v>-27108.47</v>
+        <v>1863.56</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4692,17 +4854,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0DSBPCW8R</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>10588.98</v>
+        <v>29309.3</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>34391.51</v>
       </c>
       <c r="D86" t="n">
-        <v>-10588.98</v>
+        <v>5082.21</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4713,17 +4875,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0DSBPPPJ9</t>
+          <t>B0CR5NKB4C</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>10972.03</v>
+        <v>8894.92</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>-10972.03</v>
+        <v>-8894.92</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4734,17 +4896,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0DSBQCZTK</t>
+          <t>B0CRCWV9DV</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>81335.59</v>
+        <v>27108.47</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>-81335.59</v>
+        <v>-27108.47</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4755,17 +4917,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0DSBQDZNV</t>
+          <t>B0CRCYMKY8</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>54216.95</v>
+        <v>10972.03</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>-54216.95</v>
+        <v>-10972.03</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4776,17 +4938,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0DSBRQNM8</t>
+          <t>B0CRD3QWVJ</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>21944.07</v>
+        <v>10164.41</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>-21944.07</v>
+        <v>-10164.41</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4797,17 +4959,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0DSBRWZ8N</t>
+          <t>B0CYMWQCKL</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>22023.73</v>
+        <v>12283.05</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>-22023.73</v>
+        <v>-12283.05</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4818,17 +4980,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0DSBS17RY</t>
+          <t>B0CZ8ZKPJ9</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>36849.15</v>
+        <v>37952.54</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>-36849.15</v>
+        <v>-37952.54</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4839,17 +5001,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0DSBSD26P</t>
+          <t>B0CZ9HTWNC</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>85981.36</v>
+        <v>10970.34</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>-85981.36</v>
+        <v>-10970.34</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4860,17 +5022,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0DSBSGK17</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>67771.19</v>
+        <v>5845.76</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>8768.639999999999</v>
       </c>
       <c r="D94" t="n">
-        <v>-67771.19</v>
+        <v>2922.88</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -4881,17 +5043,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0DT2KTXK3</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>14234.75</v>
+        <v>70748.25999999999</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>82609.28999999999</v>
       </c>
       <c r="D95" t="n">
-        <v>-14234.75</v>
+        <v>11861.03</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -4902,17 +5064,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0DT2ZQV18</t>
+          <t>B0D84YD59Y</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>9404.24</v>
+        <v>10588.14</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>-9404.24</v>
+        <v>-10588.14</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4923,17 +5085,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0DT381WY9</t>
+          <t>B0D84YY632</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>9403.389999999999</v>
+        <v>13554.24</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>-9403.389999999999</v>
+        <v>-13554.24</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4944,17 +5106,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0FCVBY986</t>
+          <t>B0D85171BL</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>11435.59</v>
+        <v>9316.950000000001</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>-11435.59</v>
+        <v>-9316.950000000001</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -4965,17 +5127,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0FCVHPY4B</t>
+          <t>B0D853Y52R</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>7116.1</v>
+        <v>13553.39</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>-7116.1</v>
+        <v>-13553.39</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -4986,17 +5148,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0FCVLFLGF</t>
+          <t>B0D854LDQM</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>14232.2</v>
+        <v>67775.42</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>-14232.2</v>
+        <v>-67775.42</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -5007,17 +5169,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0FCVPBY7Y</t>
+          <t>B0D8572WTJ</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>294793.22</v>
+        <v>27108.47</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>-294793.22</v>
+        <v>-27108.47</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -5028,17 +5190,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0FFDJNB8T</t>
+          <t>B0D935VW9J</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>8471.190000000001</v>
+        <v>16014.41</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>-8471.190000000001</v>
+        <v>-16014.41</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -5049,17 +5211,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0FFDM5QJX</t>
+          <t>B0D9362N4Q</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>10675.42</v>
+        <v>34309.32</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>-10675.42</v>
+        <v>-34309.32</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -5070,17 +5232,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0FFHXRJNS</t>
+          <t>B0D9363BB2</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>6777.97</v>
+        <v>15672.88</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>-6777.97</v>
+        <v>-15672.88</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -5091,17 +5253,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0FFJJM7DS</t>
+          <t>B0D93652ZY</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>15672.88</v>
+        <v>194405.08</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>-15672.88</v>
+        <v>-194405.08</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -5112,17 +5274,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0FJ2RND61</t>
+          <t>B0D9369MTM</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>33888.14</v>
+        <v>20328.81</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>-33888.14</v>
+        <v>-20328.81</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -5133,17 +5295,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0FJ2SSSZR</t>
+          <t>B0D936GPVL</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>18977.97</v>
+        <v>80049.14999999999</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>-18977.97</v>
+        <v>-80049.14999999999</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5154,17 +5316,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0FKBV3N4Y</t>
+          <t>B0D936YHDH</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>17368.64</v>
+        <v>11861.02</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>-17368.64</v>
+        <v>-11861.02</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5175,17 +5337,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0FQ8K147H</t>
+          <t>B0D955L5S7</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>13641.53</v>
+        <v>15672.88</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>-13641.53</v>
+        <v>-15672.88</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5196,17 +5358,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0FRVBBDM9</t>
+          <t>B0D955NZTN</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>32023.73</v>
+        <v>16606.78</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>-32023.73</v>
+        <v>-16606.78</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -5217,17 +5379,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0FS5QZRYB</t>
+          <t>B0D955YGX7</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>30493.22</v>
+        <v>12455.08</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>-30493.22</v>
+        <v>-12455.08</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5238,17 +5400,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0FTK1RVG8</t>
+          <t>B0D9564Z9T</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>16264.41</v>
+        <v>24399.15</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>-16264.41</v>
+        <v>-24399.15</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5259,17 +5421,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0FTK7KQ1P</t>
+          <t>B0D9573TBX</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>9192.370000000001</v>
+        <v>41518.64</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>-9192.370000000001</v>
+        <v>-41518.64</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -5280,17 +5442,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0FTL6QH21</t>
+          <t>B0D9574DPS</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>16944.92</v>
+        <v>27444.92</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>-16944.92</v>
+        <v>-27444.92</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -5301,17 +5463,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0FTML3VHG</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>34306.78</v>
+        <v>207569.26</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>39519.49</v>
       </c>
       <c r="D115" t="n">
-        <v>-34306.78</v>
+        <v>-168049.77</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -5322,17 +5484,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0FTMLYC74</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>101644.07</v>
+        <v>54457.64</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>29823.73</v>
       </c>
       <c r="D116" t="n">
-        <v>-101644.07</v>
+        <v>-24633.91</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -5343,17 +5505,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0FTMM455Z</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>182983.05</v>
+        <v>9949.16</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>4444.07</v>
       </c>
       <c r="D117" t="n">
-        <v>-182983.05</v>
+        <v>-5505.09</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -5364,17 +5526,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0FTMMNCK7</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>27108.47</v>
+        <v>41173.94</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>2783.9</v>
       </c>
       <c r="D118" t="n">
-        <v>-27108.47</v>
+        <v>-38390.04</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -5385,17 +5547,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0FTMRC37L</t>
+          <t>B0DC64BD5R</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>30495.76</v>
+        <v>7369.49</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>-30495.76</v>
+        <v>-7369.49</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -5406,17 +5568,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0GDJPJKSG</t>
+          <t>B0DC674ZNR</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>29650.85</v>
+        <v>44217.8</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>-29650.85</v>
+        <v>-44217.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -5427,17 +5589,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0GDJXGF4H</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>16944.92</v>
+        <v>20888.13</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>22751.69</v>
       </c>
       <c r="D121" t="n">
-        <v>-16944.92</v>
+        <v>1863.56</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -5448,17 +5610,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0GF72VQSX</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>27110.17</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>5338.14</v>
       </c>
       <c r="D122" t="n">
-        <v>-27110.17</v>
+        <v>5338.14</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -5469,17 +5631,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B0GF73VZZ2</t>
+          <t>B0DJ2V3TH2</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>19487.29</v>
+        <v>11435.59</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>-19487.29</v>
+        <v>-11435.59</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -5490,17 +5652,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0GF7561XM</t>
+          <t>B0DJ2VFZWN</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>11012.71</v>
+        <v>20326.27</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>-11012.71</v>
+        <v>-20326.27</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -5511,17 +5673,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B0GF7BLQ27</t>
+          <t>B0DJ2WKCPD</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>50830.51</v>
+        <v>34309.32</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>-50830.51</v>
+        <v>-34309.32</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -5532,17 +5694,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0GF7BR5NH</t>
+          <t>B0DJ2WP1M5</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>22025.42</v>
+        <v>13894.92</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>-22025.42</v>
+        <v>-13894.92</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -5553,17 +5715,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0GF7GZ4K7</t>
+          <t>B0DJ2XHK2N</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>24017.8</v>
+        <v>264274.58</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>-24017.8</v>
+        <v>-264274.58</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -5574,17 +5736,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0GF7J5Y4W</t>
+          <t>B0DJ2Y1BG6</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>12283.9</v>
+        <v>13554.24</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>-12283.9</v>
+        <v>-13554.24</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5595,17 +5757,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B0GF7JSSRF</t>
+          <t>B0DKJHSD8R</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>12283.9</v>
+        <v>162640.68</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>-12283.9</v>
+        <v>-162640.68</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5616,17 +5778,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B0GF7KPRXB</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>27110.17</v>
+        <v>107411.18</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="D130" t="n">
-        <v>-27110.17</v>
+        <v>-105717.11</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5637,19 +5799,1510 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>B0DP3194QN</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>29830.51</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3143.22</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-26687.29</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>46802.41</v>
+      </c>
+      <c r="C132" t="n">
+        <v>2592.37</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-44210.04</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>B0DSBN62LR</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>27108.47</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-27108.47</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>B0DSBPCW8R</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>10588.98</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-10588.98</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>B0DSBPPPJ9</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>10972.03</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-10972.03</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>B0DSBQCZTK</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>81335.59</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-81335.59</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>B0DSBQDZNV</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>54216.95</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-54216.95</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>B0DSBRQNM8</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>21944.07</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-21944.07</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>B0DSBRWZ8N</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>22023.73</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-22023.73</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>B0DSBS17RY</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>36849.15</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-36849.15</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>B0DSBSD26P</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>85981.36</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-85981.36</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>B0DSBSGK17</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>67771.19</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-67771.19</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>B0DT2KTXK3</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>14234.75</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-14234.75</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>B0DT2ZQV18</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>9404.24</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-9404.24</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>B0DT381WY9</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>9403.389999999999</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-9403.389999999999</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>B0DT6T6N6B</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>32234.63</v>
+      </c>
+      <c r="C146" t="n">
+        <v>38833.77</v>
+      </c>
+      <c r="D146" t="n">
+        <v>6599.14</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>B0DXFPM4N2</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>501024.49</v>
+      </c>
+      <c r="C147" t="n">
+        <v>532048.21</v>
+      </c>
+      <c r="D147" t="n">
+        <v>31023.72</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>B0FCVBY986</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>11435.59</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-11435.59</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>B0FCVHPY4B</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>7116.1</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>-7116.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>B0FCVLFLGF</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>14232.2</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-14232.2</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>B0FCVPBY7Y</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>294793.22</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>-294793.22</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>B0FFB6YJM1</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>30506.74</v>
+      </c>
+      <c r="C152" t="n">
+        <v>33682.17</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3175.43</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>B0FFDJNB8T</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>8471.190000000001</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-8471.190000000001</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>B0FFDM5QJX</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>10675.42</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-10675.42</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>B0FFHXRJNS</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>6777.97</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>-6777.97</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>B0FFJJM7DS</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>15672.88</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-15672.88</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>B0FG88HVQ8</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>150455.37</v>
+      </c>
+      <c r="C157" t="n">
+        <v>160955.37</v>
+      </c>
+      <c r="D157" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>B0FJ2K95XT</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>4490.68</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-4490.68</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>B0FJ2RND61</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>33888.14</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-33888.14</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>B0FJ2SSSZR</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>18977.97</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>-18977.97</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>B0FJ8PZ9H7</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0</v>
+      </c>
+      <c r="C161" t="n">
+        <v>11694.07</v>
+      </c>
+      <c r="D161" t="n">
+        <v>11694.07</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>B0FJ8TSQK1</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>15934.73</v>
+      </c>
+      <c r="C162" t="n">
+        <v>26609.29</v>
+      </c>
+      <c r="D162" t="n">
+        <v>10674.56</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>B0FKBV3N4Y</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>17368.64</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>-17368.64</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>B0FN7B3KWS</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>50758.46</v>
+      </c>
+      <c r="C164" t="n">
+        <v>61774.56</v>
+      </c>
+      <c r="D164" t="n">
+        <v>11016.1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>B0FQ8K147H</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>13641.53</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>-13641.53</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>B0FQBTRM28</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>4966.94</v>
+      </c>
+      <c r="C166" t="n">
+        <v>6661.01</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1694.07</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>B0FQBX8J17</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>25042.28</v>
+      </c>
+      <c r="C167" t="n">
+        <v>26288.89</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1246.61</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>B0FQBXS6Y2</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>86975.24000000001</v>
+      </c>
+      <c r="C168" t="n">
+        <v>91511.69</v>
+      </c>
+      <c r="D168" t="n">
+        <v>4536.45</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>B0FRVBBDM9</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>32023.73</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>-32023.73</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>B0FS5QZRYB</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>30493.22</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>-30493.22</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>B0FTK1RVG8</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>16264.41</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>-16264.41</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>B0FTK7KQ1P</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>9192.370000000001</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-9192.370000000001</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>B0FTL6QH21</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>16944.92</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>-16944.92</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>B0FTML3VHG</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>34306.78</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>-34306.78</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>B0FTMLYC74</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>101644.07</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>-101644.07</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>B0FTMM455Z</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>182983.05</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>-182983.05</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>B0FTMMNCK7</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>27108.47</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>-27108.47</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>B0FTMRC37L</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>30495.76</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>-30495.76</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>B0FTVQQVDC</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>65831.36</v>
+      </c>
+      <c r="C179" t="n">
+        <v>82778.82000000001</v>
+      </c>
+      <c r="D179" t="n">
+        <v>16947.46</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>B0G39ZHDYP</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>37011.87</v>
+      </c>
+      <c r="C180" t="n">
+        <v>40060.17</v>
+      </c>
+      <c r="D180" t="n">
+        <v>3048.3</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>B0G3B152FR</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>41560.99</v>
+      </c>
+      <c r="C181" t="n">
+        <v>44779.63</v>
+      </c>
+      <c r="D181" t="n">
+        <v>3218.64</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>B0G4DNF8RZ</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>24321.17</v>
+      </c>
+      <c r="C182" t="n">
+        <v>27116.93</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2795.76</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>B0G53H49BS</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>140146.87</v>
+      </c>
+      <c r="C183" t="n">
+        <v>152735.87</v>
+      </c>
+      <c r="D183" t="n">
+        <v>12589</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>B0GDJPJKSG</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>29650.85</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>-29650.85</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>B0GDJXGF4H</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>16944.92</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>-16944.92</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>B0GF72VQSX</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>27110.17</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>-27110.17</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>B0GF73VZZ2</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>19487.29</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-19487.29</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>B0GF7561XM</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>11012.71</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>-11012.71</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>B0GF7BLQ27</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>50830.51</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>-50830.51</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>B0GF7BR5NH</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>22025.42</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>-22025.42</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>B0GF7GZ4K7</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>24017.8</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>-24017.8</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>B0GF7J5Y4W</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>12283.9</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>-12283.9</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>B0GF7JSSRF</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>12283.9</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" t="n">
+        <v>-12283.9</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>B0GF7KPRXB</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>27110.17</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>-27110.17</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
           <t>B0GHDHD4B9</t>
         </is>
       </c>
-      <c r="B131" t="n">
+      <c r="B195" t="n">
         <v>13555.08</v>
       </c>
-      <c r="C131" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" t="n">
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
         <v>-13555.08</v>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>B0GKPXQ8G3</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>5761.02</v>
+      </c>
+      <c r="C196" t="n">
+        <v>8641.52</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2880.5</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>B0GN2LHJY4</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>52327.97</v>
+      </c>
+      <c r="C197" t="n">
+        <v>59954.24</v>
+      </c>
+      <c r="D197" t="n">
+        <v>7626.27</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>B0GN8MPYPG</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>0</v>
+      </c>
+      <c r="C198" t="n">
+        <v>9320.34</v>
+      </c>
+      <c r="D198" t="n">
+        <v>9320.34</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>369199.78</v>
+      </c>
+      <c r="C199" t="n">
+        <v>401615.04</v>
+      </c>
+      <c r="D199" t="n">
+        <v>32415.26</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>B0GW8ZQRFK</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>0</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1355.08</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1355.08</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>B0GW92316G</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0</v>
+      </c>
+      <c r="C201" t="n">
+        <v>6778.81</v>
+      </c>
+      <c r="D201" t="n">
+        <v>6778.81</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>B0GXP97CZG</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>41368.64</v>
+      </c>
+      <c r="C202" t="n">
+        <v>38149.15</v>
+      </c>
+      <c r="D202" t="n">
+        <v>-3219.49</v>
+      </c>
+      <c r="E202" t="inlineStr">
         <is>
           <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
         </is>
@@ -5666,11 +7319,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_file_spend</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_spend</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -5679,7 +7352,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route ads rule consistency</t>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -5694,11 +7381,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>file_sessions</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_sessions</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -5707,7 +7414,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route sessions consistency</t>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -5722,31 +7443,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sales_trend_units</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ams_trend_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -6259,17 +7980,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B08QVCPDVT</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D26" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -6280,7 +8001,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B09NC2NFR9</t>
+          <t>B08QVCPDVT</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6301,7 +8022,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B09SHQSHBF</t>
+          <t>B09NC2NFR9</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6322,17 +8043,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0CHXGWVZJ</t>
+          <t>B09SHQSHBF</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -6343,17 +8064,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0CRCWV9DV</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="D30" t="n">
-        <v>-2</v>
+        <v>18</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6364,17 +8085,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0CZ8ZKPJ9</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -6385,17 +8106,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0D854LDQM</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -6406,17 +8127,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0D8572WTJ</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D33" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -6427,17 +8148,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0D9362N4Q</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>41</v>
+      </c>
+      <c r="C34" t="n">
+        <v>44</v>
+      </c>
+      <c r="D34" t="n">
         <v>3</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -6448,17 +8169,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0D93652ZY</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="D35" t="n">
-        <v>-17</v>
+        <v>20</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -6469,17 +8190,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0D9369MTM</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
         <v>2</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -6490,17 +8211,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0D936GPVL</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D37" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -6511,17 +8232,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0D955NZTN</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D38" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -6532,17 +8253,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0D9564Z9T</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D39" t="n">
-        <v>-3</v>
+        <v>8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -6553,17 +8274,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0D9573TBX</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>24</v>
+      </c>
+      <c r="D40" t="n">
         <v>4</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -6574,17 +8295,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0D9574DPS</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D41" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -6595,17 +8316,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0DC674ZNR</t>
+          <t>B0CHXGWVZJ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -6616,17 +8337,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0DJ2VFZWN</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D43" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -6637,17 +8358,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0DJ2WKCPD</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>21</v>
+      </c>
+      <c r="C44" t="n">
+        <v>24</v>
+      </c>
+      <c r="D44" t="n">
         <v>3</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -6658,17 +8379,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0DJ2XHK2N</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>-26</v>
+        <v>2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -6679,17 +8400,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0DKJHSD8R</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D46" t="n">
-        <v>-12</v>
+        <v>3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -6700,7 +8421,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0DSBN62LR</t>
+          <t>B0CRCWV9DV</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -6721,7 +8442,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0DSBQCZTK</t>
+          <t>B0CZ8ZKPJ9</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -6742,17 +8463,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0DSBQDZNV</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>24</v>
+      </c>
+      <c r="C49" t="n">
+        <v>28</v>
+      </c>
+      <c r="D49" t="n">
         <v>4</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -6763,17 +8484,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0DSBRQNM8</t>
+          <t>B0D854LDQM</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -6784,7 +8505,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0DSBRWZ8N</t>
+          <t>B0D8572WTJ</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -6805,7 +8526,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0DSBS17RY</t>
+          <t>B0D9362N4Q</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -6826,17 +8547,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0DSBSD26P</t>
+          <t>B0D93652ZY</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -6847,17 +8568,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0DSBSGK17</t>
+          <t>B0D9369MTM</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -6868,17 +8589,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0FCVLFLGF</t>
+          <t>B0D936GPVL</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -6889,17 +8610,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0FCVPBY7Y</t>
+          <t>B0D955NZTN</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>-25</v>
+        <v>-2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -6910,17 +8631,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0FJ2RND61</t>
+          <t>B0D9564Z9T</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -6931,17 +8652,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0FJ2SSSZR</t>
+          <t>B0D9573TBX</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -6952,17 +8673,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0FRVBBDM9</t>
+          <t>B0D9574DPS</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -6973,17 +8694,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0FS5QZRYB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D60" t="n">
-        <v>-3</v>
+        <v>-76</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -6994,17 +8715,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0FTK1RVG8</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D61" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -7015,17 +8736,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0FTML3VHG</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="B62" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" t="n">
         <v>3</v>
       </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
       <c r="D62" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -7036,17 +8757,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0FTMLYC74</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -7057,17 +8778,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0FTMM455Z</t>
+          <t>B0DC674ZNR</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>-16</v>
+        <v>-6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -7078,17 +8799,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0FTMMNCK7</t>
+          <t>B0DJ2VFZWN</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -7099,7 +8820,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0FTMRC37L</t>
+          <t>B0DJ2WKCPD</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -7120,17 +8841,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0GDJPJKSG</t>
+          <t>B0DJ2XHK2N</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>-2</v>
+        <v>-26</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -7141,17 +8862,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0GF72VQSX</t>
+          <t>B0DKJHSD8R</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -7162,17 +8883,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0GF7BLQ27</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>-4</v>
+        <v>-64</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -7183,17 +8904,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0GF7BR5NH</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -7204,17 +8925,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0GF7GZ4K7</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>-3</v>
+        <v>-17</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -7225,7 +8946,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0GF7KPRXB</t>
+          <t>B0DSBN62LR</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -7238,6 +8959,783 @@
         <v>-2</v>
       </c>
       <c r="E72" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B0DSBQCZTK</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>B0DSBQDZNV</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>B0DSBRQNM8</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>B0DSBRWZ8N</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>B0DSBS17RY</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>B0DSBSD26P</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>7</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>B0DSBSGK17</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>B0DT6T6N6B</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>69</v>
+      </c>
+      <c r="C80" t="n">
+        <v>82</v>
+      </c>
+      <c r="D80" t="n">
+        <v>13</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B0DXFPM4N2</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>69</v>
+      </c>
+      <c r="C81" t="n">
+        <v>73</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B0FCVLFLGF</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B0FCVPBY7Y</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>25</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-25</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B0FFB6YJM1</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>29</v>
+      </c>
+      <c r="C84" t="n">
+        <v>32</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>B0FG88HVQ8</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>92</v>
+      </c>
+      <c r="C85" t="n">
+        <v>98</v>
+      </c>
+      <c r="D85" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>B0FJ2RND61</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>B0FJ2SSSZR</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>B0FJ8TSQK1</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>6</v>
+      </c>
+      <c r="C88" t="n">
+        <v>10</v>
+      </c>
+      <c r="D88" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>B0FQBXS6Y2</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>72</v>
+      </c>
+      <c r="C89" t="n">
+        <v>75</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>B0FRVBBDM9</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>B0FS5QZRYB</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>B0FTK1RVG8</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>2</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>B0FTML3VHG</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>B0FTMLYC74</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>10</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>B0FTMM455Z</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-16</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>B0FTMMNCK7</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>B0FTMRC37L</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>3</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>B0FTVQQVDC</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>8</v>
+      </c>
+      <c r="C98" t="n">
+        <v>10</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>B0G39ZHDYP</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>38</v>
+      </c>
+      <c r="C99" t="n">
+        <v>41</v>
+      </c>
+      <c r="D99" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>B0G3B152FR</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>26</v>
+      </c>
+      <c r="C100" t="n">
+        <v>28</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>B0G53H49BS</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>61</v>
+      </c>
+      <c r="C101" t="n">
+        <v>66</v>
+      </c>
+      <c r="D101" t="n">
+        <v>5</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>B0GDJPJKSG</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>B0GF72VQSX</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>B0GF7BLQ27</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>B0GF7BR5NH</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>B0GF7GZ4K7</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>3</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>B0GF7KPRXB</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>B0GN8MPYPG</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>61</v>
+      </c>
+      <c r="C109" t="n">
+        <v>66</v>
+      </c>
+      <c r="D109" t="n">
+        <v>5</v>
+      </c>
+      <c r="E109" t="inlineStr">
         <is>
           <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
         </is>
@@ -7254,11 +9752,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>snap_total_sales</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>am1p_route_sales</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7267,7 +9785,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route per-brand totals consistency</t>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -7286,7 +9818,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7310,21 +9842,665 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sales_gmv</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ams_gmv</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pct</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>clean — AMS Trend GMV &gt; Sales Trend GMV (per brand×model×wk)</t>
-        </is>
+      <c r="A2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AI-04 RED</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>524967</v>
+      </c>
+      <c r="E2" t="n">
+        <v>609696</v>
+      </c>
+      <c r="F2" t="n">
+        <v>84729</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AM-C1</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>418103</v>
+      </c>
+      <c r="E3" t="n">
+        <v>460070</v>
+      </c>
+      <c r="F3" t="n">
+        <v>41967</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>369200</v>
+      </c>
+      <c r="E4" t="n">
+        <v>401615</v>
+      </c>
+      <c r="F4" t="n">
+        <v>32415</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AM-S1</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>530258</v>
+      </c>
+      <c r="E5" t="n">
+        <v>561282</v>
+      </c>
+      <c r="F5" t="n">
+        <v>31024</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AA-21</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>125436</v>
+      </c>
+      <c r="E6" t="n">
+        <v>152060</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26624</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>65831</v>
+      </c>
+      <c r="E7" t="n">
+        <v>82779</v>
+      </c>
+      <c r="F7" t="n">
+        <v>16947</v>
+      </c>
+      <c r="G7" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AA-19</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>100531</v>
+      </c>
+      <c r="E8" t="n">
+        <v>114053</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13522</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AI-13</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>144637</v>
+      </c>
+      <c r="E9" t="n">
+        <v>157226</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12589</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AM-C46</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>70748</v>
+      </c>
+      <c r="E10" t="n">
+        <v>82609</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11861</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PB-04 (AI-04 RED + AM-C44 X 2)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11694</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11694</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1169407</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>UB-02 (AM-S1 + AA-21)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>50758</v>
+      </c>
+      <c r="E12" t="n">
+        <v>61775</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11016</v>
+      </c>
+      <c r="G12" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GB-03 (AI-12 + AM-C43)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15935</v>
+      </c>
+      <c r="E13" t="n">
+        <v>26609</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10675</v>
+      </c>
+      <c r="G13" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AH-50</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>150455</v>
+      </c>
+      <c r="E14" t="n">
+        <v>160955</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>28</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK-61 PRO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9320</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9320</v>
+      </c>
+      <c r="G15" t="n">
+        <v>932034</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>28</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AM-C43</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>41914</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50385</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8471</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>28</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MT-12</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>52328</v>
+      </c>
+      <c r="E17" t="n">
+        <v>59954</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7626</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>28</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TM20</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>29880</v>
+      </c>
+      <c r="E18" t="n">
+        <v>37504</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7625</v>
+      </c>
+      <c r="G18" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>28</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AM-W36 PRO</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6779</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6779</v>
+      </c>
+      <c r="G19" t="n">
+        <v>677881</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>28</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AI-03</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3219</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9997</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6778</v>
+      </c>
+      <c r="G20" t="n">
+        <v>210.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AA-26</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>32235</v>
+      </c>
+      <c r="E21" t="n">
+        <v>38834</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6599</v>
+      </c>
+      <c r="G21" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AM-W14</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>46924</v>
+      </c>
+      <c r="E22" t="n">
+        <v>52262</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5338</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>28</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AM-W36</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5338</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5338</v>
+      </c>
+      <c r="G23" t="n">
+        <v>533814</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>28</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TD310</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>29309</v>
+      </c>
+      <c r="E24" t="n">
+        <v>34392</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5082</v>
+      </c>
+      <c r="G24" t="n">
+        <v>17.3</v>
       </c>
     </row>
   </sheetData>
@@ -7342,32 +10518,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7386,14 +10562,14 @@
         <v>181329</v>
       </c>
       <c r="D2" t="n">
-        <v>181329</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -7407,17 +10583,17 @@
         <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>173571</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>173571</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -7432,11 +10608,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>lag_sec</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7445,7 +10636,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Derivative snapshot stale vs parent (re-run needed)</t>
+          <t>data\processed\weekly_sales_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>data\ams_weekly_data\ams_weekly_fact\ams_weekly_fact.csv</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>weekly_sales_snapshot → ams_weekly_fact (biz_ads_weekly_etl needs re-run)</t>
         </is>
       </c>
     </row>
@@ -7464,32 +10668,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>prior_4w_median</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7510,7 +10714,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>445432</v>
+        <v>445071</v>
       </c>
       <c r="E2" t="n">
         <v>-100</v>
@@ -7536,7 +10740,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2656253</v>
+        <v>2654878</v>
       </c>
       <c r="E3" t="n">
         <v>-100</v>
@@ -7614,7 +10818,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7642,7 +10846,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7666,11 +10870,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sales_trend_amz_side</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_gmv</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7679,7 +10903,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — AMS Trend GMV vs Sales Trend Amazon-side per brand</t>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4281008.83</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4726879.23</v>
+      </c>
+      <c r="D2" t="n">
+        <v>445870.4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>287987.11</v>
+      </c>
+      <c r="C3" t="n">
+        <v>312502.37</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24515.26</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1158683.09</v>
+      </c>
+      <c r="C4" t="n">
+        <v>745489.84</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-413193.25</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
         </is>
       </c>
     </row>
@@ -7698,7 +10978,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7726,7 +11006,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7750,41 +11030,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sales_trend_amz_side</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ams_trend_gmv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta_rs</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7793,25 +11073,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3095009.71</v>
+        <v>667942.12</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>584995.51</v>
       </c>
       <c r="E2" t="n">
-        <v>-3095009.71</v>
+        <v>-82946.61</v>
       </c>
       <c r="F2" t="n">
-        <v>-100</v>
+        <v>-12.42</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7822,25 +11102,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2392739.69</v>
+        <v>713759.26</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>690287.23</v>
       </c>
       <c r="E3" t="n">
-        <v>-2392739.69</v>
+        <v>-23472.03</v>
       </c>
       <c r="F3" t="n">
-        <v>-100</v>
+        <v>-3.29</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7851,25 +11131,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>324781.32</v>
+        <v>1077787.08</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>976121.8199999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-324781.32</v>
+        <v>-101665.26</v>
       </c>
       <c r="F4" t="n">
-        <v>-100</v>
+        <v>-9.43</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -7880,7 +11160,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7889,16 +11169,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1906527.52</v>
+        <v>911351.88</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>749514.71</v>
       </c>
       <c r="E5" t="n">
-        <v>-1906527.52</v>
+        <v>-161837.17</v>
       </c>
       <c r="F5" t="n">
-        <v>-100</v>
+        <v>-17.76</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -7909,25 +11189,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2654996.45</v>
+        <v>888714.46</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>823641.58</v>
       </c>
       <c r="E6" t="n">
-        <v>-2654996.45</v>
+        <v>-65072.88</v>
       </c>
       <c r="F6" t="n">
-        <v>-100</v>
+        <v>-7.32</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -7938,25 +11218,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1396572.19</v>
+        <v>1135238.81</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1078365.93</v>
       </c>
       <c r="E7" t="n">
-        <v>-1396572.19</v>
+        <v>-56872.88</v>
       </c>
       <c r="F7" t="n">
-        <v>-100</v>
+        <v>-5.01</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -7967,25 +11247,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>346045.54</v>
+        <v>4281008.83</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4726879.23</v>
       </c>
       <c r="E8" t="n">
-        <v>-346045.54</v>
+        <v>445870.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-100</v>
+        <v>10.42</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -7996,25 +11276,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1104654.21</v>
+        <v>287987.11</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>312502.37</v>
       </c>
       <c r="E9" t="n">
-        <v>-1104654.21</v>
+        <v>24515.26</v>
       </c>
       <c r="F9" t="n">
-        <v>-100</v>
+        <v>8.51</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -8025,1738 +11305,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3119828.81</v>
+        <v>1158683.09</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>745489.84</v>
       </c>
       <c r="E10" t="n">
-        <v>-3119828.81</v>
+        <v>-413193.25</v>
       </c>
       <c r="F10" t="n">
-        <v>-100</v>
+        <v>-35.66</v>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1608376.27</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-1608376.27</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>314639.94</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-314639.94</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1130237.2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1130237.2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>3039578.87</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-3039578.87</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1577064.99</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-1577064.99</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>252253.44</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-252253.44</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1067856.25</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-1067856.25</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3033347.93</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-3033347.93</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1410246.25</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-1410246.25</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>203072.94</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-203072.94</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>938633.14</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-938633.14</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2957495.02</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-2957495.02</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1467359.63</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-1467359.63</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>184894.03</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-184894.03</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1181052.36</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-1181052.36</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>3066258.52</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-3066258.52</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1643099.86</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-1643099.86</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>110584.75</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-110584.75</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>914785.01</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-914785.01</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>3097839.36</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-3097839.36</v>
-      </c>
-      <c r="F30" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>2190479.57</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-2190479.57</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>87927.05</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-87927.05</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>667998.22</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-667998.22</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>2904810.42</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-2904810.42</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1929190.89</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-1929190.89</v>
-      </c>
-      <c r="F35" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>114738.08</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-114738.08</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>555963.54</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-555963.54</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>W13</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>3225192.62</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-3225192.62</v>
-      </c>
-      <c r="F38" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>W13</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1573750.55</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-1573750.55</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>W13</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>161457.56</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-161457.56</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>W13</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>784099.59</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-784099.59</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>3058255.43</v>
-      </c>
-      <c r="D42" t="n">
-        <v>5019971.19</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1961715.76</v>
-      </c>
-      <c r="F42" t="n">
-        <v>64.14</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1694388.76</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-1694388.76</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>114756.74</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-114756.74</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>663401.58</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-663401.58</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>2511216.45</v>
-      </c>
-      <c r="D46" t="n">
-        <v>5635809.32</v>
-      </c>
-      <c r="E46" t="n">
-        <v>3124592.87</v>
-      </c>
-      <c r="F46" t="n">
-        <v>124.43</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1917524.41</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-1917524.41</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>151414.35</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-151414.35</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>494952.2</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-494952.2</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>W16</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>2623900.45</v>
-      </c>
-      <c r="D50" t="n">
-        <v>4668839.83</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2044939.38</v>
-      </c>
-      <c r="F50" t="n">
-        <v>77.94</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>W16</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1700277.86</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-1700277.86</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>W16</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>138892.26</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-138892.26</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>W16</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>470608.43</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-470608.43</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>W17</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>2522344.88</v>
-      </c>
-      <c r="D54" t="n">
-        <v>6872220.3</v>
-      </c>
-      <c r="E54" t="n">
-        <v>4349875.42</v>
-      </c>
-      <c r="F54" t="n">
-        <v>172.45</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>W18</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>2715491.35</v>
-      </c>
-      <c r="D55" t="n">
-        <v>8174573.55</v>
-      </c>
-      <c r="E55" t="n">
-        <v>5459082.2</v>
-      </c>
-      <c r="F55" t="n">
-        <v>201.03</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>W18</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>667942.12</v>
-      </c>
-      <c r="D56" t="n">
-        <v>584995.51</v>
-      </c>
-      <c r="E56" t="n">
-        <v>-82946.61</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-12.42</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>W19</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>3152749.66</v>
-      </c>
-      <c r="D57" t="n">
-        <v>8552069.15</v>
-      </c>
-      <c r="E57" t="n">
-        <v>5399319.49</v>
-      </c>
-      <c r="F57" t="n">
-        <v>171.26</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>W19</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>713759.26</v>
-      </c>
-      <c r="D58" t="n">
-        <v>690287.23</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-23472.03</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>W20</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>3584872.07</v>
-      </c>
-      <c r="D59" t="n">
-        <v>9429570.390000001</v>
-      </c>
-      <c r="E59" t="n">
-        <v>5844698.32</v>
-      </c>
-      <c r="F59" t="n">
-        <v>163.04</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>W20</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1077787.08</v>
-      </c>
-      <c r="D60" t="n">
-        <v>976121.8199999999</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-101665.26</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-9.43</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>W21</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>3149317.17</v>
-      </c>
-      <c r="D61" t="n">
-        <v>9042481.039999999</v>
-      </c>
-      <c r="E61" t="n">
-        <v>5893163.87</v>
-      </c>
-      <c r="F61" t="n">
-        <v>187.13</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>W21</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>911351.88</v>
-      </c>
-      <c r="D62" t="n">
-        <v>749514.71</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-161837.17</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-17.76</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>W22</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>3513017.55</v>
-      </c>
-      <c r="D63" t="n">
-        <v>8443631.970000001</v>
-      </c>
-      <c r="E63" t="n">
-        <v>4930614.42</v>
-      </c>
-      <c r="F63" t="n">
-        <v>140.35</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>W22</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>888714.46</v>
-      </c>
-      <c r="D64" t="n">
-        <v>823641.58</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-65072.88</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-7.32</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>W23</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>3904809.28</v>
-      </c>
-      <c r="D65" t="n">
-        <v>9454071.99</v>
-      </c>
-      <c r="E65" t="n">
-        <v>5549262.71</v>
-      </c>
-      <c r="F65" t="n">
-        <v>142.11</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>W23</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1135238.81</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1078365.93</v>
-      </c>
-      <c r="E66" t="n">
-        <v>-56872.88</v>
-      </c>
-      <c r="F66" t="n">
-        <v>-5.01</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>W24</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>4237199.81</v>
-      </c>
-      <c r="D67" t="n">
-        <v>9605431.17</v>
-      </c>
-      <c r="E67" t="n">
-        <v>5368231.36</v>
-      </c>
-      <c r="F67" t="n">
-        <v>126.69</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>W24</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>624059.3199999999</v>
-      </c>
-      <c r="D68" t="n">
-        <v>743727.1</v>
-      </c>
-      <c r="E68" t="n">
-        <v>119667.78</v>
-      </c>
-      <c r="F68" t="n">
-        <v>19.18</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>W25</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>4068361.84</v>
-      </c>
-      <c r="D69" t="n">
-        <v>9160789.810000001</v>
-      </c>
-      <c r="E69" t="n">
-        <v>5092427.97</v>
-      </c>
-      <c r="F69" t="n">
-        <v>125.17</v>
-      </c>
-      <c r="G69" t="inlineStr">
         <is>
           <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
         </is>
@@ -9773,11 +11342,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>week_num</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -9786,7 +11375,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Never-Zero column regression</t>
+          <t>ams_trend.inventory_snapshot (load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -9805,7 +11410,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -9829,36 +11434,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -9886,7 +11491,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1259888.27</v>
+        <v>1259780.88</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -9914,7 +11519,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7168741.970000001</v>
+        <v>7168235.189999999</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -10057,34 +11662,6 @@
         <v>6000</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1p sales</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>330</v>
-      </c>
-      <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10103,22 +11680,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -10403,7 +11980,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -10427,26 +12004,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -10455,160 +12017,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in sales for W28</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in sales for W28</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>28</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in sales for W28</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>28</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in sales for W28</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in inventory for W28</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>28</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in inventory for W28</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>28</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in inventory for W28</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>28</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W28</t>
+          <t>clean — Brand missing from a layer (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -10627,32 +12036,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,39 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,16 +43,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -63,7 +60,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -71,21 +68,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,32 +443,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2781,32 +2769,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -2851,86 +2839,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>raw_units</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>snap_units</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2042</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1880</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-162</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ROWS LOST (ETL drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tonor</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>170</v>
-      </c>
-      <c r="D3" t="n">
-        <v>158</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-12</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ROWS LOST (ETL drop)</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Sales raw vs snapshot (per brand×wk)</t>
         </is>
       </c>
     </row>
@@ -2945,105 +2867,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>pair</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>amazon+1p_inventory</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ams_trend_total_amazon</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>sales_trend_inv</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>inv_dashboard_total</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>amazon+1p_vs_ams_trend</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>(load failed)</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales_trend_vs_inv_dashboard</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>(load failed)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
+          <t>clean — Cross-route inventory rule consistency</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3057,31 +2895,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E202"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>sales_trend_amzn+1p_gmv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ams_trend_gmv</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>delta_rs</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -3510,17 +3348,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B01KNMEVDG</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53868.48</v>
+        <v>6607.63</v>
       </c>
       <c r="C22" t="n">
-        <v>54156.62</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>288.14</v>
+        <v>-6607.63</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -3531,17 +3369,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B01KNMEVDG</t>
+          <t>B06VV5QB6Q</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6607.63</v>
+        <v>40233.05</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-6607.63</v>
+        <v>-40233.05</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -3552,17 +3390,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B06VV5QB6Q</t>
+          <t>B078Y2PJL4</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>40233.05</v>
+        <v>97586.44</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-40233.05</v>
+        <v>-97586.44</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -3573,17 +3411,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B078Y2PJL4</t>
+          <t>B079XB5RXH</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>97586.44</v>
+        <v>62272.88</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-97586.44</v>
+        <v>-62272.88</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -3594,17 +3432,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B079XB5RXH</t>
+          <t>B07CSNG8XL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>62272.88</v>
+        <v>64352.54</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-62272.88</v>
+        <v>-64352.54</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3615,17 +3453,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B07CSNG8XL</t>
+          <t>B07M7P7VLX</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64352.54</v>
+        <v>41171.19</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-64352.54</v>
+        <v>-41171.19</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -3636,17 +3474,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B07MFZ6S2Q</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>49604.24</v>
+        <v>24566.1</v>
       </c>
       <c r="C28" t="n">
-        <v>51891.52</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>2287.28</v>
+        <v>-24566.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -3657,17 +3495,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B07M7P7VLX</t>
+          <t>B07MM5MH6F</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>41171.19</v>
+        <v>33035.59</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-41171.19</v>
+        <v>-33035.59</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -3678,17 +3516,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B07MFZ6S2Q</t>
+          <t>B07RZ1R1HJ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24566.1</v>
+        <v>33035.59</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-24566.1</v>
+        <v>-33035.59</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -3699,17 +3537,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B07MM5MH6F</t>
+          <t>B07T2XYGR5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>33035.59</v>
+        <v>20334.75</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-33035.59</v>
+        <v>-20334.75</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -3720,17 +3558,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B07RZ1R1HJ</t>
+          <t>B07T3ZPD9X</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>33035.59</v>
+        <v>9192.370000000001</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-33035.59</v>
+        <v>-9192.370000000001</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3741,17 +3579,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B07T2XYGR5</t>
+          <t>B07T53T1KV</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20334.75</v>
+        <v>27538.14</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-20334.75</v>
+        <v>-27538.14</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3762,17 +3600,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B07T3ZPD9X</t>
+          <t>B07T62YVHY</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9192.370000000001</v>
+        <v>17791.53</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-9192.370000000001</v>
+        <v>-17791.53</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -3783,17 +3621,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B07T53T1KV</t>
+          <t>B0846Q1JT5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27538.14</v>
+        <v>13130.51</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-27538.14</v>
+        <v>-13130.51</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -3804,17 +3642,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B07T62YVHY</t>
+          <t>B08QTW81S9</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17791.53</v>
+        <v>11434.75</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>-17791.53</v>
+        <v>-11434.75</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -3825,17 +3663,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B08QVCPDVT</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9910.16</v>
+        <v>24566.1</v>
       </c>
       <c r="C37" t="n">
-        <v>11604.22</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1694.06</v>
+        <v>-24566.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3846,17 +3684,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0846Q1JT5</t>
+          <t>B08XBYKWW3</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>13130.51</v>
+        <v>13640.68</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-13130.51</v>
+        <v>-13640.68</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3867,17 +3705,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B09BBK2LV4</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29879.67</v>
+        <v>23724.58</v>
       </c>
       <c r="C39" t="n">
-        <v>37504.26</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>7624.59</v>
+        <v>-23724.58</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -3888,17 +3726,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B08QTW81S9</t>
+          <t>B09NC2NFR9</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>11434.75</v>
+        <v>20328.81</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>-11434.75</v>
+        <v>-20328.81</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -3909,17 +3747,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B08QVCPDVT</t>
+          <t>B09SHQSHBF</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>24566.1</v>
+        <v>27279.66</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>-24566.1</v>
+        <v>-27279.66</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -3930,17 +3768,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B08XBYKWW3</t>
+          <t>B0B75LLWV6</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>13640.68</v>
+        <v>10166.95</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>-13640.68</v>
+        <v>-10166.95</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3951,17 +3789,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B09BBK2LV4</t>
+          <t>B0BFXL8ZP9</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>23724.58</v>
+        <v>11012.71</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>-23724.58</v>
+        <v>-11012.71</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -3972,17 +3810,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B09NC2NFR9</t>
+          <t>B0BQZH3LGP</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20328.81</v>
+        <v>8895.76</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>-20328.81</v>
+        <v>-8895.76</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3993,17 +3831,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B09SHQSHBF</t>
+          <t>B0C77PPS9S</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27279.66</v>
+        <v>10164.41</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>-27279.66</v>
+        <v>-10164.41</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -4014,17 +3852,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0CHXGWVZJ</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>418102.9</v>
+        <v>44476.27</v>
       </c>
       <c r="C46" t="n">
-        <v>460069.93</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>41967.03</v>
+        <v>-44476.27</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -4035,17 +3873,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0CHXTV16D</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34057.92</v>
+        <v>8894.92</v>
       </c>
       <c r="C47" t="n">
-        <v>37429.11</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>3371.19</v>
+        <v>-8894.92</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -4056,17 +3894,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0CJ6ZHK1S</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7964.4</v>
+        <v>13554.24</v>
       </c>
       <c r="C48" t="n">
-        <v>11946.6</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>3982.2</v>
+        <v>-13554.24</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -4077,17 +3915,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0CJ6ZW8F6</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>46923.75</v>
+        <v>10164.41</v>
       </c>
       <c r="C49" t="n">
-        <v>52261.89</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>5338.14</v>
+        <v>-10164.41</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -4098,17 +3936,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0CR5NKB4C</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9705.959999999999</v>
+        <v>8894.92</v>
       </c>
       <c r="C50" t="n">
-        <v>14025.47</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>4319.51</v>
+        <v>-8894.92</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -4119,17 +3957,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0CRCWV9DV</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5294.07</v>
+        <v>27108.47</v>
       </c>
       <c r="C51" t="n">
-        <v>7115.26</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1821.19</v>
+        <v>-27108.47</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -4140,17 +3978,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0CRCYMKY8</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5966.96</v>
+        <v>10972.03</v>
       </c>
       <c r="C52" t="n">
-        <v>6833.9</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>866.9400000000001</v>
+        <v>-10972.03</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -4161,17 +3999,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0CRD3QWVJ</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>8471.200000000001</v>
+        <v>10164.41</v>
       </c>
       <c r="C53" t="n">
-        <v>12706.8</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>4235.6</v>
+        <v>-10164.41</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -4182,17 +4020,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0CYMWQCKL</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>42395.73</v>
+        <v>12283.05</v>
       </c>
       <c r="C54" t="n">
-        <v>45784.71</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>3388.98</v>
+        <v>-12283.05</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -4203,17 +4041,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0CZ8ZKPJ9</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>27361.9</v>
+        <v>37952.54</v>
       </c>
       <c r="C55" t="n">
-        <v>29479.7</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>2117.8</v>
+        <v>-37952.54</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -4224,17 +4062,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0B75LLWV6</t>
+          <t>B0CZ9HTWNC</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10166.95</v>
+        <v>10970.34</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>-10166.95</v>
+        <v>-10970.34</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -4245,17 +4083,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0BFXL8ZP9</t>
+          <t>B0D84YD59Y</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>11012.71</v>
+        <v>10588.14</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>-11012.71</v>
+        <v>-10588.14</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -4266,17 +4104,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0D84YY632</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>23322.04</v>
+        <v>13554.24</v>
       </c>
       <c r="C58" t="n">
-        <v>26072.04</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>2750</v>
+        <v>-13554.24</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -4287,17 +4125,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0D85171BL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>9316.950000000001</v>
       </c>
       <c r="C59" t="n">
-        <v>1863.56</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>1863.56</v>
+        <v>-9316.950000000001</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -4308,17 +4146,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0D853Y52R</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>54740.76</v>
+        <v>13553.39</v>
       </c>
       <c r="C60" t="n">
-        <v>59009.4</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>4268.64</v>
+        <v>-13553.39</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -4329,17 +4167,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0D854LDQM</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>524966.73</v>
+        <v>67775.42</v>
       </c>
       <c r="C61" t="n">
-        <v>609695.53</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>84728.8</v>
+        <v>-67775.42</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -4350,17 +4188,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0D8572WTJ</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3219.49</v>
+        <v>27108.47</v>
       </c>
       <c r="C62" t="n">
-        <v>9997.450000000001</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>6777.96</v>
+        <v>-27108.47</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -4371,17 +4209,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0D935VW9J</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>11446.59</v>
+        <v>16014.41</v>
       </c>
       <c r="C63" t="n">
-        <v>12547.44</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>1100.85</v>
+        <v>-16014.41</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -4392,17 +4230,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0BQZH3LGP</t>
+          <t>B0D9362N4Q</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>8895.76</v>
+        <v>34309.32</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>-8895.76</v>
+        <v>-34309.32</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -4413,17 +4251,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0D9363BB2</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>6183.91</v>
+        <v>15672.88</v>
       </c>
       <c r="C65" t="n">
-        <v>8301.709999999999</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>2117.8</v>
+        <v>-15672.88</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -4434,17 +4272,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0D93652ZY</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>22991.52</v>
+        <v>194405.08</v>
       </c>
       <c r="C66" t="n">
-        <v>26549.14</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>3557.62</v>
+        <v>-194405.08</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -4455,17 +4293,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0C77PPS9S</t>
+          <t>B0D9369MTM</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>10164.41</v>
+        <v>20328.81</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>-10164.41</v>
+        <v>-20328.81</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -4476,17 +4314,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0D936GPVL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>10755.9</v>
+        <v>80049.14999999999</v>
       </c>
       <c r="C68" t="n">
-        <v>12110.98</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>1355.08</v>
+        <v>-80049.14999999999</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -4497,17 +4335,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0D936YHDH</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>100531.4</v>
+        <v>11861.02</v>
       </c>
       <c r="C69" t="n">
-        <v>114053.42</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>13522.02</v>
+        <v>-11861.02</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -4518,17 +4356,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0D955L5S7</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>30337.27</v>
+        <v>15672.88</v>
       </c>
       <c r="C70" t="n">
-        <v>27202.52</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>-3134.75</v>
+        <v>-15672.88</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -4539,17 +4377,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0D955NZTN</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>125435.88</v>
+        <v>16606.78</v>
       </c>
       <c r="C71" t="n">
-        <v>152059.59</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>26623.71</v>
+        <v>-16606.78</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -4560,17 +4398,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0D955YGX7</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>5316.11</v>
+        <v>12455.08</v>
       </c>
       <c r="C72" t="n">
-        <v>6671.19</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>1355.08</v>
+        <v>-12455.08</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -4581,17 +4419,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0D9564Z9T</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>634.75</v>
+        <v>24399.15</v>
       </c>
       <c r="C73" t="n">
-        <v>1311.87</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>677.12</v>
+        <v>-24399.15</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -4602,17 +4440,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0D9573TBX</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>41913.6</v>
+        <v>41518.64</v>
       </c>
       <c r="C74" t="n">
-        <v>50384.8</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>8471.200000000001</v>
+        <v>-41518.64</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -4623,17 +4461,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0D9574DPS</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>20974.57</v>
+        <v>27444.92</v>
       </c>
       <c r="C75" t="n">
-        <v>23300.85</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>2326.28</v>
+        <v>-27444.92</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -4644,17 +4482,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0CHXGWVZJ</t>
+          <t>B0DC64BD5R</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>44476.27</v>
+        <v>7369.49</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>-44476.27</v>
+        <v>-7369.49</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -4665,17 +4503,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0CHXTV16D</t>
+          <t>B0DC674ZNR</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>8894.92</v>
+        <v>44217.8</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>-8894.92</v>
+        <v>-44217.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -4686,17 +4524,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0CJ6ZHK1S</t>
+          <t>B0DJ2V3TH2</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>13554.24</v>
+        <v>11435.59</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>-13554.24</v>
+        <v>-11435.59</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -4707,17 +4545,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0CJ6ZW8F6</t>
+          <t>B0DJ2VFZWN</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>10164.41</v>
+        <v>20326.27</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>-10164.41</v>
+        <v>-20326.27</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4728,17 +4566,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0DJ2WKCPD</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>6305.93</v>
+        <v>34309.32</v>
       </c>
       <c r="C80" t="n">
-        <v>9183.889999999999</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>2877.96</v>
+        <v>-34309.32</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4749,17 +4587,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0DJ2WP1M5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>53939.84</v>
+        <v>13894.92</v>
       </c>
       <c r="C81" t="n">
-        <v>56566.11</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>2626.27</v>
+        <v>-13894.92</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -4770,17 +4608,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0DJ2XHK2N</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>27932.14</v>
+        <v>264274.58</v>
       </c>
       <c r="C82" t="n">
-        <v>31931.29</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>3999.15</v>
+        <v>-264274.58</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4791,17 +4629,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0DJ2Y1BG6</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>13554.24</v>
       </c>
       <c r="C83" t="n">
-        <v>3982.2</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>3982.2</v>
+        <v>-13554.24</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4812,17 +4650,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0DKJHSD8R</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1439.83</v>
+        <v>162640.68</v>
       </c>
       <c r="C84" t="n">
-        <v>4319.51</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>2879.68</v>
+        <v>-162640.68</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4833,17 +4671,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0DSBN62LR</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>5421.19</v>
+        <v>27108.47</v>
       </c>
       <c r="C85" t="n">
-        <v>7284.75</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>1863.56</v>
+        <v>-27108.47</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4854,17 +4692,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0DSBPCW8R</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>29309.3</v>
+        <v>10588.98</v>
       </c>
       <c r="C86" t="n">
-        <v>34391.51</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>5082.21</v>
+        <v>-10588.98</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4875,17 +4713,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0CR5NKB4C</t>
+          <t>B0DSBPPPJ9</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>8894.92</v>
+        <v>10972.03</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>-8894.92</v>
+        <v>-10972.03</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4896,17 +4734,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0CRCWV9DV</t>
+          <t>B0DSBQCZTK</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27108.47</v>
+        <v>81335.59</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>-27108.47</v>
+        <v>-81335.59</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4917,17 +4755,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0CRCYMKY8</t>
+          <t>B0DSBQDZNV</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>10972.03</v>
+        <v>54216.95</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>-10972.03</v>
+        <v>-54216.95</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4938,17 +4776,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0CRD3QWVJ</t>
+          <t>B0DSBRQNM8</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>10164.41</v>
+        <v>21944.07</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>-10164.41</v>
+        <v>-21944.07</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4959,17 +4797,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0CYMWQCKL</t>
+          <t>B0DSBRWZ8N</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>12283.05</v>
+        <v>22023.73</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>-12283.05</v>
+        <v>-22023.73</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4980,17 +4818,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0CZ8ZKPJ9</t>
+          <t>B0DSBS17RY</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>37952.54</v>
+        <v>36849.15</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>-37952.54</v>
+        <v>-36849.15</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -5001,17 +4839,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0CZ9HTWNC</t>
+          <t>B0DSBSD26P</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>10970.34</v>
+        <v>85981.36</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>-10970.34</v>
+        <v>-85981.36</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -5022,17 +4860,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0DSBSGK17</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>5845.76</v>
+        <v>67771.19</v>
       </c>
       <c r="C94" t="n">
-        <v>8768.639999999999</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>2922.88</v>
+        <v>-67771.19</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -5043,17 +4881,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0DT2KTXK3</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>70748.25999999999</v>
+        <v>14234.75</v>
       </c>
       <c r="C95" t="n">
-        <v>82609.28999999999</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>11861.03</v>
+        <v>-14234.75</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -5064,17 +4902,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0D84YD59Y</t>
+          <t>B0DT2ZQV18</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>10588.14</v>
+        <v>9404.24</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>-10588.14</v>
+        <v>-9404.24</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -5085,17 +4923,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0D84YY632</t>
+          <t>B0DT381WY9</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13554.24</v>
+        <v>9403.389999999999</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>-13554.24</v>
+        <v>-9403.389999999999</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -5106,17 +4944,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0D85171BL</t>
+          <t>B0FCVBY986</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>9316.950000000001</v>
+        <v>11435.59</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>-9316.950000000001</v>
+        <v>-11435.59</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -5127,17 +4965,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0D853Y52R</t>
+          <t>B0FCVHPY4B</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>13553.39</v>
+        <v>7116.1</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>-13553.39</v>
+        <v>-7116.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -5148,17 +4986,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0D854LDQM</t>
+          <t>B0FCVLFLGF</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>67775.42</v>
+        <v>14232.2</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>-67775.42</v>
+        <v>-14232.2</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -5169,17 +5007,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0D8572WTJ</t>
+          <t>B0FCVPBY7Y</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>27108.47</v>
+        <v>294793.22</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>-27108.47</v>
+        <v>-294793.22</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -5190,17 +5028,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0D935VW9J</t>
+          <t>B0FFDJNB8T</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>16014.41</v>
+        <v>8471.190000000001</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>-16014.41</v>
+        <v>-8471.190000000001</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -5211,17 +5049,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0D9362N4Q</t>
+          <t>B0FFDM5QJX</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>34309.32</v>
+        <v>10675.42</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>-34309.32</v>
+        <v>-10675.42</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -5232,17 +5070,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0D9363BB2</t>
+          <t>B0FFHXRJNS</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>15672.88</v>
+        <v>6777.97</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>-15672.88</v>
+        <v>-6777.97</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -5253,17 +5091,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0D93652ZY</t>
+          <t>B0FFJJM7DS</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>194405.08</v>
+        <v>15672.88</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>-194405.08</v>
+        <v>-15672.88</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -5274,17 +5112,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0D9369MTM</t>
+          <t>B0FJ2RND61</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>20328.81</v>
+        <v>33888.14</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>-20328.81</v>
+        <v>-33888.14</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -5295,17 +5133,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0D936GPVL</t>
+          <t>B0FJ2SSSZR</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>80049.14999999999</v>
+        <v>18977.97</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>-80049.14999999999</v>
+        <v>-18977.97</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5316,17 +5154,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0D936YHDH</t>
+          <t>B0FKBV3N4Y</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>11861.02</v>
+        <v>17368.64</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>-11861.02</v>
+        <v>-17368.64</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5337,17 +5175,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0D955L5S7</t>
+          <t>B0FQ8K147H</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>15672.88</v>
+        <v>13641.53</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>-15672.88</v>
+        <v>-13641.53</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5358,17 +5196,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0D955NZTN</t>
+          <t>B0FRVBBDM9</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>16606.78</v>
+        <v>32023.73</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>-16606.78</v>
+        <v>-32023.73</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -5379,17 +5217,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0D955YGX7</t>
+          <t>B0FS5QZRYB</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>12455.08</v>
+        <v>30493.22</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>-12455.08</v>
+        <v>-30493.22</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5400,17 +5238,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0D9564Z9T</t>
+          <t>B0FTK1RVG8</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>24399.15</v>
+        <v>16264.41</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>-24399.15</v>
+        <v>-16264.41</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5421,17 +5259,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0D9573TBX</t>
+          <t>B0FTK7KQ1P</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>41518.64</v>
+        <v>9192.370000000001</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>-41518.64</v>
+        <v>-9192.370000000001</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -5442,17 +5280,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0D9574DPS</t>
+          <t>B0FTL6QH21</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>27444.92</v>
+        <v>16944.92</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>-27444.92</v>
+        <v>-16944.92</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -5463,17 +5301,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0FTML3VHG</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>207569.26</v>
+        <v>34306.78</v>
       </c>
       <c r="C115" t="n">
-        <v>39519.49</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>-168049.77</v>
+        <v>-34306.78</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -5484,17 +5322,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0FTMLYC74</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>54457.64</v>
+        <v>101644.07</v>
       </c>
       <c r="C116" t="n">
-        <v>29823.73</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>-24633.91</v>
+        <v>-101644.07</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -5505,17 +5343,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0FTMM455Z</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>9949.16</v>
+        <v>182983.05</v>
       </c>
       <c r="C117" t="n">
-        <v>4444.07</v>
+        <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>-5505.09</v>
+        <v>-182983.05</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -5526,17 +5364,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0FTMMNCK7</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>41173.94</v>
+        <v>27108.47</v>
       </c>
       <c r="C118" t="n">
-        <v>2783.9</v>
+        <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>-38390.04</v>
+        <v>-27108.47</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -5547,17 +5385,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0DC64BD5R</t>
+          <t>B0FTMRC37L</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>7369.49</v>
+        <v>30495.76</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>-7369.49</v>
+        <v>-30495.76</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -5568,17 +5406,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0DC674ZNR</t>
+          <t>B0GDJPJKSG</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>44217.8</v>
+        <v>29650.85</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>-44217.8</v>
+        <v>-29650.85</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -5589,17 +5427,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0GDJXGF4H</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>20888.13</v>
+        <v>16944.92</v>
       </c>
       <c r="C121" t="n">
-        <v>22751.69</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>1863.56</v>
+        <v>-16944.92</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -5610,17 +5448,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0GF72VQSX</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>27110.17</v>
       </c>
       <c r="C122" t="n">
-        <v>5338.14</v>
+        <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>5338.14</v>
+        <v>-27110.17</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -5631,17 +5469,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B0DJ2V3TH2</t>
+          <t>B0GF73VZZ2</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>11435.59</v>
+        <v>19487.29</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>-11435.59</v>
+        <v>-19487.29</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -5652,17 +5490,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0DJ2VFZWN</t>
+          <t>B0GF7561XM</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>20326.27</v>
+        <v>11012.71</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>-20326.27</v>
+        <v>-11012.71</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -5673,17 +5511,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B0DJ2WKCPD</t>
+          <t>B0GF7BLQ27</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>34309.32</v>
+        <v>50830.51</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>-34309.32</v>
+        <v>-50830.51</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -5694,17 +5532,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0DJ2WP1M5</t>
+          <t>B0GF7BR5NH</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>13894.92</v>
+        <v>22025.42</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>-13894.92</v>
+        <v>-22025.42</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -5715,17 +5553,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0DJ2XHK2N</t>
+          <t>B0GF7GZ4K7</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>264274.58</v>
+        <v>24017.8</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>-264274.58</v>
+        <v>-24017.8</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -5736,17 +5574,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0DJ2Y1BG6</t>
+          <t>B0GF7J5Y4W</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>13554.24</v>
+        <v>12283.9</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>-13554.24</v>
+        <v>-12283.9</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5757,17 +5595,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B0DKJHSD8R</t>
+          <t>B0GF7JSSRF</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>162640.68</v>
+        <v>12283.9</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>-162640.68</v>
+        <v>-12283.9</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5778,17 +5616,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0GF7KPRXB</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>107411.18</v>
+        <v>27110.17</v>
       </c>
       <c r="C130" t="n">
-        <v>1694.07</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>-105717.11</v>
+        <v>-27110.17</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5799,1510 +5637,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0GHDHD4B9</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>29830.51</v>
+        <v>13555.08</v>
       </c>
       <c r="C131" t="n">
-        <v>3143.22</v>
+        <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>-26687.29</v>
+        <v>-13555.08</v>
       </c>
       <c r="E131" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>46802.41</v>
-      </c>
-      <c r="C132" t="n">
-        <v>2592.37</v>
-      </c>
-      <c r="D132" t="n">
-        <v>-44210.04</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>B0DSBN62LR</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>27108.47</v>
-      </c>
-      <c r="C133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" t="n">
-        <v>-27108.47</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>B0DSBPCW8R</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>10588.98</v>
-      </c>
-      <c r="C134" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" t="n">
-        <v>-10588.98</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>B0DSBPPPJ9</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>10972.03</v>
-      </c>
-      <c r="C135" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" t="n">
-        <v>-10972.03</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>B0DSBQCZTK</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>81335.59</v>
-      </c>
-      <c r="C136" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" t="n">
-        <v>-81335.59</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>B0DSBQDZNV</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>54216.95</v>
-      </c>
-      <c r="C137" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" t="n">
-        <v>-54216.95</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>B0DSBRQNM8</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>21944.07</v>
-      </c>
-      <c r="C138" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" t="n">
-        <v>-21944.07</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>B0DSBRWZ8N</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>22023.73</v>
-      </c>
-      <c r="C139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" t="n">
-        <v>-22023.73</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>B0DSBS17RY</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>36849.15</v>
-      </c>
-      <c r="C140" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-36849.15</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>B0DSBSD26P</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>85981.36</v>
-      </c>
-      <c r="C141" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-85981.36</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>B0DSBSGK17</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>67771.19</v>
-      </c>
-      <c r="C142" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-67771.19</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>B0DT2KTXK3</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>14234.75</v>
-      </c>
-      <c r="C143" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-14234.75</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>B0DT2ZQV18</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>9404.24</v>
-      </c>
-      <c r="C144" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-9404.24</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>B0DT381WY9</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>9403.389999999999</v>
-      </c>
-      <c r="C145" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" t="n">
-        <v>-9403.389999999999</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>B0DT6T6N6B</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>32234.63</v>
-      </c>
-      <c r="C146" t="n">
-        <v>38833.77</v>
-      </c>
-      <c r="D146" t="n">
-        <v>6599.14</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>B0DXFPM4N2</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>501024.49</v>
-      </c>
-      <c r="C147" t="n">
-        <v>532048.21</v>
-      </c>
-      <c r="D147" t="n">
-        <v>31023.72</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>B0FCVBY986</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>11435.59</v>
-      </c>
-      <c r="C148" t="n">
-        <v>0</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-11435.59</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>B0FCVHPY4B</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>7116.1</v>
-      </c>
-      <c r="C149" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-7116.1</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>B0FCVLFLGF</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>14232.2</v>
-      </c>
-      <c r="C150" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-14232.2</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>B0FCVPBY7Y</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>294793.22</v>
-      </c>
-      <c r="C151" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-294793.22</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>B0FFB6YJM1</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>30506.74</v>
-      </c>
-      <c r="C152" t="n">
-        <v>33682.17</v>
-      </c>
-      <c r="D152" t="n">
-        <v>3175.43</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>B0FFDJNB8T</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>8471.190000000001</v>
-      </c>
-      <c r="C153" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" t="n">
-        <v>-8471.190000000001</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>B0FFDM5QJX</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>10675.42</v>
-      </c>
-      <c r="C154" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" t="n">
-        <v>-10675.42</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>B0FFHXRJNS</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>6777.97</v>
-      </c>
-      <c r="C155" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" t="n">
-        <v>-6777.97</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>B0FFJJM7DS</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>15672.88</v>
-      </c>
-      <c r="C156" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" t="n">
-        <v>-15672.88</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>B0FG88HVQ8</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>150455.37</v>
-      </c>
-      <c r="C157" t="n">
-        <v>160955.37</v>
-      </c>
-      <c r="D157" t="n">
-        <v>10500</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>B0FJ2K95XT</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>4490.68</v>
-      </c>
-      <c r="C158" t="n">
-        <v>0</v>
-      </c>
-      <c r="D158" t="n">
-        <v>-4490.68</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>B0FJ2RND61</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>33888.14</v>
-      </c>
-      <c r="C159" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" t="n">
-        <v>-33888.14</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>B0FJ2SSSZR</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>18977.97</v>
-      </c>
-      <c r="C160" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" t="n">
-        <v>-18977.97</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>B0FJ8PZ9H7</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>0</v>
-      </c>
-      <c r="C161" t="n">
-        <v>11694.07</v>
-      </c>
-      <c r="D161" t="n">
-        <v>11694.07</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>B0FJ8TSQK1</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>15934.73</v>
-      </c>
-      <c r="C162" t="n">
-        <v>26609.29</v>
-      </c>
-      <c r="D162" t="n">
-        <v>10674.56</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>B0FKBV3N4Y</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>17368.64</v>
-      </c>
-      <c r="C163" t="n">
-        <v>0</v>
-      </c>
-      <c r="D163" t="n">
-        <v>-17368.64</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>B0FN7B3KWS</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>50758.46</v>
-      </c>
-      <c r="C164" t="n">
-        <v>61774.56</v>
-      </c>
-      <c r="D164" t="n">
-        <v>11016.1</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>B0FQ8K147H</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>13641.53</v>
-      </c>
-      <c r="C165" t="n">
-        <v>0</v>
-      </c>
-      <c r="D165" t="n">
-        <v>-13641.53</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>B0FQBTRM28</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>4966.94</v>
-      </c>
-      <c r="C166" t="n">
-        <v>6661.01</v>
-      </c>
-      <c r="D166" t="n">
-        <v>1694.07</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>B0FQBX8J17</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>25042.28</v>
-      </c>
-      <c r="C167" t="n">
-        <v>26288.89</v>
-      </c>
-      <c r="D167" t="n">
-        <v>1246.61</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>B0FQBXS6Y2</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>86975.24000000001</v>
-      </c>
-      <c r="C168" t="n">
-        <v>91511.69</v>
-      </c>
-      <c r="D168" t="n">
-        <v>4536.45</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>B0FRVBBDM9</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>32023.73</v>
-      </c>
-      <c r="C169" t="n">
-        <v>0</v>
-      </c>
-      <c r="D169" t="n">
-        <v>-32023.73</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>B0FS5QZRYB</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>30493.22</v>
-      </c>
-      <c r="C170" t="n">
-        <v>0</v>
-      </c>
-      <c r="D170" t="n">
-        <v>-30493.22</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>B0FTK1RVG8</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>16264.41</v>
-      </c>
-      <c r="C171" t="n">
-        <v>0</v>
-      </c>
-      <c r="D171" t="n">
-        <v>-16264.41</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>B0FTK7KQ1P</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>9192.370000000001</v>
-      </c>
-      <c r="C172" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" t="n">
-        <v>-9192.370000000001</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>B0FTL6QH21</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>16944.92</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" t="n">
-        <v>-16944.92</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>B0FTML3VHG</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>34306.78</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" t="n">
-        <v>-34306.78</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>B0FTMLYC74</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>101644.07</v>
-      </c>
-      <c r="C175" t="n">
-        <v>0</v>
-      </c>
-      <c r="D175" t="n">
-        <v>-101644.07</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>B0FTMM455Z</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>182983.05</v>
-      </c>
-      <c r="C176" t="n">
-        <v>0</v>
-      </c>
-      <c r="D176" t="n">
-        <v>-182983.05</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>B0FTMMNCK7</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>27108.47</v>
-      </c>
-      <c r="C177" t="n">
-        <v>0</v>
-      </c>
-      <c r="D177" t="n">
-        <v>-27108.47</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>B0FTMRC37L</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>30495.76</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0</v>
-      </c>
-      <c r="D178" t="n">
-        <v>-30495.76</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>B0FTVQQVDC</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>65831.36</v>
-      </c>
-      <c r="C179" t="n">
-        <v>82778.82000000001</v>
-      </c>
-      <c r="D179" t="n">
-        <v>16947.46</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>B0G39ZHDYP</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>37011.87</v>
-      </c>
-      <c r="C180" t="n">
-        <v>40060.17</v>
-      </c>
-      <c r="D180" t="n">
-        <v>3048.3</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>B0G3B152FR</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>41560.99</v>
-      </c>
-      <c r="C181" t="n">
-        <v>44779.63</v>
-      </c>
-      <c r="D181" t="n">
-        <v>3218.64</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>B0G4DNF8RZ</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>24321.17</v>
-      </c>
-      <c r="C182" t="n">
-        <v>27116.93</v>
-      </c>
-      <c r="D182" t="n">
-        <v>2795.76</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>B0G53H49BS</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>140146.87</v>
-      </c>
-      <c r="C183" t="n">
-        <v>152735.87</v>
-      </c>
-      <c r="D183" t="n">
-        <v>12589</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>B0GDJPJKSG</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>29650.85</v>
-      </c>
-      <c r="C184" t="n">
-        <v>0</v>
-      </c>
-      <c r="D184" t="n">
-        <v>-29650.85</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>B0GDJXGF4H</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>16944.92</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0</v>
-      </c>
-      <c r="D185" t="n">
-        <v>-16944.92</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>B0GF72VQSX</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>27110.17</v>
-      </c>
-      <c r="C186" t="n">
-        <v>0</v>
-      </c>
-      <c r="D186" t="n">
-        <v>-27110.17</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>B0GF73VZZ2</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>19487.29</v>
-      </c>
-      <c r="C187" t="n">
-        <v>0</v>
-      </c>
-      <c r="D187" t="n">
-        <v>-19487.29</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>B0GF7561XM</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>11012.71</v>
-      </c>
-      <c r="C188" t="n">
-        <v>0</v>
-      </c>
-      <c r="D188" t="n">
-        <v>-11012.71</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>B0GF7BLQ27</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>50830.51</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0</v>
-      </c>
-      <c r="D189" t="n">
-        <v>-50830.51</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>B0GF7BR5NH</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>22025.42</v>
-      </c>
-      <c r="C190" t="n">
-        <v>0</v>
-      </c>
-      <c r="D190" t="n">
-        <v>-22025.42</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>B0GF7GZ4K7</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>24017.8</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0</v>
-      </c>
-      <c r="D191" t="n">
-        <v>-24017.8</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>B0GF7J5Y4W</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>12283.9</v>
-      </c>
-      <c r="C192" t="n">
-        <v>0</v>
-      </c>
-      <c r="D192" t="n">
-        <v>-12283.9</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>B0GF7JSSRF</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>12283.9</v>
-      </c>
-      <c r="C193" t="n">
-        <v>0</v>
-      </c>
-      <c r="D193" t="n">
-        <v>-12283.9</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>B0GF7KPRXB</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>27110.17</v>
-      </c>
-      <c r="C194" t="n">
-        <v>0</v>
-      </c>
-      <c r="D194" t="n">
-        <v>-27110.17</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>B0GHDHD4B9</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>13555.08</v>
-      </c>
-      <c r="C195" t="n">
-        <v>0</v>
-      </c>
-      <c r="D195" t="n">
-        <v>-13555.08</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>B0GKPXQ8G3</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>5761.02</v>
-      </c>
-      <c r="C196" t="n">
-        <v>8641.52</v>
-      </c>
-      <c r="D196" t="n">
-        <v>2880.5</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>B0GN2LHJY4</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>52327.97</v>
-      </c>
-      <c r="C197" t="n">
-        <v>59954.24</v>
-      </c>
-      <c r="D197" t="n">
-        <v>7626.27</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>B0GN8MPYPG</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>0</v>
-      </c>
-      <c r="C198" t="n">
-        <v>9320.34</v>
-      </c>
-      <c r="D198" t="n">
-        <v>9320.34</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>369199.78</v>
-      </c>
-      <c r="C199" t="n">
-        <v>401615.04</v>
-      </c>
-      <c r="D199" t="n">
-        <v>32415.26</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>B0GW8ZQRFK</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>0</v>
-      </c>
-      <c r="C200" t="n">
-        <v>1355.08</v>
-      </c>
-      <c r="D200" t="n">
-        <v>1355.08</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>B0GW92316G</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>0</v>
-      </c>
-      <c r="C201" t="n">
-        <v>6778.81</v>
-      </c>
-      <c r="D201" t="n">
-        <v>6778.81</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>B0GXP97CZG</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>41368.64</v>
-      </c>
-      <c r="C202" t="n">
-        <v>38149.15</v>
-      </c>
-      <c r="D202" t="n">
-        <v>-3219.49</v>
-      </c>
-      <c r="E202" t="inlineStr">
         <is>
           <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
         </is>
@@ -7319,31 +5666,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>raw_file_spend</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ams_trend_spend</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7352,21 +5679,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(load failed)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>clean — Cross-route ads rule consistency</t>
         </is>
       </c>
     </row>
@@ -7381,31 +5694,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>file_sessions</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ams_trend_sessions</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7414,21 +5707,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(load failed)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>clean — Cross-route sessions consistency</t>
         </is>
       </c>
     </row>
@@ -7443,31 +5722,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>sales_trend_units</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ams_trend_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -7980,17 +6259,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B08QVCPDVT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -8001,7 +6280,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B08QVCPDVT</t>
+          <t>B09NC2NFR9</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -8022,7 +6301,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B09NC2NFR9</t>
+          <t>B09SHQSHBF</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -8043,17 +6322,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B09SHQSHBF</t>
+          <t>B0CHXGWVZJ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -8064,17 +6343,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0CRCWV9DV</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>190</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>-2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -8085,17 +6364,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0CZ8ZKPJ9</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -8106,17 +6385,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0D854LDQM</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -8127,17 +6406,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0D8572WTJ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -8148,17 +6427,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0D9362N4Q</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -8169,17 +6448,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0D93652ZY</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="C35" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>-17</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -8190,17 +6469,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0D9369MTM</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -8211,17 +6490,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0D936GPVL</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -8232,17 +6511,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0D955NZTN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -8253,17 +6532,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0D9564Z9T</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -8274,17 +6553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0D9573TBX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -8295,17 +6574,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0D9574DPS</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -8316,17 +6595,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0CHXGWVZJ</t>
+          <t>B0DC674ZNR</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -8337,17 +6616,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0DJ2VFZWN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -8358,17 +6637,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0DJ2WKCPD</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -8379,17 +6658,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0DJ2XHK2N</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>-26</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -8400,17 +6679,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0DKJHSD8R</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C46" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>-12</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -8421,7 +6700,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0CRCWV9DV</t>
+          <t>B0DSBN62LR</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -8442,7 +6721,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0CZ8ZKPJ9</t>
+          <t>B0DSBQCZTK</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -8463,17 +6742,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0DSBQDZNV</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -8484,17 +6763,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0D854LDQM</t>
+          <t>B0DSBRQNM8</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -8505,7 +6784,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0D8572WTJ</t>
+          <t>B0DSBRWZ8N</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -8526,7 +6805,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0D9362N4Q</t>
+          <t>B0DSBS17RY</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -8547,17 +6826,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0D93652ZY</t>
+          <t>B0DSBSD26P</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>-17</v>
+        <v>-7</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -8568,17 +6847,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0D9369MTM</t>
+          <t>B0DSBSGK17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -8589,17 +6868,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0D936GPVL</t>
+          <t>B0FCVLFLGF</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -8610,17 +6889,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0D955NZTN</t>
+          <t>B0FCVPBY7Y</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>-2</v>
+        <v>-25</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -8631,17 +6910,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0D9564Z9T</t>
+          <t>B0FJ2RND61</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -8652,17 +6931,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0D9573TBX</t>
+          <t>B0FJ2SSSZR</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -8673,17 +6952,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0D9574DPS</t>
+          <t>B0FRVBBDM9</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -8694,17 +6973,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0FS5QZRYB</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="C60" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>-76</v>
+        <v>-3</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -8715,17 +6994,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0FTK1RVG8</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -8736,17 +7015,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0FTML3VHG</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -8757,17 +7036,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0FTMLYC74</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>-23</v>
+        <v>-10</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -8778,17 +7057,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0DC674ZNR</t>
+          <t>B0FTMM455Z</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>-6</v>
+        <v>-16</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -8799,17 +7078,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0DJ2VFZWN</t>
+          <t>B0FTMMNCK7</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -8820,7 +7099,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0DJ2WKCPD</t>
+          <t>B0FTMRC37L</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -8841,17 +7120,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0DJ2XHK2N</t>
+          <t>B0GDJPJKSG</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>-26</v>
+        <v>-2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -8862,17 +7141,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0DKJHSD8R</t>
+          <t>B0GF72VQSX</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -8883,17 +7162,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0GF7BLQ27</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>-64</v>
+        <v>-4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -8904,17 +7183,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0GF7BR5NH</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -8925,17 +7204,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0GF7GZ4K7</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -8946,7 +7225,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0DSBN62LR</t>
+          <t>B0GF7KPRXB</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -8959,783 +7238,6 @@
         <v>-2</v>
       </c>
       <c r="E72" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>B0DSBQCZTK</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>4</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>B0DSBQDZNV</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>4</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>B0DSBRQNM8</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>2</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>B0DSBRWZ8N</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>B0DSBS17RY</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>3</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>B0DSBSD26P</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>7</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="n">
-        <v>-7</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>B0DSBSGK17</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>5</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>B0DT6T6N6B</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>69</v>
-      </c>
-      <c r="C80" t="n">
-        <v>82</v>
-      </c>
-      <c r="D80" t="n">
-        <v>13</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>B0DXFPM4N2</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>69</v>
-      </c>
-      <c r="C81" t="n">
-        <v>73</v>
-      </c>
-      <c r="D81" t="n">
-        <v>4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>B0FCVLFLGF</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>2</v>
-      </c>
-      <c r="C82" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>B0FCVPBY7Y</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>25</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="n">
-        <v>-25</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>B0FFB6YJM1</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>29</v>
-      </c>
-      <c r="C84" t="n">
-        <v>32</v>
-      </c>
-      <c r="D84" t="n">
-        <v>3</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>B0FG88HVQ8</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>92</v>
-      </c>
-      <c r="C85" t="n">
-        <v>98</v>
-      </c>
-      <c r="D85" t="n">
-        <v>6</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>B0FJ2RND61</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>2</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>B0FJ2SSSZR</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>2</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>B0FJ8TSQK1</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>6</v>
-      </c>
-      <c r="C88" t="n">
-        <v>10</v>
-      </c>
-      <c r="D88" t="n">
-        <v>4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>B0FQBXS6Y2</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>72</v>
-      </c>
-      <c r="C89" t="n">
-        <v>75</v>
-      </c>
-      <c r="D89" t="n">
-        <v>3</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>B0FRVBBDM9</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>4</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>B0FS5QZRYB</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>3</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>B0FTK1RVG8</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>2</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>B0FTML3VHG</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>3</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>B0FTMLYC74</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>10</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="n">
-        <v>-10</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>B0FTMM455Z</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-16</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>B0FTMMNCK7</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>2</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>B0FTMRC37L</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>3</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>B0FTVQQVDC</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>8</v>
-      </c>
-      <c r="C98" t="n">
-        <v>10</v>
-      </c>
-      <c r="D98" t="n">
-        <v>2</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>B0G39ZHDYP</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>38</v>
-      </c>
-      <c r="C99" t="n">
-        <v>41</v>
-      </c>
-      <c r="D99" t="n">
-        <v>3</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>B0G3B152FR</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>26</v>
-      </c>
-      <c r="C100" t="n">
-        <v>28</v>
-      </c>
-      <c r="D100" t="n">
-        <v>2</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>B0G53H49BS</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>61</v>
-      </c>
-      <c r="C101" t="n">
-        <v>66</v>
-      </c>
-      <c r="D101" t="n">
-        <v>5</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>B0GDJPJKSG</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>2</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>B0GF72VQSX</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>2</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>B0GF7BLQ27</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>4</v>
-      </c>
-      <c r="C104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>B0GF7BR5NH</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>2</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>B0GF7GZ4K7</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>3</v>
-      </c>
-      <c r="C106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>B0GF7KPRXB</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>2</v>
-      </c>
-      <c r="C107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>B0GN8MPYPG</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>0</v>
-      </c>
-      <c r="C108" t="n">
-        <v>2</v>
-      </c>
-      <c r="D108" t="n">
-        <v>2</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>61</v>
-      </c>
-      <c r="C109" t="n">
-        <v>66</v>
-      </c>
-      <c r="D109" t="n">
-        <v>5</v>
-      </c>
-      <c r="E109" t="inlineStr">
         <is>
           <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
         </is>
@@ -9752,31 +7254,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>snap_total_sales</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>am1p_route_sales</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -9785,21 +7267,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(load failed)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>clean — Cross-route per-brand totals consistency</t>
         </is>
       </c>
     </row>
@@ -9818,7 +7286,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -9842,665 +7310,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sales_gmv</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ams_gmv</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pct</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AI-04 RED</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>524967</v>
-      </c>
-      <c r="E2" t="n">
-        <v>609696</v>
-      </c>
-      <c r="F2" t="n">
-        <v>84729</v>
-      </c>
-      <c r="G2" t="n">
-        <v>16.1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AM-C1</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>418103</v>
-      </c>
-      <c r="E3" t="n">
-        <v>460070</v>
-      </c>
-      <c r="F3" t="n">
-        <v>41967</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AM-S2</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>369200</v>
-      </c>
-      <c r="E4" t="n">
-        <v>401615</v>
-      </c>
-      <c r="F4" t="n">
-        <v>32415</v>
-      </c>
-      <c r="G4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AM-S1</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>530258</v>
-      </c>
-      <c r="E5" t="n">
-        <v>561282</v>
-      </c>
-      <c r="F5" t="n">
-        <v>31024</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AA-21</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>125436</v>
-      </c>
-      <c r="E6" t="n">
-        <v>152060</v>
-      </c>
-      <c r="F6" t="n">
-        <v>26624</v>
-      </c>
-      <c r="G6" t="n">
-        <v>21.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>65831</v>
-      </c>
-      <c r="E7" t="n">
-        <v>82779</v>
-      </c>
-      <c r="F7" t="n">
-        <v>16947</v>
-      </c>
-      <c r="G7" t="n">
-        <v>25.7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>28</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AA-19</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>100531</v>
-      </c>
-      <c r="E8" t="n">
-        <v>114053</v>
-      </c>
-      <c r="F8" t="n">
-        <v>13522</v>
-      </c>
-      <c r="G8" t="n">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>28</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AI-13</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>144637</v>
-      </c>
-      <c r="E9" t="n">
-        <v>157226</v>
-      </c>
-      <c r="F9" t="n">
-        <v>12589</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AM-C46</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>70748</v>
-      </c>
-      <c r="E10" t="n">
-        <v>82609</v>
-      </c>
-      <c r="F10" t="n">
-        <v>11861</v>
-      </c>
-      <c r="G10" t="n">
-        <v>16.8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>28</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PB-04 (AI-04 RED + AM-C44 X 2)</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>11694</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11694</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1169407</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>28</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>50758</v>
-      </c>
-      <c r="E12" t="n">
-        <v>61775</v>
-      </c>
-      <c r="F12" t="n">
-        <v>11016</v>
-      </c>
-      <c r="G12" t="n">
-        <v>21.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>28</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>15935</v>
-      </c>
-      <c r="E13" t="n">
-        <v>26609</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10675</v>
-      </c>
-      <c r="G13" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>28</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AH-50</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>150455</v>
-      </c>
-      <c r="E14" t="n">
-        <v>160955</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10500</v>
-      </c>
-      <c r="G14" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>28</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AK-61 PRO</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>9320</v>
-      </c>
-      <c r="F15" t="n">
-        <v>9320</v>
-      </c>
-      <c r="G15" t="n">
-        <v>932034</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>28</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AM-C43</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>41914</v>
-      </c>
-      <c r="E16" t="n">
-        <v>50385</v>
-      </c>
-      <c r="F16" t="n">
-        <v>8471</v>
-      </c>
-      <c r="G16" t="n">
-        <v>20.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>28</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MT-12</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>52328</v>
-      </c>
-      <c r="E17" t="n">
-        <v>59954</v>
-      </c>
-      <c r="F17" t="n">
-        <v>7626</v>
-      </c>
-      <c r="G17" t="n">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>28</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tonor</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TM20</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>29880</v>
-      </c>
-      <c r="E18" t="n">
-        <v>37504</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7625</v>
-      </c>
-      <c r="G18" t="n">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>28</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AM-W36 PRO</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>6779</v>
-      </c>
-      <c r="F19" t="n">
-        <v>6779</v>
-      </c>
-      <c r="G19" t="n">
-        <v>677881</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>28</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AI-03</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3219</v>
-      </c>
-      <c r="E20" t="n">
-        <v>9997</v>
-      </c>
-      <c r="F20" t="n">
-        <v>6778</v>
-      </c>
-      <c r="G20" t="n">
-        <v>210.5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>28</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AA-26</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>32235</v>
-      </c>
-      <c r="E21" t="n">
-        <v>38834</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6599</v>
-      </c>
-      <c r="G21" t="n">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>28</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AM-W14</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>46924</v>
-      </c>
-      <c r="E22" t="n">
-        <v>52262</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5338</v>
-      </c>
-      <c r="G22" t="n">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>28</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AM-W36</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5338</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5338</v>
-      </c>
-      <c r="G23" t="n">
-        <v>533814</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>28</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Tonor</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TD310</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>29309</v>
-      </c>
-      <c r="E24" t="n">
-        <v>34392</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5082</v>
-      </c>
-      <c r="G24" t="n">
-        <v>17.3</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — AMS Trend GMV &gt; Sales Trend GMV (per brand×model×wk)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -10518,32 +7342,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -10562,14 +7386,14 @@
         <v>181329</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>181329</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -10583,17 +7407,17 @@
         <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>173571</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>173571</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -10608,26 +7432,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>child</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>lag_sec</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -10636,20 +7445,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>data\processed\weekly_sales_snapshot.csv</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>data\ams_weekly_data\ams_weekly_fact\ams_weekly_fact.csv</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>weekly_sales_snapshot → ams_weekly_fact (biz_ads_weekly_etl needs re-run)</t>
+          <t>clean — Derivative snapshot stale vs parent (re-run needed)</t>
         </is>
       </c>
     </row>
@@ -10664,36 +7460,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>prior_4w_median</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -10702,104 +7498,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ad_spend</t>
+          <t>attributed</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2499168</v>
       </c>
       <c r="D2" t="n">
-        <v>445071</v>
+        <v>841594</v>
       </c>
       <c r="E2" t="n">
-        <v>-100</v>
+        <v>197</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2654878</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>264619</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>841594</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
+          <t>SPIKE &gt; 2x vs prior 4-week median</t>
         </is>
       </c>
     </row>
@@ -10818,7 +7536,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -10846,7 +7564,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -10870,31 +7588,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sales_trend_amz_side</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ams_trend_gmv</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -10903,63 +7601,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>4281008.83</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4726879.23</v>
-      </c>
-      <c r="D2" t="n">
-        <v>445870.4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>287987.11</v>
-      </c>
-      <c r="C3" t="n">
-        <v>312502.37</v>
-      </c>
-      <c r="D3" t="n">
-        <v>24515.26</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1158683.09</v>
-      </c>
-      <c r="C4" t="n">
-        <v>745489.84</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-413193.25</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
+          <t>clean — AMS Trend GMV vs Sales Trend Amazon-side per brand</t>
         </is>
       </c>
     </row>
@@ -10978,7 +7620,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -11006,7 +7648,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -11030,41 +7672,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sales_trend_amz_side</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ams_trend_gmv</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta_rs</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -11247,85 +7889,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4281008.83</v>
+        <v>624059.3199999999</v>
       </c>
       <c r="D8" t="n">
-        <v>4726879.23</v>
+        <v>743727.1</v>
       </c>
       <c r="E8" t="n">
-        <v>445870.4</v>
+        <v>119667.78</v>
       </c>
       <c r="F8" t="n">
-        <v>10.42</v>
+        <v>19.18</v>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>W28</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>287987.11</v>
-      </c>
-      <c r="D9" t="n">
-        <v>312502.37</v>
-      </c>
-      <c r="E9" t="n">
-        <v>24515.26</v>
-      </c>
-      <c r="F9" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>W28</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1158683.09</v>
-      </c>
-      <c r="D10" t="n">
-        <v>745489.84</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-413193.25</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-35.66</v>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
         </is>
@@ -11342,31 +7926,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>rule</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>week_num</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -11375,23 +7939,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ams_trend.inventory_snapshot (load failed)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>clean — Never-Zero column regression</t>
         </is>
       </c>
     </row>
@@ -11410,7 +7958,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -11434,36 +7982,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -11472,26 +8020,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ad_spend</t>
+          <t>inventory_units</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1259780.88</v>
+        <v>6000</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -11500,168 +8048,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>1p sales</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>attributed_sales</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7168235.189999999</v>
+        <v>330</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>877425.63</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>attributed_sales</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3402509.54</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>33762.36</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>attributed_sales</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>281657.64</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11680,22 +8088,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -11980,7 +8388,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -12004,11 +8412,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -12017,7 +8440,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand missing from a layer (diagnostic)</t>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in sales for W28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in sales for W28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in sales for W28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in sales for W28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in inventory for W28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>28</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in inventory for W28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>28</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in inventory for W28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>28</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in inventory for W28</t>
         </is>
       </c>
     </row>
@@ -12036,32 +8612,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -583,10 +583,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>15384</v>
+        <v>15463</v>
       </c>
       <c r="E6" t="n">
-        <v>15384</v>
+        <v>15463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -903,21 +903,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sales_gmv</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ams_gmv</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>clean — AMS Trend GMV &gt; Sales Trend GMV (per brand×model×wk)</t>
-        </is>
+      <c r="A2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MS1ML</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5082</v>
+      </c>
+      <c r="E2" t="n">
+        <v>79621</v>
+      </c>
+      <c r="F2" t="n">
+        <v>74539</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1466.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>WM-GS1M-BK</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>48288</v>
+      </c>
+      <c r="E3" t="n">
+        <v>78574</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30286</v>
+      </c>
+      <c r="G3" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HDWF1ML</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2711</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21037</v>
+      </c>
+      <c r="F4" t="n">
+        <v>18326</v>
+      </c>
+      <c r="G4" t="n">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WM-HA2M-BK</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>34419</v>
+      </c>
+      <c r="E5" t="n">
+        <v>44583</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10164</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29.5</v>
       </c>
     </row>
   </sheetData>
@@ -976,10 +1107,10 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>188748</v>
+        <v>188822</v>
       </c>
       <c r="D2" t="n">
-        <v>188748</v>
+        <v>188822</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1000,10 +1131,10 @@
         <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>181336</v>
+        <v>181410</v>
       </c>
       <c r="D3" t="n">
-        <v>181336</v>
+        <v>181410</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1053,37 +1184,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>latest</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>prior_4w_median</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>delta_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -1091,182 +1197,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>445943</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2670067</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>317967</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1343381</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tonor</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>103896</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>123583</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>587144</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
+          <t>clean — Brand metric &gt; 50% drop or 2x spike vs prior 4w median</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1914,252 +1845,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ad_spend</t>
+          <t>inventory_units</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1322251.4</v>
+        <v>4000</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>attributed_sales</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>7852700.710000001</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1134692.94</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>attributed_sales</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4934237.560000001</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>45825.99</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>attributed_sales</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>335188.89</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>418447.745</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>attributed_sales</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1687832.525</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4623,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>3263</v>
+        <v>3278</v>
       </c>
       <c r="F80" t="n">
-        <v>3263</v>
+        <v>3278</v>
       </c>
     </row>
     <row r="81">
@@ -4647,10 +4354,10 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>6368</v>
+        <v>6363</v>
       </c>
       <c r="F81" t="n">
-        <v>6368</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="82">
@@ -4671,10 +4378,10 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10590</v>
+        <v>10652</v>
       </c>
       <c r="F82" t="n">
-        <v>10590</v>
+        <v>10652</v>
       </c>
     </row>
     <row r="83">
@@ -4719,10 +4426,10 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="F84" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -583,10 +583,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>15463</v>
+        <v>15637</v>
       </c>
       <c r="E6" t="n">
-        <v>15463</v>
+        <v>15637</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>188822</v>
+        <v>188956</v>
       </c>
       <c r="D2" t="n">
-        <v>188822</v>
+        <v>188956</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1131,10 +1131,10 @@
         <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>181410</v>
+        <v>181544</v>
       </c>
       <c r="D3" t="n">
-        <v>181410</v>
+        <v>181544</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>3278</v>
+        <v>3338</v>
       </c>
       <c r="F80" t="n">
-        <v>3278</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="81">
@@ -4354,10 +4354,10 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>6363</v>
+        <v>6323</v>
       </c>
       <c r="F81" t="n">
-        <v>6363</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="82">
@@ -4378,10 +4378,10 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10652</v>
+        <v>10739</v>
       </c>
       <c r="F82" t="n">
-        <v>10652</v>
+        <v>10739</v>
       </c>
     </row>
     <row r="83">
@@ -4402,10 +4402,10 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F83" t="n">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="84">
@@ -4426,10 +4426,10 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>1142</v>
+        <v>1164</v>
       </c>
       <c r="F84" t="n">
-        <v>1142</v>
+        <v>1164</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,39 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,13 +43,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -60,7 +63,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -68,12 +71,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,32 +455,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -609,32 +621,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -683,7 +695,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -707,21 +719,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>amazon+1p_inventory</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_total_amazon</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sales_trend_inv</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>inv_dashboard_total</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route inventory rule consistency</t>
-        </is>
+          <t>amazon+1p_vs_ams_trend</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales_trend_vs_inv_dashboard</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -735,11 +831,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sales_trend_amzn+1p_gmv</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_gmv</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -748,7 +864,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-source sales drift (diagnostic)</t>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>90222.02</v>
+      </c>
+      <c r="C2" t="n">
+        <v>48288.14</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-41933.88</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>48294.07</v>
+      </c>
+      <c r="C3" t="n">
+        <v>41007.63</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-7286.44</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4192.38</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-4192.38</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>56441.54</v>
+      </c>
+      <c r="C5" t="n">
+        <v>34418.64</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-22022.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>94867.73</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5082.21</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-89785.52</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>28245.76</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27957.63</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-288.13</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>34168.34</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2711.02</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-31457.32</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
         </is>
       </c>
     </row>
@@ -763,11 +1019,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_file_spend</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_spend</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -776,7 +1052,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route ads rule consistency</t>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -791,11 +1081,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>file_sessions</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_sessions</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -804,7 +1114,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route sessions consistency</t>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -819,11 +1143,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sales_trend_units</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_units</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -832,7 +1176,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-source units drift (diagnostic)</t>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41954.88</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41915.88</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7297.44</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7284.44</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4192.38</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4189.38</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C5" t="n">
+        <v>22038.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>22009.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>56</v>
+      </c>
+      <c r="C6" t="n">
+        <v>89788.52</v>
+      </c>
+      <c r="D6" t="n">
+        <v>89732.52</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="n">
+        <v>298.13</v>
+      </c>
+      <c r="D7" t="n">
+        <v>288.13</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" t="n">
+        <v>31458.32</v>
+      </c>
+      <c r="D8" t="n">
+        <v>31445.32</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
         </is>
       </c>
     </row>
@@ -847,11 +1331,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>snap_total_sales</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>am1p_route_sales</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -860,7 +1364,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-route per-brand totals consistency</t>
+          <t>(load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -879,7 +1397,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -903,152 +1421,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>sales_gmv</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ams_gmv</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>pct</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MS1ML</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>5082</v>
-      </c>
-      <c r="E2" t="n">
-        <v>79621</v>
-      </c>
-      <c r="F2" t="n">
-        <v>74539</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1466.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>WM-GS1M-BK</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>48288</v>
-      </c>
-      <c r="E3" t="n">
-        <v>78574</v>
-      </c>
-      <c r="F3" t="n">
-        <v>30286</v>
-      </c>
-      <c r="G3" t="n">
-        <v>62.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HDWF1ML</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2711</v>
-      </c>
-      <c r="E4" t="n">
-        <v>21037</v>
-      </c>
-      <c r="F4" t="n">
-        <v>18326</v>
-      </c>
-      <c r="G4" t="n">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>WM-HA2M-BK</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>34419</v>
-      </c>
-      <c r="E5" t="n">
-        <v>44583</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10164</v>
-      </c>
-      <c r="G5" t="n">
-        <v>29.5</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — AMS Trend GMV &gt; Sales Trend GMV (per brand×model×wk)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1066,32 +1453,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1110,14 +1497,14 @@
         <v>188956</v>
       </c>
       <c r="D2" t="n">
-        <v>188956</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -1131,17 +1518,17 @@
         <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>181544</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>181544</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1547,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1188,7 +1575,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1216,7 +1603,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1244,7 +1631,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1268,11 +1655,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sales_trend_amz_side</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ams_trend_gmv</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1281,7 +1688,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — AMS Trend GMV vs Sales Trend Amazon-side per brand</t>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>908097.08</v>
+      </c>
+      <c r="C2" t="n">
+        <v>711130.51</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-196966.57</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1721,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1328,7 +1749,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1352,41 +1773,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sales_trend_amz_side</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ams_trend_gmv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta_rs</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1607,16 +2028,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>624059.3199999999</v>
+        <v>750505.91</v>
       </c>
       <c r="D9" t="n">
         <v>699655.0600000001</v>
       </c>
       <c r="E9" t="n">
-        <v>75595.74000000001</v>
+        <v>-50850.85</v>
       </c>
       <c r="F9" t="n">
-        <v>12.11</v>
+        <v>-6.78</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1735,6 +2156,35 @@
         <v>-2.25</v>
       </c>
       <c r="G13" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>W29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>908097.08</v>
+      </c>
+      <c r="D14" t="n">
+        <v>711130.51</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-196966.57</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-21.69</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
         </is>
@@ -1751,11 +2201,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>week_num</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1764,7 +2234,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Never-Zero column regression</t>
+          <t>ams_trend.inventory_snapshot (load failed)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
         </is>
       </c>
     </row>
@@ -1783,7 +2269,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1811,32 +2297,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1885,22 +2371,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -2185,7 +2671,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2209,26 +2695,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2237,160 +2708,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in sales for W29</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>29</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in sales for W29</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>29</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in sales for W29</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>29</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in sales for W29</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>29</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in inventory for W29</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>29</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in inventory for W29</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>29</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in inventory for W29</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>29</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W29</t>
+          <t>clean — Brand missing from a layer (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -2409,32 +2727,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -831,32 +831,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sales_trend_amzn+1p_gmv</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ams_trend_gmv</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -864,147 +844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>90222.02</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48288.14</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-41933.88</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B0DB5VVPSB</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>48294.07</v>
-      </c>
-      <c r="C3" t="n">
-        <v>41007.63</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-7286.44</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4192.38</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-4192.38</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>56441.54</v>
-      </c>
-      <c r="C5" t="n">
-        <v>34418.64</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-22022.9</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>B0DP2VVRND</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>94867.73</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5082.21</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-89785.52</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>28245.76</v>
-      </c>
-      <c r="C7" t="n">
-        <v>27957.63</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-288.13</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>34168.34</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2711.02</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-31457.32</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+          <t>clean — Cross-source sales drift (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -1143,32 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sales_trend_units</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ams_trend_units</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -1176,147 +996,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>39</v>
-      </c>
-      <c r="C2" t="n">
-        <v>41954.88</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41915.88</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B0DB5VVPSB</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C3" t="n">
-        <v>7297.44</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7284.44</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4192.38</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4189.38</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>29</v>
-      </c>
-      <c r="C5" t="n">
-        <v>22038.9</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22009.9</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>B0DP2VVRND</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>56</v>
-      </c>
-      <c r="C6" t="n">
-        <v>89788.52</v>
-      </c>
-      <c r="D6" t="n">
-        <v>89732.52</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" t="n">
-        <v>298.13</v>
-      </c>
-      <c r="D7" t="n">
-        <v>288.13</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>13</v>
-      </c>
-      <c r="C8" t="n">
-        <v>31458.32</v>
-      </c>
-      <c r="D8" t="n">
-        <v>31445.32</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+          <t>clean — Cross-source units drift (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -1655,32 +1335,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sales_trend_amz_side</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ams_trend_gmv</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -1688,21 +1348,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>908097.08</v>
-      </c>
-      <c r="C2" t="n">
-        <v>711130.51</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-196966.57</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
+          <t>clean — AMS Trend GMV vs Sales Trend Amazon-side per brand</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2156,35 +1802,6 @@
         <v>-2.25</v>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>W29</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>908097.08</v>
-      </c>
-      <c r="D14" t="n">
-        <v>711130.51</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-196966.57</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-21.69</v>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
         </is>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -34,6 +34,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_ams_vs_sales_units_per_asin" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_unit_price_sanity" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1812,6 +1814,62 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — AMS units_ordered vs Sales units_sold (per ASIN, latest week)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — Unit price (sales/units) deviates &gt;10x from 4w median (latest week)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_ams_vs_sales_units_per_asin" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_unit_price_sanity" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="28_ams_vs_sales_units_per_asin" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="29_unit_price_sanity" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,16 +45,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -65,7 +62,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -73,21 +70,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,36 +441,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -603,6 +591,30 @@
         <v>15637</v>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15034</v>
+      </c>
+      <c r="E7" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>EXTRA IN SNAPSHOT (stale rows?)</t>
         </is>
@@ -623,32 +635,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw_sku</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>brand_folder</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>weeks_seen</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>total_qty</t>
         </is>
@@ -697,7 +709,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -721,105 +733,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>pair</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>amazon+1p_inventory</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ams_trend_total_amazon</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>sales_trend_inv</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>inv_dashboard_total</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>amazon+1p_vs_ams_trend</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>(load failed)</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales_trend_vs_inv_dashboard</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>(load failed)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
+          <t>clean — Cross-route inventory rule consistency</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -837,7 +765,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -861,31 +789,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>raw_file_spend</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ams_trend_spend</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -894,21 +802,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(load failed)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>clean — Cross-route ads rule consistency</t>
         </is>
       </c>
     </row>
@@ -923,31 +817,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>file_sessions</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ams_trend_sessions</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -956,21 +830,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(load failed)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>clean — Cross-route sessions consistency</t>
         </is>
       </c>
     </row>
@@ -989,7 +849,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1013,31 +873,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>snap_total_sales</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>am1p_route_sales</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1046,21 +886,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(load failed)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>clean — Cross-route per-brand totals consistency</t>
         </is>
       </c>
     </row>
@@ -1079,7 +905,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1103,21 +929,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sales_gmv</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ams_gmv</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>clean — AMS Trend GMV &gt; Sales Trend GMV (per brand×model×wk)</t>
-        </is>
+      <c r="A2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WM-GS1M-BK</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2414</v>
+      </c>
+      <c r="E2" t="n">
+        <v>121227</v>
+      </c>
+      <c r="F2" t="n">
+        <v>118813</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4921</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MS1ML</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>32187</v>
+      </c>
+      <c r="E3" t="n">
+        <v>120203</v>
+      </c>
+      <c r="F3" t="n">
+        <v>88015</v>
+      </c>
+      <c r="G3" t="n">
+        <v>273.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HDWF1ML</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>57778</v>
+      </c>
+      <c r="F4" t="n">
+        <v>57778</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5777803</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WM-HA2M-BK</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1864</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50991</v>
+      </c>
+      <c r="F5" t="n">
+        <v>49128</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2636.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>WM-GS2M-BK</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11184</v>
+      </c>
+      <c r="E6" t="n">
+        <v>40330</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29146</v>
+      </c>
+      <c r="G6" t="n">
+        <v>260.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WM-HA1M-BK</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5590</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5590</v>
+      </c>
+      <c r="G7" t="n">
+        <v>558984</v>
       </c>
     </row>
   </sheetData>
@@ -1135,32 +1146,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1173,20 +1184,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>188956</v>
+        <v>185047</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>185047</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1197,20 +1208,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>177818</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>177818</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1240,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1253,11 +1264,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>latest</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>prior_4w_median</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>delta_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1266,7 +1302,182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand metric &gt; 50% drop or 2x spike vs prior 4w median</t>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ad_spend</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>451125</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>attributed</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2587964</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ad_spend</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>424278</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>attributed</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1759259</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>attributed</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>127116</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ad_spend</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>137812</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>attributed</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>621705</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DROP &gt; 50% vs prior 4-week median</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1496,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1313,7 +1524,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1341,7 +1552,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1369,7 +1580,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1397,7 +1608,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1421,41 +1632,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sales_trend_amz_side</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ams_trend_gmv</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta_rs</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1464,25 +1675,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>667942.12</v>
+        <v>171494.05</v>
       </c>
       <c r="D2" t="n">
-        <v>589134.49</v>
+        <v>161455.91</v>
       </c>
       <c r="E2" t="n">
-        <v>-78807.63</v>
+        <v>-10038.14</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.8</v>
+        <v>-5.85</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1498,20 +1709,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>171494.05</v>
+        <v>713759.26</v>
       </c>
       <c r="D3" t="n">
-        <v>161455.91</v>
+        <v>676492.3199999999</v>
       </c>
       <c r="E3" t="n">
-        <v>-10038.14</v>
+        <v>-37266.94</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.85</v>
+        <v>-5.22</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1522,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1531,16 +1742,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>713759.26</v>
+        <v>1077787.08</v>
       </c>
       <c r="D4" t="n">
-        <v>676492.3199999999</v>
+        <v>971121.8199999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-37266.94</v>
+        <v>-106665.26</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.22</v>
+        <v>-9.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1551,7 +1762,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1560,16 +1771,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1077787.08</v>
+        <v>911351.88</v>
       </c>
       <c r="D5" t="n">
-        <v>971121.8199999999</v>
+        <v>732132.51</v>
       </c>
       <c r="E5" t="n">
-        <v>-106665.26</v>
+        <v>-179219.37</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.9</v>
+        <v>-19.67</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1580,7 +1791,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1589,16 +1800,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>911351.88</v>
+        <v>888714.46</v>
       </c>
       <c r="D6" t="n">
-        <v>736802</v>
+        <v>732317.85</v>
       </c>
       <c r="E6" t="n">
-        <v>-174549.88</v>
+        <v>-156396.61</v>
       </c>
       <c r="F6" t="n">
-        <v>-19.15</v>
+        <v>-17.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1609,7 +1820,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1618,16 +1829,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>888714.46</v>
+        <v>1135238.81</v>
       </c>
       <c r="D7" t="n">
-        <v>734652.59</v>
+        <v>1031959.15</v>
       </c>
       <c r="E7" t="n">
-        <v>-154061.87</v>
+        <v>-103279.66</v>
       </c>
       <c r="F7" t="n">
-        <v>-17.34</v>
+        <v>-9.1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1638,7 +1849,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1647,16 +1858,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1135238.81</v>
+        <v>624059.3199999999</v>
       </c>
       <c r="D8" t="n">
-        <v>1034293.9</v>
+        <v>699655.0600000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-100944.91</v>
+        <v>75595.74000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.890000000000001</v>
+        <v>12.11</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1667,7 +1878,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1676,16 +1887,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>750505.91</v>
+        <v>970911.86</v>
       </c>
       <c r="D9" t="n">
-        <v>699655.0600000001</v>
+        <v>907348.3</v>
       </c>
       <c r="E9" t="n">
-        <v>-50850.85</v>
+        <v>-63563.56</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.78</v>
+        <v>-6.55</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1696,25 +1907,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>970911.86</v>
+        <v>199271.08</v>
       </c>
       <c r="D10" t="n">
-        <v>907348.3</v>
+        <v>181904.13</v>
       </c>
       <c r="E10" t="n">
-        <v>-63563.56</v>
+        <v>-17366.95</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.55</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1730,20 +1941,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>199271.08</v>
+        <v>768346.55</v>
       </c>
       <c r="D11" t="n">
-        <v>188851.59</v>
+        <v>704910.12</v>
       </c>
       <c r="E11" t="n">
-        <v>-10419.49</v>
+        <v>-63436.43</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.23</v>
+        <v>-8.26</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1754,7 +1965,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1763,16 +1974,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>768346.55</v>
+        <v>1122800.58</v>
       </c>
       <c r="D12" t="n">
-        <v>704910.12</v>
+        <v>1090799.74</v>
       </c>
       <c r="E12" t="n">
-        <v>-63436.43</v>
+        <v>-32000.84</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.26</v>
+        <v>-2.85</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1783,27 +1994,56 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>312502.37</v>
+      </c>
+      <c r="D13" t="n">
+        <v>300387.97</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-12114.4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>W28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>white mulberry</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>1122800.58</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1097502.28</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-25298.3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="C14" t="n">
+        <v>1192822.95</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1167062.78</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-25760.17</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
         </is>
@@ -1824,7 +2064,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1852,7 +2092,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1876,31 +2116,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>rule</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>week_num</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1909,23 +2129,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ams_trend.inventory_snapshot (load failed)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>loader raised: ModuleNotFoundError("No module named 'weekly_app'")</t>
+          <t>clean — Never-Zero column regression</t>
         </is>
       </c>
     </row>
@@ -1944,7 +2148,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1968,36 +2172,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -2006,28 +2210,308 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ad_spend</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1384537.88</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>attributed_sales</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>8412745.43</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ad_spend</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1366734.42</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>attributed_sales</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6017686.069999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ad_spend</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>55739.72000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>attributed_sales</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>417905.81</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ad_spend</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>446906.235</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ams_trend</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>(brand-total)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>attributed_sales</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1965638.295</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>inventory</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>white mulberry</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>open order</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>inventory_units</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="E10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>151</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bi worldwide</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>182</v>
+      </c>
+      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2046,22 +2530,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -2346,7 +2830,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2370,11 +2854,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2383,7 +2882,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand missing from a layer (diagnostic)</t>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in sales for W30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in sales for W30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in sales for W30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in sales for W30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in inventory for W30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in inventory for W30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in inventory for W30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in inventory for W30</t>
         </is>
       </c>
     </row>
@@ -2398,36 +3050,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
@@ -4423,6 +5075,126 @@
       </c>
       <c r="F84" t="n">
         <v>1164</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>30</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3206</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>30</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>fossil</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>6108</v>
+      </c>
+      <c r="F86" t="n">
+        <v>6108</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>30</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>10454</v>
+      </c>
+      <c r="F87" t="n">
+        <v>10454</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>30</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>366</v>
+      </c>
+      <c r="F88" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>30</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1008</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1008</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1264,37 +1264,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>latest</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>prior_4w_median</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>delta_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -1302,182 +1277,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>451125</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2587964</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>424278</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1759259</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tonor</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>127116</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>137812</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>attributed</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>621705</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>DROP &gt; 50% vs prior 4-week median</t>
+          <t>clean — Brand metric &gt; 50% drop or 2x spike vs prior 4w median</t>
         </is>
       </c>
     </row>
@@ -2172,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2210,26 +2010,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ad_spend</t>
+          <t>inventory_units</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1384537.88</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2238,7 +2038,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2248,16 +2048,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>flipkart</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>attributed_sales</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8412745.43</v>
+        <v>151</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2266,7 +2066,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ams_trend</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2276,242 +2076,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(brand-total)</t>
+          <t>bi worldwide</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ad_spend</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1366734.42</v>
+        <v>182</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>attributed_sales</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6017686.069999999</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>55739.72000000001</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>attributed_sales</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>417905.81</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ad_spend</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>446906.235</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ams_trend</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>(brand-total)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>attributed_sales</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1965638.295</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>inventory_units</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>151</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bi worldwide</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>182</v>
-      </c>
-      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>15034</v>
+        <v>15078</v>
       </c>
       <c r="E7" t="n">
-        <v>15034</v>
+        <v>15078</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -631,67 +631,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>raw_sku</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>brand_folder</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>weeks_seen</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>total_qty</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0GYSS16FJ</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FBA80111</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36</v>
+          <t>clean — (info) Off-master ASINs in raw inv</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1187,10 +1141,10 @@
         <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>185047</v>
+        <v>185084</v>
       </c>
       <c r="D2" t="n">
-        <v>185047</v>
+        <v>185084</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1211,10 +1165,10 @@
         <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>177818</v>
+        <v>177855</v>
       </c>
       <c r="D3" t="n">
-        <v>177818</v>
+        <v>177855</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4695,10 +4649,10 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>6108</v>
+        <v>6101</v>
       </c>
       <c r="F86" t="n">
-        <v>6108</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="87">
@@ -4719,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>10454</v>
+        <v>10497</v>
       </c>
       <c r="F87" t="n">
-        <v>10454</v>
+        <v>10497</v>
       </c>
     </row>
     <row r="88">
@@ -4767,10 +4721,10 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F89" t="n">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>15078</v>
+        <v>14854</v>
       </c>
       <c r="E7" t="n">
-        <v>15078</v>
+        <v>14854</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>185084</v>
+        <v>184743</v>
       </c>
       <c r="D2" t="n">
-        <v>185084</v>
+        <v>184743</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>177855</v>
+        <v>177514</v>
       </c>
       <c r="D3" t="n">
-        <v>177855</v>
+        <v>177514</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3206</v>
+        <v>3145</v>
       </c>
       <c r="F85" t="n">
-        <v>3206</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="86">
@@ -4649,10 +4649,10 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>6101</v>
+        <v>5984</v>
       </c>
       <c r="F86" t="n">
-        <v>6101</v>
+        <v>5984</v>
       </c>
     </row>
     <row r="87">
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>10497</v>
+        <v>10428</v>
       </c>
       <c r="F87" t="n">
-        <v>10497</v>
+        <v>10428</v>
       </c>
     </row>
     <row r="88">
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F88" t="n">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="89">
@@ -4721,10 +4721,10 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>1009</v>
+        <v>917</v>
       </c>
       <c r="F89" t="n">
-        <v>1009</v>
+        <v>917</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>14854</v>
+        <v>14876</v>
       </c>
       <c r="E7" t="n">
-        <v>14854</v>
+        <v>14876</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>184743</v>
+        <v>184763</v>
       </c>
       <c r="D2" t="n">
-        <v>184743</v>
+        <v>184763</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>177514</v>
+        <v>177534</v>
       </c>
       <c r="D3" t="n">
-        <v>177514</v>
+        <v>177534</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3145</v>
+        <v>3140</v>
       </c>
       <c r="F85" t="n">
-        <v>3145</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="86">
@@ -4649,10 +4649,10 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>5984</v>
+        <v>5982</v>
       </c>
       <c r="F86" t="n">
-        <v>5984</v>
+        <v>5982</v>
       </c>
     </row>
     <row r="87">
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>10428</v>
+        <v>10435</v>
       </c>
       <c r="F87" t="n">
-        <v>10428</v>
+        <v>10435</v>
       </c>
     </row>
     <row r="88">
@@ -4721,10 +4721,10 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>917</v>
+        <v>937</v>
       </c>
       <c r="F89" t="n">
-        <v>917</v>
+        <v>937</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,30 @@
         <v>14876</v>
       </c>
       <c r="F7" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13951</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13951</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>EXTRA IN SNAPSHOT (stale rows?)</t>
         </is>
@@ -715,12 +739,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sales_trend_amzn+1p_gmv</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ams_trend_gmv</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -728,7 +772,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-source sales drift (diagnostic)</t>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>186372.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>186372.8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>44735.59</v>
+      </c>
+      <c r="C3" t="n">
+        <v>66594.91</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21859.32</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1481.36</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9866.120000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8384.76</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7454.24</v>
+      </c>
+      <c r="C5" t="n">
+        <v>48111.84</v>
+      </c>
+      <c r="D5" t="n">
+        <v>40657.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8894.07</v>
+      </c>
+      <c r="C6" t="n">
+        <v>122396.47</v>
+      </c>
+      <c r="D6" t="n">
+        <v>113502.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B0DP3194QN</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3143.22</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6108.47</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2965.25</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>70909.37</v>
+      </c>
+      <c r="D8" t="n">
+        <v>70909.37</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
         </is>
       </c>
     </row>
@@ -799,12 +983,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sales_trend_units</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ams_trend_units</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -812,7 +1016,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Cross-source units drift (diagnostic)</t>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>72</v>
+      </c>
+      <c r="D6" t="n">
+        <v>67</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
         </is>
       </c>
     </row>
@@ -925,7 +1248,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -938,21 +1261,21 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2414</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>121227</v>
+        <v>186373</v>
       </c>
       <c r="F2" t="n">
-        <v>118813</v>
+        <v>186373</v>
       </c>
       <c r="G2" t="n">
-        <v>4921</v>
+        <v>18637280</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -965,21 +1288,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32187</v>
+        <v>8894</v>
       </c>
       <c r="E3" t="n">
-        <v>120203</v>
+        <v>122396</v>
       </c>
       <c r="F3" t="n">
-        <v>88015</v>
+        <v>113502</v>
       </c>
       <c r="G3" t="n">
-        <v>273.4</v>
+        <v>1276.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -995,18 +1318,18 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>57778</v>
+        <v>70909</v>
       </c>
       <c r="F4" t="n">
-        <v>57778</v>
+        <v>70909</v>
       </c>
       <c r="G4" t="n">
-        <v>5777803</v>
+        <v>7090937</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1019,21 +1342,21 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1864</v>
+        <v>7454</v>
       </c>
       <c r="E5" t="n">
-        <v>50991</v>
+        <v>48112</v>
       </c>
       <c r="F5" t="n">
-        <v>49128</v>
+        <v>40658</v>
       </c>
       <c r="G5" t="n">
-        <v>2636.2</v>
+        <v>545.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1046,21 +1369,21 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11184</v>
+        <v>44736</v>
       </c>
       <c r="E6" t="n">
-        <v>40330</v>
+        <v>66595</v>
       </c>
       <c r="F6" t="n">
-        <v>29146</v>
+        <v>21859</v>
       </c>
       <c r="G6" t="n">
-        <v>260.6</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1073,16 +1396,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1481</v>
       </c>
       <c r="E7" t="n">
-        <v>5590</v>
+        <v>9866</v>
       </c>
       <c r="F7" t="n">
-        <v>5590</v>
+        <v>8385</v>
       </c>
       <c r="G7" t="n">
-        <v>558984</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -1138,13 +1461,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>184763</v>
+        <v>181896</v>
       </c>
       <c r="D2" t="n">
-        <v>184763</v>
+        <v>181896</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1162,13 +1485,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>177534</v>
+        <v>174472</v>
       </c>
       <c r="D3" t="n">
-        <v>177534</v>
+        <v>174472</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1302,12 +1625,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sales_trend_amz_side</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ams_trend_gmv</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -1315,7 +1658,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — AMS Trend GMV vs Sales Trend Amazon-side per brand</t>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>538616.98</v>
+      </c>
+      <c r="C2" t="n">
+        <v>983268.48</v>
+      </c>
+      <c r="D2" t="n">
+        <v>444651.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,25 +1786,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>171494.05</v>
+        <v>1077787.08</v>
       </c>
       <c r="D2" t="n">
-        <v>161455.91</v>
+        <v>971121.8199999999</v>
       </c>
       <c r="E2" t="n">
-        <v>-10038.14</v>
+        <v>-106665.26</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.85</v>
+        <v>-9.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1458,7 +1815,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1467,16 +1824,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>713759.26</v>
+        <v>911351.88</v>
       </c>
       <c r="D3" t="n">
-        <v>676492.3199999999</v>
+        <v>732132.51</v>
       </c>
       <c r="E3" t="n">
-        <v>-37266.94</v>
+        <v>-179219.37</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.22</v>
+        <v>-19.67</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1487,7 +1844,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1496,16 +1853,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1077787.08</v>
+        <v>888714.46</v>
       </c>
       <c r="D4" t="n">
-        <v>971121.8199999999</v>
+        <v>732317.85</v>
       </c>
       <c r="E4" t="n">
-        <v>-106665.26</v>
+        <v>-156396.61</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.9</v>
+        <v>-17.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1516,7 +1873,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1525,16 +1882,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>911351.88</v>
+        <v>1135238.81</v>
       </c>
       <c r="D5" t="n">
-        <v>732132.51</v>
+        <v>1031959.15</v>
       </c>
       <c r="E5" t="n">
-        <v>-179219.37</v>
+        <v>-103279.66</v>
       </c>
       <c r="F5" t="n">
-        <v>-19.67</v>
+        <v>-9.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1545,7 +1902,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1554,16 +1911,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>888714.46</v>
+        <v>624059.3199999999</v>
       </c>
       <c r="D6" t="n">
-        <v>732317.85</v>
+        <v>699655.0600000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-156396.61</v>
+        <v>75595.74000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-17.6</v>
+        <v>12.11</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1574,7 +1931,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1583,16 +1940,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1135238.81</v>
+        <v>970911.86</v>
       </c>
       <c r="D7" t="n">
-        <v>1031959.15</v>
+        <v>907348.3</v>
       </c>
       <c r="E7" t="n">
-        <v>-103279.66</v>
+        <v>-63563.56</v>
       </c>
       <c r="F7" t="n">
-        <v>-9.1</v>
+        <v>-6.55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1603,25 +1960,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>624059.3199999999</v>
+        <v>199271.08</v>
       </c>
       <c r="D8" t="n">
-        <v>699655.0600000001</v>
+        <v>181904.13</v>
       </c>
       <c r="E8" t="n">
-        <v>75595.74000000001</v>
+        <v>-17366.95</v>
       </c>
       <c r="F8" t="n">
-        <v>12.11</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1632,7 +1989,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1641,16 +1998,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>970911.86</v>
+        <v>768346.55</v>
       </c>
       <c r="D9" t="n">
-        <v>907348.3</v>
+        <v>704910.12</v>
       </c>
       <c r="E9" t="n">
-        <v>-63563.56</v>
+        <v>-63436.43</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.55</v>
+        <v>-8.26</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1661,25 +2018,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>199271.08</v>
+        <v>1122800.58</v>
       </c>
       <c r="D10" t="n">
-        <v>181904.13</v>
+        <v>1090799.74</v>
       </c>
       <c r="E10" t="n">
-        <v>-17366.95</v>
+        <v>-32000.84</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.720000000000001</v>
+        <v>-2.85</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1690,7 +2047,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1699,16 +2056,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>768346.55</v>
+        <v>1192822.95</v>
       </c>
       <c r="D11" t="n">
-        <v>704910.12</v>
+        <v>1167062.78</v>
       </c>
       <c r="E11" t="n">
-        <v>-63436.43</v>
+        <v>-25760.17</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.26</v>
+        <v>-2.16</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1719,7 +2076,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1728,76 +2085,18 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1122800.58</v>
+        <v>538616.98</v>
       </c>
       <c r="D12" t="n">
-        <v>1090799.74</v>
+        <v>983268.48</v>
       </c>
       <c r="E12" t="n">
-        <v>-32000.84</v>
+        <v>444651.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.85</v>
+        <v>82.55</v>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>W28</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>312502.37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>300387.97</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-12114.4</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-3.88</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>W28</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1192822.95</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1167062.78</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-25760.17</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-2.16</v>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
         </is>
@@ -1926,7 +2225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1964,26 +2263,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>flipkart</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>inventory_units</t>
+          <t>units_sold</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2000</v>
+        <v>79</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1997,12 +2296,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flipkart</t>
+          <t>bi worldwide</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2011,7 +2310,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2030,7 +2329,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bi worldwide</t>
+          <t>pharmaeasy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2039,9 +2338,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1p sales</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>482</v>
+      </c>
+      <c r="F5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2421,11 +2748,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MISSING — no rows for audio array in sales for W30</t>
+          <t>MISSING — no rows for audio array in sales for W31</t>
         </is>
       </c>
     </row>
@@ -2441,11 +2768,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MISSING — no rows for nexlev in sales for W30</t>
+          <t>MISSING — no rows for nexlev in sales for W31</t>
         </is>
       </c>
     </row>
@@ -2461,11 +2788,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MISSING — no rows for tonor in sales for W30</t>
+          <t>MISSING — no rows for tonor in sales for W31</t>
         </is>
       </c>
     </row>
@@ -2481,11 +2808,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MISSING — no rows for white mulberry in sales for W30</t>
+          <t>MISSING — no rows for white mulberry in sales for W31</t>
         </is>
       </c>
     </row>
@@ -2501,11 +2828,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MISSING — no rows for audio array in inventory for W30</t>
+          <t>MISSING — no rows for audio array in inventory for W31</t>
         </is>
       </c>
     </row>
@@ -2521,11 +2848,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MISSING — no rows for nexlev in inventory for W30</t>
+          <t>MISSING — no rows for nexlev in inventory for W31</t>
         </is>
       </c>
     </row>
@@ -2541,11 +2868,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MISSING — no rows for tonor in inventory for W30</t>
+          <t>MISSING — no rows for tonor in inventory for W31</t>
         </is>
       </c>
     </row>
@@ -2561,11 +2888,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MISSING — no rows for white mulberry in inventory for W30</t>
+          <t>MISSING — no rows for white mulberry in inventory for W31</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4727,6 +5054,126 @@
         <v>937</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>31</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3085</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3085</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>31</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>fossil</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>5927</v>
+      </c>
+      <c r="F91" t="n">
+        <v>5927</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>31</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>9522</v>
+      </c>
+      <c r="F92" t="n">
+        <v>9522</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>31</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>364</v>
+      </c>
+      <c r="F93" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>31</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>980</v>
+      </c>
+      <c r="F94" t="n">
+        <v>980</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -633,10 +633,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>13951</v>
+        <v>13942</v>
       </c>
       <c r="E8" t="n">
-        <v>13951</v>
+        <v>13942</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -739,32 +739,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>sales_trend_amzn+1p_gmv</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ams_trend_gmv</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -772,147 +752,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>186372.8</v>
-      </c>
-      <c r="D2" t="n">
-        <v>186372.8</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B0DB5VVPSB</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>44735.59</v>
-      </c>
-      <c r="C3" t="n">
-        <v>66594.91</v>
-      </c>
-      <c r="D3" t="n">
-        <v>21859.32</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1481.36</v>
-      </c>
-      <c r="C4" t="n">
-        <v>9866.120000000001</v>
-      </c>
-      <c r="D4" t="n">
-        <v>8384.76</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7454.24</v>
-      </c>
-      <c r="C5" t="n">
-        <v>48111.84</v>
-      </c>
-      <c r="D5" t="n">
-        <v>40657.6</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>B0DP2VVRND</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>8894.07</v>
-      </c>
-      <c r="C6" t="n">
-        <v>122396.47</v>
-      </c>
-      <c r="D6" t="n">
-        <v>113502.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>B0DP3194QN</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3143.22</v>
-      </c>
-      <c r="C7" t="n">
-        <v>6108.47</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2965.25</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>70909.37</v>
-      </c>
-      <c r="D8" t="n">
-        <v>70909.37</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AMAZON+1P GMV drifts between sales_snapshot and business_ads_joined</t>
+          <t>clean — Cross-source sales drift (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -983,32 +823,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>sales_trend_units</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ams_trend_units</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -1016,126 +836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>80</v>
-      </c>
-      <c r="D2" t="n">
-        <v>80</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B0DB5VVPSB</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C3" t="n">
-        <v>19</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>28</v>
-      </c>
-      <c r="D5" t="n">
-        <v>24</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>B0DP2VVRND</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>72</v>
-      </c>
-      <c r="D6" t="n">
-        <v>67</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>27</v>
-      </c>
-      <c r="D7" t="n">
-        <v>27</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AMAZON+1P UNITS drift between sales_snapshot and business_ads_joined</t>
+          <t>clean — Cross-source units drift (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -1464,10 +1165,10 @@
         <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>181896</v>
+        <v>181883</v>
       </c>
       <c r="D2" t="n">
-        <v>181896</v>
+        <v>181883</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1488,10 +1189,10 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>174472</v>
+        <v>174459</v>
       </c>
       <c r="D3" t="n">
-        <v>174472</v>
+        <v>174459</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1625,32 +1326,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>sales_trend_amz_side</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ams_trend_gmv</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -1658,21 +1339,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>538616.98</v>
-      </c>
-      <c r="C2" t="n">
-        <v>983268.48</v>
-      </c>
-      <c r="D2" t="n">
-        <v>444651.5</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AMS Trend GMV ≠ Sales Trend Amazon-side gross_sales — one chain is missing a 3P/1P source or column format</t>
+          <t>clean — AMS Trend GMV vs Sales Trend Amazon-side per brand</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2068,35 +1735,6 @@
         <v>-2.16</v>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>W31</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>538616.98</v>
-      </c>
-      <c r="D12" t="n">
-        <v>983268.48</v>
-      </c>
-      <c r="E12" t="n">
-        <v>444651.5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>82.55</v>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
         </is>
@@ -2225,7 +1863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2341,34 +1979,6 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1p sales</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>482</v>
-      </c>
-      <c r="F5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5072,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>3085</v>
+        <v>3083</v>
       </c>
       <c r="F90" t="n">
-        <v>3085</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="91">
@@ -5096,10 +4706,10 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>5927</v>
+        <v>5923</v>
       </c>
       <c r="F91" t="n">
-        <v>5927</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="92">
@@ -5120,10 +4730,10 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>9522</v>
+        <v>9515</v>
       </c>
       <c r="F92" t="n">
-        <v>9522</v>
+        <v>9515</v>
       </c>
     </row>
     <row r="93">

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -633,10 +633,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>13942</v>
+        <v>13932</v>
       </c>
       <c r="E8" t="n">
-        <v>13942</v>
+        <v>13932</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -907,206 +907,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>sales_gmv</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ams_gmv</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>pct</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>WM-GS1M-BK</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>186373</v>
-      </c>
-      <c r="F2" t="n">
-        <v>186373</v>
-      </c>
-      <c r="G2" t="n">
-        <v>18637280</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MS1ML</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>8894</v>
-      </c>
-      <c r="E3" t="n">
-        <v>122396</v>
-      </c>
-      <c r="F3" t="n">
-        <v>113502</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1276.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HDWF1ML</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>70909</v>
-      </c>
-      <c r="F4" t="n">
-        <v>70909</v>
-      </c>
-      <c r="G4" t="n">
-        <v>7090937</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>WM-HA2M-BK</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>7454</v>
-      </c>
-      <c r="E5" t="n">
-        <v>48112</v>
-      </c>
-      <c r="F5" t="n">
-        <v>40658</v>
-      </c>
-      <c r="G5" t="n">
-        <v>545.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>WM-GS2M-BK</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>44736</v>
-      </c>
-      <c r="E6" t="n">
-        <v>66595</v>
-      </c>
-      <c r="F6" t="n">
-        <v>21859</v>
-      </c>
-      <c r="G6" t="n">
-        <v>48.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>WM-HA1M-BK</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="E7" t="n">
-        <v>9866</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8385</v>
-      </c>
-      <c r="G7" t="n">
-        <v>566</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>clean — AMS Trend GMV &gt; Sales Trend GMV (per brand×model×wk)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1165,10 +980,10 @@
         <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>181883</v>
+        <v>181872</v>
       </c>
       <c r="D2" t="n">
-        <v>181883</v>
+        <v>181872</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1189,10 +1004,10 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>174459</v>
+        <v>174448</v>
       </c>
       <c r="D3" t="n">
-        <v>174459</v>
+        <v>174448</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4682,10 +4497,10 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>3083</v>
+        <v>3080</v>
       </c>
       <c r="F90" t="n">
-        <v>3083</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="91">
@@ -4706,10 +4521,10 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>5923</v>
+        <v>5922</v>
       </c>
       <c r="F91" t="n">
-        <v>5923</v>
+        <v>5922</v>
       </c>
     </row>
     <row r="92">
@@ -4730,10 +4545,10 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>9515</v>
+        <v>9511</v>
       </c>
       <c r="F92" t="n">
-        <v>9515</v>
+        <v>9511</v>
       </c>
     </row>
     <row r="93">
@@ -4754,10 +4569,10 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F93" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="94">

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="28_ams_vs_sales_units_per_asin" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="29_unit_price_sanity" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_ams_vs_sales_units_per_asin" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_unit_price_sanity" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,13 +45,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -62,7 +65,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -70,12 +73,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,36 +453,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -478,7 +490,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,13 +498,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17825</v>
+        <v>20449</v>
       </c>
       <c r="D2" t="n">
-        <v>17975</v>
+        <v>20429</v>
       </c>
       <c r="E2" t="n">
-        <v>150</v>
+        <v>-20</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -502,7 +514,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -510,23 +522,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>19485</v>
       </c>
       <c r="D3" t="n">
-        <v>19699</v>
+        <v>19466</v>
       </c>
       <c r="E3" t="n">
-        <v>19699</v>
+        <v>-19</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -534,23 +546,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>18970</v>
       </c>
       <c r="D4" t="n">
-        <v>15309</v>
+        <v>18810</v>
       </c>
       <c r="E4" t="n">
-        <v>15309</v>
+        <v>-160</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -558,23 +570,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>17597</v>
       </c>
       <c r="D5" t="n">
-        <v>16274</v>
+        <v>17477</v>
       </c>
       <c r="E5" t="n">
-        <v>16274</v>
+        <v>-120</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -582,23 +594,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="D6" t="n">
-        <v>15637</v>
+        <v>16878</v>
       </c>
       <c r="E6" t="n">
-        <v>15637</v>
+        <v>-122</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -606,41 +618,353 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>17825</v>
       </c>
       <c r="D7" t="n">
-        <v>14876</v>
+        <v>17975</v>
       </c>
       <c r="E7" t="n">
-        <v>14876</v>
+        <v>150</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>17000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16975</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>16174</v>
+      </c>
+      <c r="D9" t="n">
+        <v>16149</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>19699</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19699</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15309</v>
+      </c>
+      <c r="E11" t="n">
+        <v>15309</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16274</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16274</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15637</v>
+      </c>
+      <c r="E13" t="n">
+        <v>15637</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>14876</v>
+      </c>
+      <c r="E14" t="n">
+        <v>14876</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>31</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D15" t="n">
         <v>13932</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E15" t="n">
         <v>13932</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>31</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>78897</v>
+      </c>
+      <c r="D16" t="n">
+        <v>152804</v>
+      </c>
+      <c r="E16" t="n">
+        <v>73907</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>31</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5015</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10008</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4993</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>31</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>blinkit</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2930</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1465</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>31</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>37500</v>
+      </c>
+      <c r="D19" t="n">
+        <v>74920</v>
+      </c>
+      <c r="E19" t="n">
+        <v>37420</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>31</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>26256</v>
+      </c>
+      <c r="D20" t="n">
+        <v>50504</v>
+      </c>
+      <c r="E20" t="n">
+        <v>24248</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>31</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ynt</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>944</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1874</v>
+      </c>
+      <c r="E21" t="n">
+        <v>930</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
@@ -659,7 +983,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -687,7 +1011,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -715,7 +1039,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -743,7 +1067,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -771,7 +1095,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -799,7 +1123,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -827,7 +1151,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -855,7 +1179,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -879,21 +1203,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>brand_folder</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weeks_seen</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — (info) Off-master ASINs in raw sales</t>
-        </is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FBA79347</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>other_channels</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pharmaeasy</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -911,7 +1291,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -939,32 +1319,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -980,10 +1360,10 @@
         <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>181872</v>
+        <v>324835</v>
       </c>
       <c r="D2" t="n">
-        <v>181872</v>
+        <v>324835</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1004,10 +1384,10 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>174448</v>
+        <v>310023</v>
       </c>
       <c r="D3" t="n">
-        <v>174448</v>
+        <v>310023</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1033,7 +1413,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1061,7 +1441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1089,7 +1469,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1117,7 +1497,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1145,7 +1525,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1173,7 +1553,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1201,7 +1581,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1225,41 +1605,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sales_trend_amz_side</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ams_trend_gmv</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>delta_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1268,290 +1618,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W20</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1077787.08</v>
-      </c>
-      <c r="D2" t="n">
-        <v>971121.8199999999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-106665.26</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>W21</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>911351.88</v>
-      </c>
-      <c r="D3" t="n">
-        <v>732132.51</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-179219.37</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-19.67</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>W22</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>888714.46</v>
-      </c>
-      <c r="D4" t="n">
-        <v>732317.85</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-156396.61</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-17.6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>W23</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1135238.81</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1031959.15</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-103279.66</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>W24</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>624059.3199999999</v>
-      </c>
-      <c r="D6" t="n">
-        <v>699655.0600000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>75595.74000000001</v>
-      </c>
-      <c r="F6" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>W25</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>970911.86</v>
-      </c>
-      <c r="D7" t="n">
-        <v>907348.3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-63563.56</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-6.55</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>W26</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>199271.08</v>
-      </c>
-      <c r="D8" t="n">
-        <v>181904.13</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-17366.95</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>W26</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>768346.55</v>
-      </c>
-      <c r="D9" t="n">
-        <v>704910.12</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-63436.43</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-8.26</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>W27</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1122800.58</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1090799.74</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-32000.84</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>W28</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1192822.95</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1167062.78</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-25760.17</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-2.16</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+          <t>clean — AMS Trend GMV vs Sales Trend Amazon+1P per brand (ALL weeks)</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1637,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1598,7 +1665,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1626,7 +1693,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1654,7 +1721,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1678,36 +1745,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1735,7 +1802,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1766,34 +1833,6 @@
         <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>pharmaeasy</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>units_sold</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1812,22 +1851,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -2112,7 +2151,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2136,26 +2175,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2164,160 +2188,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in sales for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>31</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in sales for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>31</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in sales for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>31</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in sales for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>31</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in inventory for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>31</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in inventory for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>31</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in inventory for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>31</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W31</t>
+          <t>clean — Brand missing from a layer (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -2332,36 +2203,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
@@ -2378,17 +2249,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1168</v>
+        <v>13006</v>
       </c>
       <c r="E2" t="n">
-        <v>1163</v>
+        <v>12986</v>
       </c>
       <c r="F2" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="3">
@@ -2397,7 +2268,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2406,22 +2277,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>1168</v>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>1163</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2430,13 +2301,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>297</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>230</v>
+        <v>34</v>
       </c>
       <c r="F4" t="n">
-        <v>-67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -2450,22 +2321,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3228</v>
+        <v>12180</v>
       </c>
       <c r="E5" t="n">
-        <v>3295</v>
+        <v>12161</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2489,7 +2360,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2513,7 +2384,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2522,113 +2393,113 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>38019</v>
+        <v>4609</v>
       </c>
       <c r="E8" t="n">
-        <v>38238</v>
+        <v>4449</v>
       </c>
       <c r="F8" t="n">
-        <v>219</v>
+        <v>-160</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ampm</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40948</v>
+        <v>297</v>
       </c>
       <c r="E9" t="n">
-        <v>40729</v>
+        <v>230</v>
       </c>
       <c r="F9" t="n">
-        <v>-219</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2497</v>
+        <v>3228</v>
       </c>
       <c r="E10" t="n">
-        <v>2467</v>
+        <v>3295</v>
       </c>
       <c r="F10" t="n">
-        <v>-30</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>ampm</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6013</v>
+        <v>38019</v>
       </c>
       <c r="E11" t="n">
-        <v>5959</v>
+        <v>38238</v>
       </c>
       <c r="F11" t="n">
-        <v>-54</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>ampm</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>40948</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>40729</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>-219</v>
       </c>
     </row>
     <row r="13">
@@ -2637,27 +2508,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>11393</v>
       </c>
       <c r="E13" t="n">
-        <v>184</v>
+        <v>11273</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2670,18 +2541,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2526</v>
+        <v>2497</v>
       </c>
       <c r="E14" t="n">
-        <v>2506</v>
+        <v>2467</v>
       </c>
       <c r="F14" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2694,10 +2565,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5830</v>
+        <v>6013</v>
       </c>
       <c r="E15" t="n">
-        <v>5776</v>
+        <v>5959</v>
       </c>
       <c r="F15" t="n">
         <v>-54</v>
@@ -2705,7 +2576,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2718,18 +2589,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2753,11 +2624,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2766,22 +2637,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4067</v>
+        <v>10862</v>
       </c>
       <c r="E18" t="n">
-        <v>4070</v>
+        <v>10742</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2790,94 +2661,94 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1476</v>
       </c>
       <c r="E19" t="n">
-        <v>5565</v>
+        <v>1474</v>
       </c>
       <c r="F19" t="n">
-        <v>5565</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11931</v>
+        <v>2526</v>
       </c>
       <c r="E20" t="n">
-        <v>12071</v>
+        <v>2506</v>
       </c>
       <c r="F20" t="n">
-        <v>140</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>508</v>
+        <v>5830</v>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>5776</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1319</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1324</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2886,13 +2757,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2367</v>
+        <v>130</v>
       </c>
       <c r="E23" t="n">
-        <v>2317</v>
+        <v>184</v>
       </c>
       <c r="F23" t="n">
-        <v>-50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
@@ -2901,22 +2772,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5524</v>
+        <v>4067</v>
       </c>
       <c r="E24" t="n">
-        <v>5470</v>
+        <v>4070</v>
       </c>
       <c r="F24" t="n">
-        <v>-54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -2925,22 +2796,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>50</v>
+        <v>5240</v>
       </c>
       <c r="F25" t="n">
-        <v>50</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="26">
@@ -2949,31 +2820,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>130</v>
+        <v>11931</v>
       </c>
       <c r="E26" t="n">
-        <v>184</v>
+        <v>12071</v>
       </c>
       <c r="F26" t="n">
-        <v>54</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2982,138 +2853,138 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="E27" t="n">
-        <v>5337</v>
+        <v>510</v>
       </c>
       <c r="F27" t="n">
-        <v>5337</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>34971</v>
+        <v>1319</v>
       </c>
       <c r="E28" t="n">
-        <v>3860</v>
+        <v>1324</v>
       </c>
       <c r="F28" t="n">
-        <v>-31111</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9300</v>
+        <v>2367</v>
       </c>
       <c r="E29" t="n">
-        <v>38403</v>
+        <v>2317</v>
       </c>
       <c r="F29" t="n">
-        <v>29103</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2490</v>
+        <v>5524</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>5470</v>
       </c>
       <c r="F30" t="n">
-        <v>-2490</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>4998</v>
+        <v>50</v>
       </c>
       <c r="F31" t="n">
-        <v>4498</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E32" t="n">
-        <v>5014</v>
+        <v>184</v>
       </c>
       <c r="F32" t="n">
-        <v>5014</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3129,259 +3000,259 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>5288</v>
+        <v>5337</v>
       </c>
       <c r="F33" t="n">
-        <v>5288</v>
+        <v>5337</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>34971</v>
       </c>
       <c r="E34" t="n">
-        <v>5226</v>
+        <v>3860</v>
       </c>
       <c r="F34" t="n">
-        <v>5226</v>
+        <v>-31111</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9279</v>
+        <v>9300</v>
       </c>
       <c r="E35" t="n">
-        <v>9179</v>
+        <v>38403</v>
       </c>
       <c r="F35" t="n">
-        <v>-100</v>
+        <v>29103</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3024</v>
+        <v>2490</v>
       </c>
       <c r="E36" t="n">
-        <v>3124</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>-2490</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E37" t="n">
-        <v>6455</v>
+        <v>4998</v>
       </c>
       <c r="F37" t="n">
-        <v>6455</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>42</v>
+        <v>5014</v>
       </c>
       <c r="F38" t="n">
-        <v>-13</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>131</v>
+        <v>5288</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>5288</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>5226</v>
       </c>
       <c r="F40" t="n">
-        <v>-2</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>9279</v>
       </c>
       <c r="E41" t="n">
-        <v>16</v>
+        <v>9179</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="E42" t="n">
-        <v>6635</v>
+        <v>3124</v>
       </c>
       <c r="F42" t="n">
-        <v>6635</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>42</v>
+        <v>6455</v>
       </c>
       <c r="F43" t="n">
-        <v>-13</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3390,22 +3261,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="E44" t="n">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="F44" t="n">
-        <v>9</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3414,22 +3285,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>122</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="F45" t="n">
-        <v>-2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3438,22 +3309,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3462,46 +3333,46 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="E47" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="F47" t="n">
-        <v>-13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>128</v>
+        <v>6635</v>
       </c>
       <c r="F48" t="n">
-        <v>9</v>
+        <v>6635</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3510,22 +3381,22 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F49" t="n">
-        <v>-2</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3534,18 +3405,18 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="E50" t="n">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3554,22 +3425,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3578,290 +3449,290 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E52" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F52" t="n">
-        <v>-4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>10628</v>
       </c>
       <c r="E53" t="n">
-        <v>9</v>
+        <v>10603</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F54" t="n">
-        <v>-4</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="E55" t="n">
+        <v>128</v>
+      </c>
+      <c r="F55" t="n">
         <v>9</v>
-      </c>
-      <c r="F55" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>18</v>
+        <v>9769</v>
       </c>
       <c r="E58" t="n">
-        <v>14</v>
+        <v>9744</v>
       </c>
       <c r="F58" t="n">
-        <v>-4</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>4210</v>
+        <v>9</v>
       </c>
       <c r="F59" t="n">
-        <v>4210</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E60" t="n">
-        <v>6916</v>
+        <v>13</v>
       </c>
       <c r="F60" t="n">
-        <v>6916</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>13582</v>
+        <v>9</v>
       </c>
       <c r="F61" t="n">
-        <v>13582</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E62" t="n">
-        <v>409</v>
+        <v>14</v>
       </c>
       <c r="F62" t="n">
-        <v>409</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>1498</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>1498</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3870,22 +3741,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3894,46 +3765,46 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F65" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E66" t="n">
-        <v>3631</v>
+        <v>14</v>
       </c>
       <c r="F66" t="n">
-        <v>3631</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3945,19 +3816,19 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>6583</v>
+        <v>4210</v>
       </c>
       <c r="F67" t="n">
-        <v>6583</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3969,19 +3840,19 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>9798</v>
+        <v>6916</v>
       </c>
       <c r="F68" t="n">
-        <v>9798</v>
+        <v>6916</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3993,19 +3864,19 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>454</v>
+        <v>13582</v>
       </c>
       <c r="F69" t="n">
-        <v>454</v>
+        <v>13582</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4017,43 +3888,43 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1426</v>
+        <v>409</v>
       </c>
       <c r="F70" t="n">
-        <v>1426</v>
+        <v>409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>8</v>
+        <v>1498</v>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4062,46 +3933,46 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E73" t="n">
-        <v>3584</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
-        <v>3584</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4113,19 +3984,19 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>6280</v>
+        <v>3631</v>
       </c>
       <c r="F74" t="n">
-        <v>6280</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4137,19 +4008,19 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>11034</v>
+        <v>6583</v>
       </c>
       <c r="F75" t="n">
-        <v>11034</v>
+        <v>6583</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4161,19 +4032,19 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>414</v>
+        <v>9798</v>
       </c>
       <c r="F76" t="n">
-        <v>414</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4185,43 +4056,43 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1242</v>
+        <v>454</v>
       </c>
       <c r="F77" t="n">
-        <v>1242</v>
+        <v>454</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>1426</v>
       </c>
       <c r="F78" t="n">
-        <v>4</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4230,46 +4101,46 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E80" t="n">
-        <v>3338</v>
+        <v>14</v>
       </c>
       <c r="F80" t="n">
-        <v>3338</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4281,19 +4152,19 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>6323</v>
+        <v>3584</v>
       </c>
       <c r="F81" t="n">
-        <v>6323</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4305,19 +4176,19 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10739</v>
+        <v>6280</v>
       </c>
       <c r="F82" t="n">
-        <v>10739</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4329,19 +4200,19 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>396</v>
+        <v>11034</v>
       </c>
       <c r="F83" t="n">
-        <v>396</v>
+        <v>11034</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4353,19 +4224,19 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>1164</v>
+        <v>414</v>
       </c>
       <c r="F84" t="n">
-        <v>1164</v>
+        <v>414</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4377,67 +4248,67 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3140</v>
+        <v>1242</v>
       </c>
       <c r="F85" t="n">
-        <v>3140</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>5982</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
-        <v>5982</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E87" t="n">
-        <v>10435</v>
+        <v>14</v>
       </c>
       <c r="F87" t="n">
-        <v>10435</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4449,19 +4320,19 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>364</v>
+        <v>3338</v>
       </c>
       <c r="F88" t="n">
-        <v>364</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4473,19 +4344,19 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>937</v>
+        <v>6323</v>
       </c>
       <c r="F89" t="n">
-        <v>937</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4497,19 +4368,19 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>3080</v>
+        <v>10739</v>
       </c>
       <c r="F90" t="n">
-        <v>3080</v>
+        <v>10739</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4521,19 +4392,19 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>5922</v>
+        <v>396</v>
       </c>
       <c r="F91" t="n">
-        <v>5922</v>
+        <v>396</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4545,19 +4416,19 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>9511</v>
+        <v>1164</v>
       </c>
       <c r="F92" t="n">
-        <v>9511</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4569,19 +4440,19 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>361</v>
+        <v>3140</v>
       </c>
       <c r="F93" t="n">
-        <v>361</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4593,10 +4464,490 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
+        <v>5982</v>
+      </c>
+      <c r="F94" t="n">
+        <v>5982</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>30</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>10435</v>
+      </c>
+      <c r="F95" t="n">
+        <v>10435</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>30</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>364</v>
+      </c>
+      <c r="F96" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>30</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>937</v>
+      </c>
+      <c r="F97" t="n">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>31</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3080</v>
+      </c>
+      <c r="F98" t="n">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>31</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>fossil</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>5922</v>
+      </c>
+      <c r="F99" t="n">
+        <v>5922</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>31</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>9511</v>
+      </c>
+      <c r="F100" t="n">
+        <v>9511</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>31</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>361</v>
+      </c>
+      <c r="F101" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>31</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
         <v>980</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F102" t="n">
         <v>980</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>31</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>37492</v>
+      </c>
+      <c r="E103" t="n">
+        <v>74984</v>
+      </c>
+      <c r="F103" t="n">
+        <v>37492</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>31</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ampm</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>36415</v>
+      </c>
+      <c r="E104" t="n">
+        <v>72830</v>
+      </c>
+      <c r="F104" t="n">
+        <v>36415</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>31</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>950</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F105" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>31</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>b2b - ampm</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>4043</v>
+      </c>
+      <c r="E106" t="n">
+        <v>8086</v>
+      </c>
+      <c r="F106" t="n">
+        <v>4043</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>31</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>blinkit</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>399</v>
+      </c>
+      <c r="E107" t="n">
+        <v>798</v>
+      </c>
+      <c r="F107" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>31</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>blinkit</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1066</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2132</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>31</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>23696</v>
+      </c>
+      <c r="E109" t="n">
+        <v>47392</v>
+      </c>
+      <c r="F109" t="n">
+        <v>23696</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>31</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>open order</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>13724</v>
+      </c>
+      <c r="E110" t="n">
+        <v>27448</v>
+      </c>
+      <c r="F110" t="n">
+        <v>13724</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>31</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>9729</v>
+      </c>
+      <c r="E111" t="n">
+        <v>19458</v>
+      </c>
+      <c r="F111" t="n">
+        <v>9729</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>31</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>14519</v>
+      </c>
+      <c r="E112" t="n">
+        <v>29038</v>
+      </c>
+      <c r="F112" t="n">
+        <v>14519</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>31</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ynt</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>134</v>
+      </c>
+      <c r="E113" t="n">
+        <v>268</v>
+      </c>
+      <c r="F113" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>31</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ynt</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>796</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1592</v>
+      </c>
+      <c r="F114" t="n">
+        <v>796</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,150 +821,6 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>EXTRA IN SNAPSHOT (stale rows?)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>31</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>78897</v>
-      </c>
-      <c r="D16" t="n">
-        <v>152804</v>
-      </c>
-      <c r="E16" t="n">
-        <v>73907</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>UNITS MISMATCH (silent drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>31</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>5015</v>
-      </c>
-      <c r="D17" t="n">
-        <v>10008</v>
-      </c>
-      <c r="E17" t="n">
-        <v>4993</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UNITS MISMATCH (silent drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>31</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>blinkit</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1465</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2930</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1465</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UNITS MISMATCH (silent drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>31</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>37500</v>
-      </c>
-      <c r="D19" t="n">
-        <v>74920</v>
-      </c>
-      <c r="E19" t="n">
-        <v>37420</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UNITS MISMATCH (silent drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>31</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>26256</v>
-      </c>
-      <c r="D20" t="n">
-        <v>50504</v>
-      </c>
-      <c r="E20" t="n">
-        <v>24248</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>UNITS MISMATCH (silent drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>31</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ynt</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>944</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1874</v>
-      </c>
-      <c r="E21" t="n">
-        <v>930</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
@@ -1360,10 +1216,10 @@
         <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>324835</v>
+        <v>181872</v>
       </c>
       <c r="D2" t="n">
-        <v>324835</v>
+        <v>181872</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1384,10 +1240,10 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>310023</v>
+        <v>174448</v>
       </c>
       <c r="D3" t="n">
-        <v>310023</v>
+        <v>174448</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2203,7 +2059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,294 +4518,6 @@
         <v>980</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>31</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>37492</v>
-      </c>
-      <c r="E103" t="n">
-        <v>74984</v>
-      </c>
-      <c r="F103" t="n">
-        <v>37492</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>31</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>ampm</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>36415</v>
-      </c>
-      <c r="E104" t="n">
-        <v>72830</v>
-      </c>
-      <c r="F104" t="n">
-        <v>36415</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>31</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>950</v>
-      </c>
-      <c r="E105" t="n">
-        <v>1900</v>
-      </c>
-      <c r="F105" t="n">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>31</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>b2b - ampm</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>4043</v>
-      </c>
-      <c r="E106" t="n">
-        <v>8086</v>
-      </c>
-      <c r="F106" t="n">
-        <v>4043</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>31</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>blinkit</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>399</v>
-      </c>
-      <c r="E107" t="n">
-        <v>798</v>
-      </c>
-      <c r="F107" t="n">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>31</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>blinkit</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>1066</v>
-      </c>
-      <c r="E108" t="n">
-        <v>2132</v>
-      </c>
-      <c r="F108" t="n">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>31</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>23696</v>
-      </c>
-      <c r="E109" t="n">
-        <v>47392</v>
-      </c>
-      <c r="F109" t="n">
-        <v>23696</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>31</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>open order</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>13724</v>
-      </c>
-      <c r="E110" t="n">
-        <v>27448</v>
-      </c>
-      <c r="F110" t="n">
-        <v>13724</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>31</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>9729</v>
-      </c>
-      <c r="E111" t="n">
-        <v>19458</v>
-      </c>
-      <c r="F111" t="n">
-        <v>9729</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>31</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>14519</v>
-      </c>
-      <c r="E112" t="n">
-        <v>29038</v>
-      </c>
-      <c r="F112" t="n">
-        <v>14519</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>31</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>ynt</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>134</v>
-      </c>
-      <c r="E113" t="n">
-        <v>268</v>
-      </c>
-      <c r="F113" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>31</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>ynt</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>796</v>
-      </c>
-      <c r="E114" t="n">
-        <v>1592</v>
-      </c>
-      <c r="F114" t="n">
-        <v>796</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_ams_vs_sales_units_per_asin" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_unit_price_sanity" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="28_ams_vs_sales_units_per_asin" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="29_unit_price_sanity" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,16 +45,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -65,7 +62,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -73,21 +70,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,36 +441,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -490,7 +478,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -498,13 +486,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20449</v>
+        <v>17825</v>
       </c>
       <c r="D2" t="n">
-        <v>20429</v>
+        <v>17975</v>
       </c>
       <c r="E2" t="n">
-        <v>-20</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,7 +502,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -522,23 +510,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19485</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>19466</v>
+        <v>19699</v>
       </c>
       <c r="E3" t="n">
-        <v>-19</v>
+        <v>19699</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UNITS MISMATCH (silent drop)</t>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -546,23 +534,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18970</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>18810</v>
+        <v>15309</v>
       </c>
       <c r="E4" t="n">
-        <v>-160</v>
+        <v>15309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UNITS MISMATCH (silent drop)</t>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -570,23 +558,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17597</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>17477</v>
+        <v>16274</v>
       </c>
       <c r="E5" t="n">
-        <v>-120</v>
+        <v>16274</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNITS MISMATCH (silent drop)</t>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -594,23 +582,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>16878</v>
+        <v>15637</v>
       </c>
       <c r="E6" t="n">
-        <v>-122</v>
+        <v>15637</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNITS MISMATCH (silent drop)</t>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -618,23 +606,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17825</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>17975</v>
+        <v>14876</v>
       </c>
       <c r="E7" t="n">
-        <v>150</v>
+        <v>14876</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UNITS MISMATCH (silent drop)</t>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -642,183 +630,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>16975</v>
+        <v>13783</v>
       </c>
       <c r="E8" t="n">
-        <v>-25</v>
+        <v>13783</v>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>UNITS MISMATCH (silent drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>16174</v>
-      </c>
-      <c r="D9" t="n">
-        <v>16149</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-25</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UNITS MISMATCH (silent drop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>26</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>19699</v>
-      </c>
-      <c r="E10" t="n">
-        <v>19699</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>27</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>15309</v>
-      </c>
-      <c r="E11" t="n">
-        <v>15309</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>28</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>16274</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16274</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>29</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15637</v>
-      </c>
-      <c r="E13" t="n">
-        <v>15637</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>30</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14876</v>
-      </c>
-      <c r="E14" t="n">
-        <v>14876</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>31</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>13932</v>
-      </c>
-      <c r="E15" t="n">
-        <v>13932</v>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>EXTRA IN SNAPSHOT (stale rows?)</t>
         </is>
@@ -839,7 +659,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -867,7 +687,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -895,7 +715,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -923,7 +743,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -951,7 +771,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -979,7 +799,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1007,7 +827,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1035,7 +855,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1059,77 +879,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>raw_sku</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>brand_folder</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>weeks_seen</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>total_units</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FBA79347</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>other_channels</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pharmaeasy</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2</v>
+          <t>clean — (info) Off-master ASINs in raw sales</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1147,7 +911,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1175,32 +939,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1216,10 +980,10 @@
         <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>181872</v>
+        <v>181727</v>
       </c>
       <c r="D2" t="n">
-        <v>181872</v>
+        <v>181727</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1240,10 +1004,10 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>174448</v>
+        <v>174303</v>
       </c>
       <c r="D3" t="n">
-        <v>174448</v>
+        <v>174303</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1269,7 +1033,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1297,7 +1061,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1325,7 +1089,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1353,7 +1117,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1381,7 +1145,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1409,7 +1173,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1437,7 +1201,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1461,11 +1225,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sales_trend_amz_side</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ams_trend_gmv</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>delta_rs</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delta_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1474,7 +1268,290 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — AMS Trend GMV vs Sales Trend Amazon+1P per brand (ALL weeks)</t>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1077787.08</v>
+      </c>
+      <c r="D2" t="n">
+        <v>971121.8199999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-106665.26</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>911351.88</v>
+      </c>
+      <c r="D3" t="n">
+        <v>732132.51</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-179219.37</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>888714.46</v>
+      </c>
+      <c r="D4" t="n">
+        <v>732317.85</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-156396.61</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1135238.81</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1031959.15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-103279.66</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W24</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>624059.3199999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>699655.0600000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75595.74000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>W25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>970911.86</v>
+      </c>
+      <c r="D7" t="n">
+        <v>907348.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-63563.56</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-6.55</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>199271.08</v>
+      </c>
+      <c r="D8" t="n">
+        <v>181904.13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-17366.95</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>W26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>768346.55</v>
+      </c>
+      <c r="D9" t="n">
+        <v>704910.12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-63436.43</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>W27</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1122800.58</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1090799.74</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-32000.84</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>W28</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1192822.95</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1167062.78</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-25760.17</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1570,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1521,7 +1598,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1549,7 +1626,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1577,7 +1654,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1601,36 +1678,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1689,6 +1766,34 @@
         <v>99</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pharmaeasy</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>units_sold</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1707,22 +1812,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -2007,7 +2112,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2031,11 +2136,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2044,7 +2164,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand missing from a layer (diagnostic)</t>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in sales for W31</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in sales for W31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in sales for W31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in sales for W31</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>audio array</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for audio array in inventory for W31</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for nexlev in inventory for W31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tonor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>31</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for tonor in inventory for W31</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>31</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MISSING — no rows for white mulberry in inventory for W31</t>
         </is>
       </c>
     </row>
@@ -2059,36 +2332,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
@@ -2105,17 +2378,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13006</v>
+        <v>1168</v>
       </c>
       <c r="E2" t="n">
-        <v>12986</v>
+        <v>1163</v>
       </c>
       <c r="F2" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="3">
@@ -2124,7 +2397,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2133,22 +2406,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1168</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>1163</v>
+        <v>34</v>
       </c>
       <c r="F3" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2157,13 +2430,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>297</v>
       </c>
       <c r="E4" t="n">
-        <v>34</v>
+        <v>230</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="5">
@@ -2177,22 +2450,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12180</v>
+        <v>3228</v>
       </c>
       <c r="E5" t="n">
-        <v>12161</v>
+        <v>3295</v>
       </c>
       <c r="F5" t="n">
-        <v>-19</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2216,7 +2489,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2240,7 +2513,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2249,113 +2522,113 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>ampm</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4609</v>
+        <v>38019</v>
       </c>
       <c r="E8" t="n">
-        <v>4449</v>
+        <v>38238</v>
       </c>
       <c r="F8" t="n">
-        <v>-160</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>ampm</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>40948</v>
       </c>
       <c r="E9" t="n">
-        <v>230</v>
+        <v>40729</v>
       </c>
       <c r="F9" t="n">
-        <v>-67</v>
+        <v>-219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3228</v>
+        <v>2497</v>
       </c>
       <c r="E10" t="n">
-        <v>3295</v>
+        <v>2467</v>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ampm</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38019</v>
+        <v>6013</v>
       </c>
       <c r="E11" t="n">
-        <v>38238</v>
+        <v>5959</v>
       </c>
       <c r="F11" t="n">
-        <v>219</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ampm</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>40948</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>40729</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>-219</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -2364,27 +2637,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11393</v>
+        <v>130</v>
       </c>
       <c r="E13" t="n">
-        <v>11273</v>
+        <v>184</v>
       </c>
       <c r="F13" t="n">
-        <v>-120</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2397,18 +2670,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2497</v>
+        <v>2526</v>
       </c>
       <c r="E14" t="n">
-        <v>2467</v>
+        <v>2506</v>
       </c>
       <c r="F14" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2421,10 +2694,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6013</v>
+        <v>5830</v>
       </c>
       <c r="E15" t="n">
-        <v>5959</v>
+        <v>5776</v>
       </c>
       <c r="F15" t="n">
         <v>-54</v>
@@ -2432,7 +2705,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2445,18 +2718,18 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
         <v>20</v>
       </c>
-      <c r="E16" t="n">
-        <v>50</v>
-      </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2480,11 +2753,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2493,22 +2766,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10862</v>
+        <v>4067</v>
       </c>
       <c r="E18" t="n">
-        <v>10742</v>
+        <v>4070</v>
       </c>
       <c r="F18" t="n">
-        <v>-120</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2517,94 +2790,94 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1476</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1474</v>
+        <v>5565</v>
       </c>
       <c r="F19" t="n">
-        <v>-2</v>
+        <v>5565</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2526</v>
+        <v>11931</v>
       </c>
       <c r="E20" t="n">
-        <v>2506</v>
+        <v>12071</v>
       </c>
       <c r="F20" t="n">
-        <v>-20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5830</v>
+        <v>508</v>
       </c>
       <c r="E21" t="n">
-        <v>5776</v>
+        <v>510</v>
       </c>
       <c r="F21" t="n">
-        <v>-54</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1319</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>1324</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2613,13 +2886,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>130</v>
+        <v>2367</v>
       </c>
       <c r="E23" t="n">
-        <v>184</v>
+        <v>2317</v>
       </c>
       <c r="F23" t="n">
-        <v>54</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="24">
@@ -2628,22 +2901,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4067</v>
+        <v>5524</v>
       </c>
       <c r="E24" t="n">
-        <v>4070</v>
+        <v>5470</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="25">
@@ -2652,22 +2925,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>5240</v>
+        <v>50</v>
       </c>
       <c r="F25" t="n">
-        <v>5240</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -2676,31 +2949,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11931</v>
+        <v>130</v>
       </c>
       <c r="E26" t="n">
-        <v>12071</v>
+        <v>184</v>
       </c>
       <c r="F26" t="n">
-        <v>140</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2709,138 +2982,138 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>5337</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>5337</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1319</v>
+        <v>34971</v>
       </c>
       <c r="E28" t="n">
-        <v>1324</v>
+        <v>3860</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>-31111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2367</v>
+        <v>9300</v>
       </c>
       <c r="E29" t="n">
-        <v>2317</v>
+        <v>38403</v>
       </c>
       <c r="F29" t="n">
-        <v>-50</v>
+        <v>29103</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5524</v>
+        <v>2490</v>
       </c>
       <c r="E30" t="n">
-        <v>5470</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-54</v>
+        <v>-2490</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>open order</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E31" t="n">
-        <v>50</v>
+        <v>4998</v>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>184</v>
+        <v>5014</v>
       </c>
       <c r="F32" t="n">
-        <v>54</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2856,259 +3129,259 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>5337</v>
+        <v>5288</v>
       </c>
       <c r="F33" t="n">
-        <v>5337</v>
+        <v>5288</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>34971</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>3860</v>
+        <v>5226</v>
       </c>
       <c r="F34" t="n">
-        <v>-31111</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9300</v>
+        <v>9279</v>
       </c>
       <c r="E35" t="n">
-        <v>38403</v>
+        <v>9179</v>
       </c>
       <c r="F35" t="n">
-        <v>29103</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2490</v>
+        <v>3024</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>3124</v>
       </c>
       <c r="F36" t="n">
-        <v>-2490</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>open order</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>4998</v>
+        <v>6455</v>
       </c>
       <c r="F37" t="n">
-        <v>4498</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E38" t="n">
-        <v>5014</v>
+        <v>42</v>
       </c>
       <c r="F38" t="n">
-        <v>5014</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="E39" t="n">
-        <v>5288</v>
+        <v>131</v>
       </c>
       <c r="F39" t="n">
-        <v>5288</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5226</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>5226</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>17</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>white mulberry</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ynt</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="n">
         <v>16</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>pipeline</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>9279</v>
-      </c>
-      <c r="E41" t="n">
-        <v>9179</v>
-      </c>
       <c r="F41" t="n">
-        <v>-100</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>3124</v>
+        <v>6635</v>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
+        <v>6635</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E43" t="n">
-        <v>6455</v>
+        <v>42</v>
       </c>
       <c r="F43" t="n">
-        <v>6455</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3117,22 +3390,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="E44" t="n">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="F44" t="n">
-        <v>-13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3141,22 +3414,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3165,22 +3438,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F46" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3189,46 +3462,46 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E47" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="E48" t="n">
-        <v>6635</v>
+        <v>128</v>
       </c>
       <c r="F48" t="n">
-        <v>6635</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3237,22 +3510,22 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>-13</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3261,18 +3534,18 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="E50" t="n">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="F50" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3281,22 +3554,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F51" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3305,290 +3578,290 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E52" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10628</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>10603</v>
+        <v>9</v>
       </c>
       <c r="F53" t="n">
-        <v>-25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="E54" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F54" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>119</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="F55" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>9769</v>
+        <v>18</v>
       </c>
       <c r="E58" t="n">
-        <v>9744</v>
+        <v>14</v>
       </c>
       <c r="F58" t="n">
-        <v>-25</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>9</v>
+        <v>4210</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>13</v>
+        <v>6916</v>
       </c>
       <c r="F60" t="n">
-        <v>-4</v>
+        <v>6916</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>9</v>
+        <v>13582</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>13582</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>14</v>
+        <v>409</v>
       </c>
       <c r="F62" t="n">
-        <v>-4</v>
+        <v>409</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>1498</v>
       </c>
       <c r="F63" t="n">
-        <v>4</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3597,22 +3870,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3621,46 +3894,46 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E65" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>14</v>
+        <v>3631</v>
       </c>
       <c r="F66" t="n">
-        <v>-4</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3672,19 +3945,19 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>4210</v>
+        <v>6583</v>
       </c>
       <c r="F67" t="n">
-        <v>4210</v>
+        <v>6583</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3696,19 +3969,19 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>6916</v>
+        <v>9798</v>
       </c>
       <c r="F68" t="n">
-        <v>6916</v>
+        <v>9798</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3720,19 +3993,19 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>13582</v>
+        <v>454</v>
       </c>
       <c r="F69" t="n">
-        <v>13582</v>
+        <v>454</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3744,43 +4017,43 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>409</v>
+        <v>1426</v>
       </c>
       <c r="F70" t="n">
-        <v>409</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>1498</v>
+        <v>8</v>
       </c>
       <c r="F71" t="n">
-        <v>1498</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3789,46 +4062,46 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>3584</v>
       </c>
       <c r="F73" t="n">
-        <v>-4</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3840,19 +4113,19 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>3631</v>
+        <v>6280</v>
       </c>
       <c r="F74" t="n">
-        <v>3631</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3864,19 +4137,19 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>6583</v>
+        <v>11034</v>
       </c>
       <c r="F75" t="n">
-        <v>6583</v>
+        <v>11034</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3888,19 +4161,19 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>9798</v>
+        <v>414</v>
       </c>
       <c r="F76" t="n">
-        <v>9798</v>
+        <v>414</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3912,43 +4185,43 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>454</v>
+        <v>1242</v>
       </c>
       <c r="F77" t="n">
-        <v>454</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>b2b - ampm</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
-        <v>1426</v>
+        <v>8</v>
       </c>
       <c r="F78" t="n">
-        <v>1426</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3957,46 +4230,46 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>14</v>
+        <v>3338</v>
       </c>
       <c r="F80" t="n">
-        <v>-4</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4008,19 +4281,19 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>3584</v>
+        <v>6323</v>
       </c>
       <c r="F81" t="n">
-        <v>3584</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4032,19 +4305,19 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6280</v>
+        <v>10739</v>
       </c>
       <c r="F82" t="n">
-        <v>6280</v>
+        <v>10739</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4056,19 +4329,19 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>11034</v>
+        <v>396</v>
       </c>
       <c r="F83" t="n">
-        <v>11034</v>
+        <v>396</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4080,19 +4353,19 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>414</v>
+        <v>1164</v>
       </c>
       <c r="F84" t="n">
-        <v>414</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4104,67 +4377,67 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>1242</v>
+        <v>3140</v>
       </c>
       <c r="F85" t="n">
-        <v>1242</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>8</v>
+        <v>5982</v>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>5982</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>14</v>
+        <v>10435</v>
       </c>
       <c r="F87" t="n">
-        <v>-4</v>
+        <v>10435</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4176,19 +4449,19 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>3338</v>
+        <v>364</v>
       </c>
       <c r="F88" t="n">
-        <v>3338</v>
+        <v>364</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4200,19 +4473,19 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>6323</v>
+        <v>937</v>
       </c>
       <c r="F89" t="n">
-        <v>6323</v>
+        <v>937</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4224,19 +4497,19 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>10739</v>
+        <v>3032</v>
       </c>
       <c r="F90" t="n">
-        <v>10739</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>tonor</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4248,19 +4521,19 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>396</v>
+        <v>5926</v>
       </c>
       <c r="F91" t="n">
-        <v>396</v>
+        <v>5926</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4272,19 +4545,19 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>1164</v>
+        <v>9436</v>
       </c>
       <c r="F92" t="n">
-        <v>1164</v>
+        <v>9436</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4296,19 +4569,19 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>3140</v>
+        <v>354</v>
       </c>
       <c r="F93" t="n">
-        <v>3140</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4320,202 +4593,10 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>5982</v>
+        <v>961</v>
       </c>
       <c r="F94" t="n">
-        <v>5982</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>30</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="n">
-        <v>10435</v>
-      </c>
-      <c r="F95" t="n">
-        <v>10435</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>30</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="n">
-        <v>364</v>
-      </c>
-      <c r="F96" t="n">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>30</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="n">
-        <v>937</v>
-      </c>
-      <c r="F97" t="n">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>31</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" t="n">
-        <v>3080</v>
-      </c>
-      <c r="F98" t="n">
-        <v>3080</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>31</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
-        <v>5922</v>
-      </c>
-      <c r="F99" t="n">
-        <v>5922</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>31</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="n">
-        <v>9511</v>
-      </c>
-      <c r="F100" t="n">
-        <v>9511</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>31</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>361</v>
-      </c>
-      <c r="F101" t="n">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>31</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="n">
-        <v>980</v>
-      </c>
-      <c r="F102" t="n">
-        <v>980</v>
+        <v>961</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -633,10 +633,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>13783</v>
+        <v>13777</v>
       </c>
       <c r="E8" t="n">
-        <v>13783</v>
+        <v>13777</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
         <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>181727</v>
+        <v>181720</v>
       </c>
       <c r="D2" t="n">
-        <v>181727</v>
+        <v>181720</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1004,10 +1004,10 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>174303</v>
+        <v>174296</v>
       </c>
       <c r="D3" t="n">
-        <v>174303</v>
+        <v>174296</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4497,10 +4497,10 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>3032</v>
+        <v>3028</v>
       </c>
       <c r="F90" t="n">
-        <v>3032</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="91">
@@ -4521,10 +4521,10 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>5926</v>
+        <v>5925</v>
       </c>
       <c r="F91" t="n">
-        <v>5926</v>
+        <v>5925</v>
       </c>
     </row>
     <row r="92">
@@ -4545,10 +4545,10 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>9436</v>
+        <v>9434</v>
       </c>
       <c r="F92" t="n">
-        <v>9436</v>
+        <v>9434</v>
       </c>
     </row>
     <row r="93">

--- a/data/processed/pipeline_integrity_audit.xlsx
+++ b/data/processed/pipeline_integrity_audit.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="28_ams_vs_sales_units_per_asin" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="29_unit_price_sanity" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_raw_vs_snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_snapshot_vs_route" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_never_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_channel_case_drift" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_went_to_zero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_master_completeness" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_brand_name_consistency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_latest_week_presence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_brand_retags_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_off_master_asins" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_raw_vs_snap_sales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_cross_route_inv" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_cross_route_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_cross_route_ads" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_cross_route_sessions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_cross_route_units" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_cross_route_brands" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_off_master_sales" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_ams_gt_sales_per_model" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_derivative_freshness" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_brand_magnitude_regression" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_category_coverage" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_sp_api_ingestion" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_ams_vs_sales_brand" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_inv_snapshot_freshness" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_pit_snapshot_freshness" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_ams_vs_sales_brand_history" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_ams_vs_sales_units_per_asin" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_unit_price_sanity" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,13 +45,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -62,7 +65,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -70,12 +73,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,36 +453,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -478,7 +490,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,13 +498,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17825</v>
+        <v>20449</v>
       </c>
       <c r="D2" t="n">
-        <v>17975</v>
+        <v>20429</v>
       </c>
       <c r="E2" t="n">
-        <v>150</v>
+        <v>-20</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -502,7 +514,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -510,23 +522,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>19485</v>
       </c>
       <c r="D3" t="n">
-        <v>19699</v>
+        <v>19466</v>
       </c>
       <c r="E3" t="n">
-        <v>19699</v>
+        <v>-19</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -534,23 +546,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>18970</v>
       </c>
       <c r="D4" t="n">
-        <v>15309</v>
+        <v>18810</v>
       </c>
       <c r="E4" t="n">
-        <v>15309</v>
+        <v>-160</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -558,23 +570,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>17597</v>
       </c>
       <c r="D5" t="n">
-        <v>16274</v>
+        <v>17477</v>
       </c>
       <c r="E5" t="n">
-        <v>16274</v>
+        <v>-120</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -582,23 +594,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="D6" t="n">
-        <v>15637</v>
+        <v>16878</v>
       </c>
       <c r="E6" t="n">
-        <v>15637</v>
+        <v>-122</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -606,39 +618,231 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>17825</v>
       </c>
       <c r="D7" t="n">
-        <v>14876</v>
+        <v>17975</v>
       </c>
       <c r="E7" t="n">
-        <v>14876</v>
+        <v>150</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+          <t>UNITS MISMATCH (silent drop)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>17000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16975</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>16174</v>
+      </c>
+      <c r="D9" t="n">
+        <v>16149</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UNITS MISMATCH (silent drop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>19699</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19699</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15309</v>
+      </c>
+      <c r="E11" t="n">
+        <v>15309</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16274</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16274</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15637</v>
+      </c>
+      <c r="E13" t="n">
+        <v>15637</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>14876</v>
+      </c>
+      <c r="E14" t="n">
+        <v>14876</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>31</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
         <v>13777</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E15" t="n">
         <v>13777</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>EXTRA IN SNAPSHOT (stale rows?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>32</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13728</v>
+      </c>
+      <c r="E16" t="n">
+        <v>13728</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>EXTRA IN SNAPSHOT (stale rows?)</t>
         </is>
@@ -659,7 +863,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -687,7 +891,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -715,7 +919,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -743,7 +947,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -771,7 +975,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -799,7 +1003,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -827,7 +1031,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -855,7 +1059,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -879,21 +1083,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>asin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>raw_sku</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>brand_folder</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weeks_seen</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — (info) Off-master ASINs in raw sales</t>
-        </is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FBA79347</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nexlev</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>other_channels</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pharmaeasy</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -911,7 +1171,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -939,32 +1199,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>route_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -977,13 +1237,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>181720</v>
+        <v>182936</v>
       </c>
       <c r="D2" t="n">
-        <v>181720</v>
+        <v>182936</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1001,13 +1261,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>174296</v>
+        <v>175387</v>
       </c>
       <c r="D3" t="n">
-        <v>174296</v>
+        <v>175387</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1033,7 +1293,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1057,11 +1317,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>latest</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>prior_4w_median</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>delta_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1070,7 +1355,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>clean — Brand metric &gt; 50% drop or 2x spike vs prior 4w median</t>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sessions</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>361629</v>
+      </c>
+      <c r="D2" t="n">
+        <v>117888</v>
+      </c>
+      <c r="E2" t="n">
+        <v>206.8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SPIKE &gt; 2x vs prior 4-week median</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1393,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1117,7 +1421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1145,7 +1449,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1173,7 +1477,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1201,7 +1505,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1225,41 +1529,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sales_trend_amz_side</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ams_trend_gmv</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>delta_rs</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>delta_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1268,290 +1542,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W20</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1077787.08</v>
-      </c>
-      <c r="D2" t="n">
-        <v>971121.8199999999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-106665.26</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>W21</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>911351.88</v>
-      </c>
-      <c r="D3" t="n">
-        <v>732132.51</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-179219.37</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-19.67</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>W22</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>888714.46</v>
-      </c>
-      <c r="D4" t="n">
-        <v>732317.85</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-156396.61</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-17.6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>W23</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1135238.81</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1031959.15</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-103279.66</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>W24</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>624059.3199999999</v>
-      </c>
-      <c r="D6" t="n">
-        <v>699655.0600000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>75595.74000000001</v>
-      </c>
-      <c r="F6" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>W25</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>970911.86</v>
-      </c>
-      <c r="D7" t="n">
-        <v>907348.3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-63563.56</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-6.55</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>W26</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>199271.08</v>
-      </c>
-      <c r="D8" t="n">
-        <v>181904.13</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-17366.95</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>W26</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>768346.55</v>
-      </c>
-      <c r="D9" t="n">
-        <v>704910.12</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-63436.43</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-8.26</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>W27</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1122800.58</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1090799.74</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-32000.84</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>W28</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1192822.95</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1167062.78</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-25760.17</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-2.16</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AMS Trend brand-week GMV drifts from Sales Trend Amazon+1P &gt;= 2% AND &gt;= Rs 10,000 — possible brand mis-tag (see Fossil-to-AA pattern of 2026-07-13) OR missing/duplicate source ingest for this brand-week</t>
+          <t>clean — AMS Trend GMV vs Sales Trend Amazon+1P per brand (ALL weeks)</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1561,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1598,7 +1589,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1626,7 +1617,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1654,7 +1645,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1682,32 +1673,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>prior_3wk</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
@@ -1721,12 +1712,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flipkart</t>
+          <t>bi worldwide</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1735,7 +1726,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1754,7 +1745,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bi worldwide</t>
+          <t>pharmaeasy</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1763,7 +1754,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1777,12 +1768,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>tonor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pharmaeasy</t>
+          <t>flipkart</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1791,7 +1782,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1812,22 +1803,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
@@ -2112,7 +2103,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2136,26 +2127,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2164,160 +2140,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in sales for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>31</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in sales for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>31</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in sales for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>31</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in sales for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>audio array</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>31</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for audio array in inventory for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nexlev</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>31</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for nexlev in inventory for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tonor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>31</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for tonor in inventory for W31</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>white mulberry</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>31</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MISSING — no rows for white mulberry in inventory for W31</t>
+          <t>clean — Brand missing from a layer (diagnostic)</t>
         </is>
       </c>
     </row>
@@ -2332,36 +2155,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week_num</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>raw_units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>snap_units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
@@ -2378,17 +2201,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1168</v>
+        <v>13006</v>
       </c>
       <c r="E2" t="n">
-        <v>1163</v>
+        <v>12986</v>
       </c>
       <c r="F2" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="3">
@@ -2397,7 +2220,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white mulberry</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2406,22 +2229,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>1168</v>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>1163</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>white mulberry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2430,13 +2253,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>297</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>230</v>
+        <v>34</v>
       </c>
       <c r="F4" t="n">
-        <v>-67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -2450,22 +2273,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ynt</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3228</v>
+        <v>12180</v>
       </c>
       <c r="E5" t="n">
-        <v>3295</v>
+        <v>12161</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2489,7 +2312,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2513,7 +2336,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2522,113 +2345,113 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ampm</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>38019</v>
+        <v>4609</v>
       </c>
       <c r="E8" t="n">
-        <v>38238</v>
+        <v>4449</v>
       </c>
       <c r="F8" t="n">
-        <v>219</v>
+        <v>-160</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nexlev</t>
+          <t>audio array</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ampm</t>
+          <t>ynt</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40948</v>
+        <v>297</v>
       </c>
       <c r="E9" t="n">
-        <v>40729</v>
+        <v>230</v>
       </c>
       <c r="F9" t="n">
-        <v>-219</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>audio array</t>
+          <t>nexlev</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>b2b - ampm</t>
+          <t>